--- a/currentbuild/all-profiles.xlsx
+++ b/currentbuild/all-profiles.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3840" uniqueCount="594">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3841" uniqueCount="595">
   <si>
     <t>Property</t>
   </si>
@@ -732,7 +732,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://hl7.no/fhir/ig/demo-at/StructureDefinition/demo-at-patient)
+    <t xml:space="preserve">Reference(http://hl7.eu/fhir/base/StructureDefinition/patient-eu-core)
 </t>
   </si>
   <si>
@@ -776,10 +776,13 @@
     <t>AllergyIntolerance.recordedDate</t>
   </si>
   <si>
-    <t>Date when the allergy or intolerance was recorded</t>
-  </si>
-  <si>
-    <t>The recordedDate represents when this particular AllergyIntolerance record was created in the system, which is often a system-generated date.</t>
+    <t>Registreringsdato</t>
+  </si>
+  <si>
+    <t>Dato for registrering av allergi eller intoleranse</t>
+  </si>
+  <si>
+    <t>Obligatorisk i Kjernejournal</t>
   </si>
   <si>
     <t>AllergyIntolerance.recorder</t>
@@ -974,7 +977,7 @@
     <t>Clinical symptoms/signs associated with the Event</t>
   </si>
   <si>
-    <t>Clinical symptoms and/or signs that are observed or associated with the adverse reaction event.</t>
+    <t>Eksempel på kommentar/tillegg i norsk utgave</t>
   </si>
   <si>
     <t>Manifestation can be expressed as a single word, phrase or brief description. For example: nausea, rash or no reaction. It is preferable that manifestation should be coded with a terminology, where possible. The values entered here may be used to display on an application screen as part of a list of adverse reactions, as recommended in the UK NHS CUI guidelines.  Terminologies commonly used include, but are not limited to, SNOMED CT or ICD10.</t>
@@ -2199,7 +2202,7 @@
         <v>2</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
     </row>
     <row r="24">
@@ -2207,7 +2210,7 @@
         <v>4</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="25">
@@ -2223,7 +2226,7 @@
         <v>8</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
     </row>
     <row r="27">
@@ -2231,7 +2234,7 @@
         <v>10</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
     </row>
     <row r="28">
@@ -2285,7 +2288,7 @@
         <v>23</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
     </row>
     <row r="35">
@@ -2321,7 +2324,7 @@
         <v>31</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
     </row>
     <row r="40">
@@ -2329,7 +2332,7 @@
         <v>33</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
     </row>
     <row r="41">
@@ -4202,7 +4205,7 @@
         <v>85</v>
       </c>
       <c r="I18" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="J18" t="s" s="2">
         <v>86</v>
@@ -4307,7 +4310,7 @@
         <v>85</v>
       </c>
       <c r="I19" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="J19" t="s" s="2">
         <v>86</v>
@@ -4727,7 +4730,7 @@
         <v>85</v>
       </c>
       <c r="I23" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="J23" t="s" s="2">
         <v>78</v>
@@ -5238,7 +5241,7 @@
       </c>
       <c r="F28" s="2"/>
       <c r="G28" t="s" s="2">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="H28" t="s" s="2">
         <v>85</v>
@@ -5261,7 +5264,9 @@
       <c r="N28" t="s" s="2">
         <v>242</v>
       </c>
-      <c r="O28" s="2"/>
+      <c r="O28" t="s" s="2">
+        <v>243</v>
+      </c>
       <c r="P28" s="2"/>
       <c r="Q28" t="s" s="2">
         <v>78</v>
@@ -5330,14 +5335,14 @@
         <v>3</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="C29" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="D29" s="2"/>
       <c r="E29" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="F29" s="2"/>
       <c r="G29" t="s" s="2">
@@ -5356,13 +5361,13 @@
         <v>78</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="O29" s="2"/>
       <c r="P29" s="2"/>
@@ -5413,7 +5418,7 @@
         <v>78</v>
       </c>
       <c r="AG29" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="AH29" t="s" s="2">
         <v>76</v>
@@ -5433,14 +5438,14 @@
         <v>3</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="C30" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="D30" s="2"/>
       <c r="E30" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="F30" s="2"/>
       <c r="G30" t="s" s="2">
@@ -5459,16 +5464,16 @@
         <v>86</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="O30" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="P30" s="2"/>
       <c r="Q30" t="s" s="2">
@@ -5518,7 +5523,7 @@
         <v>78</v>
       </c>
       <c r="AG30" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="AH30" t="s" s="2">
         <v>76</v>
@@ -5538,10 +5543,10 @@
         <v>3</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C31" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D31" s="2"/>
       <c r="E31" t="s" s="2">
@@ -5567,13 +5572,13 @@
         <v>168</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="O31" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="P31" s="2"/>
       <c r="Q31" t="s" s="2">
@@ -5623,7 +5628,7 @@
         <v>78</v>
       </c>
       <c r="AG31" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="AH31" t="s" s="2">
         <v>76</v>
@@ -5643,10 +5648,10 @@
         <v>3</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="C32" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="D32" s="2"/>
       <c r="E32" t="s" s="2">
@@ -5669,16 +5674,16 @@
         <v>78</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="O32" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="P32" s="2"/>
       <c r="Q32" t="s" s="2">
@@ -5728,7 +5733,7 @@
         <v>78</v>
       </c>
       <c r="AG32" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="AH32" t="s" s="2">
         <v>76</v>
@@ -5748,10 +5753,10 @@
         <v>3</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="C33" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="D33" s="2"/>
       <c r="E33" t="s" s="2">
@@ -5774,7 +5779,7 @@
         <v>78</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="M33" t="s" s="2">
         <v>143</v>
@@ -5851,10 +5856,10 @@
         <v>3</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="C34" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="D34" s="2"/>
       <c r="E34" t="s" s="2">
@@ -5880,10 +5885,10 @@
         <v>128</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="O34" t="s" s="2">
         <v>174</v>
@@ -5956,10 +5961,10 @@
         <v>3</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="C35" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="D35" s="2"/>
       <c r="E35" t="s" s="2">
@@ -5982,16 +5987,16 @@
         <v>86</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="O35" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="P35" s="2"/>
       <c r="Q35" t="s" s="2">
@@ -6041,7 +6046,7 @@
         <v>78</v>
       </c>
       <c r="AG35" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="AH35" t="s" s="2">
         <v>76</v>
@@ -6061,10 +6066,10 @@
         <v>3</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="C36" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="D36" s="2"/>
       <c r="E36" t="s" s="2">
@@ -6090,10 +6095,10 @@
         <v>168</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="N36" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="O36" s="2"/>
       <c r="P36" s="2"/>
@@ -6144,7 +6149,7 @@
         <v>78</v>
       </c>
       <c r="AG36" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="AH36" t="s" s="2">
         <v>76</v>
@@ -6164,10 +6169,10 @@
         <v>3</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="C37" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="D37" s="2"/>
       <c r="E37" t="s" s="2">
@@ -6190,13 +6195,13 @@
         <v>86</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="O37" s="2"/>
       <c r="P37" s="2"/>
@@ -6247,7 +6252,7 @@
         <v>78</v>
       </c>
       <c r="AG37" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="AH37" t="s" s="2">
         <v>85</v>
@@ -6267,10 +6272,10 @@
         <v>3</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="C38" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="D38" s="2"/>
       <c r="E38" t="s" s="2">
@@ -6293,13 +6298,13 @@
         <v>78</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="O38" s="2"/>
       <c r="P38" s="2"/>
@@ -6350,7 +6355,7 @@
         <v>78</v>
       </c>
       <c r="AG38" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="AH38" t="s" s="2">
         <v>76</v>
@@ -6370,10 +6375,10 @@
         <v>3</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="C39" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="D39" s="2"/>
       <c r="E39" t="s" s="2">
@@ -6396,7 +6401,7 @@
         <v>78</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="M39" t="s" s="2">
         <v>143</v>
@@ -6473,10 +6478,10 @@
         <v>3</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="C40" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="D40" s="2"/>
       <c r="E40" t="s" s="2">
@@ -6502,10 +6507,10 @@
         <v>128</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="O40" t="s" s="2">
         <v>174</v>
@@ -6578,14 +6583,14 @@
         <v>3</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="C41" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="D41" s="2"/>
       <c r="E41" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="F41" s="2"/>
       <c r="G41" t="s" s="2">
@@ -6607,10 +6612,10 @@
         <v>128</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="O41" t="s" s="2">
         <v>174</v>
@@ -6665,7 +6670,7 @@
         <v>78</v>
       </c>
       <c r="AG41" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="AH41" t="s" s="2">
         <v>76</v>
@@ -6685,10 +6690,10 @@
         <v>3</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="C42" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="D42" s="2"/>
       <c r="E42" t="s" s="2">
@@ -6714,13 +6719,13 @@
         <v>184</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="O42" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="P42" s="2"/>
       <c r="Q42" t="s" s="2">
@@ -6746,11 +6751,11 @@
         <v>78</v>
       </c>
       <c r="Y42" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="Z42" s="2"/>
       <c r="AA42" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="AB42" t="s" s="2">
         <v>78</v>
@@ -6768,7 +6773,7 @@
         <v>78</v>
       </c>
       <c r="AG42" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="AH42" t="s" s="2">
         <v>76</v>
@@ -6788,14 +6793,14 @@
         <v>3</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="C43" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="D43" s="2"/>
       <c r="E43" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="F43" s="2"/>
       <c r="G43" t="s" s="2">
@@ -6817,13 +6822,13 @@
         <v>184</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="O43" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="P43" s="2"/>
       <c r="Q43" t="s" s="2">
@@ -6852,10 +6857,10 @@
         <v>109</v>
       </c>
       <c r="Z43" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="AA43" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="AB43" t="s" s="2">
         <v>78</v>
@@ -6873,7 +6878,7 @@
         <v>78</v>
       </c>
       <c r="AG43" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="AH43" t="s" s="2">
         <v>85</v>
@@ -6893,14 +6898,14 @@
         <v>3</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="C44" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="D44" s="2"/>
       <c r="E44" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="F44" s="2"/>
       <c r="G44" t="s" s="2">
@@ -6919,16 +6924,16 @@
         <v>78</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="O44" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="P44" s="2"/>
       <c r="Q44" t="s" s="2">
@@ -6978,7 +6983,7 @@
         <v>78</v>
       </c>
       <c r="AG44" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="AH44" t="s" s="2">
         <v>76</v>
@@ -6998,10 +7003,10 @@
         <v>3</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="C45" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="D45" s="2"/>
       <c r="E45" t="s" s="2">
@@ -7027,10 +7032,10 @@
         <v>168</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="O45" s="2"/>
       <c r="P45" s="2"/>
@@ -7081,7 +7086,7 @@
         <v>78</v>
       </c>
       <c r="AG45" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="AH45" t="s" s="2">
         <v>76</v>
@@ -7101,10 +7106,10 @@
         <v>3</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="C46" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="D46" s="2"/>
       <c r="E46" t="s" s="2">
@@ -7130,13 +7135,13 @@
         <v>105</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="O46" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="P46" s="2"/>
       <c r="Q46" t="s" s="2">
@@ -7165,10 +7170,10 @@
         <v>188</v>
       </c>
       <c r="Z46" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="AA46" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="AB46" t="s" s="2">
         <v>78</v>
@@ -7186,7 +7191,7 @@
         <v>78</v>
       </c>
       <c r="AG46" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="AH46" t="s" s="2">
         <v>76</v>
@@ -7206,10 +7211,10 @@
         <v>3</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="C47" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="D47" s="2"/>
       <c r="E47" t="s" s="2">
@@ -7235,13 +7240,13 @@
         <v>184</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="O47" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="P47" s="2"/>
       <c r="Q47" t="s" s="2">
@@ -7267,13 +7272,13 @@
         <v>78</v>
       </c>
       <c r="Y47" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="Z47" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="AA47" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="AB47" t="s" s="2">
         <v>78</v>
@@ -7291,7 +7296,7 @@
         <v>78</v>
       </c>
       <c r="AG47" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="AH47" t="s" s="2">
         <v>76</v>
@@ -7311,10 +7316,10 @@
         <v>3</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="C48" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="D48" s="2"/>
       <c r="E48" t="s" s="2">
@@ -7337,16 +7342,16 @@
         <v>78</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="O48" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="P48" s="2"/>
       <c r="Q48" t="s" s="2">
@@ -7396,7 +7401,7 @@
         <v>78</v>
       </c>
       <c r="AG48" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="AH48" t="s" s="2">
         <v>76</v>
@@ -7413,17 +7418,17 @@
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="C49" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="D49" s="2"/>
       <c r="E49" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="F49" s="2"/>
       <c r="G49" t="s" s="2">
@@ -7445,10 +7450,10 @@
         <v>79</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="O49" s="2"/>
       <c r="P49" s="2"/>
@@ -7499,7 +7504,7 @@
         <v>78</v>
       </c>
       <c r="AG49" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="AH49" t="s" s="2">
         <v>76</v>
@@ -7511,18 +7516,18 @@
         <v>78</v>
       </c>
       <c r="AK49" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="C50" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="D50" s="2"/>
       <c r="E50" t="s" s="2">
@@ -7621,13 +7626,13 @@
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="C51" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="D51" s="2"/>
       <c r="E51" t="s" s="2">
@@ -7724,13 +7729,13 @@
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="C52" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="D52" s="2"/>
       <c r="E52" t="s" s="2">
@@ -7829,13 +7834,13 @@
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="C53" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="D53" s="2"/>
       <c r="E53" t="s" s="2">
@@ -7861,7 +7866,7 @@
         <v>105</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="N53" t="s" s="2">
         <v>107</v>
@@ -7934,13 +7939,13 @@
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="C54" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="D54" s="2"/>
       <c r="E54" t="s" s="2">
@@ -8039,13 +8044,13 @@
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="C55" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="D55" s="2"/>
       <c r="E55" t="s" s="2">
@@ -8144,13 +8149,13 @@
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="C56" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="D56" s="2"/>
       <c r="E56" t="s" s="2">
@@ -8245,16 +8250,16 @@
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B57" t="s" s="2">
+        <v>351</v>
+      </c>
+      <c r="C57" t="s" s="2">
         <v>350</v>
       </c>
-      <c r="C57" t="s" s="2">
-        <v>349</v>
-      </c>
       <c r="D57" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="E57" t="s" s="2">
         <v>78</v>
@@ -8276,13 +8281,13 @@
         <v>78</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="N57" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="O57" s="2"/>
       <c r="P57" s="2"/>
@@ -8350,13 +8355,13 @@
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="C58" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="D58" s="2"/>
       <c r="E58" t="s" s="2">
@@ -8453,13 +8458,13 @@
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="C59" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="D59" s="2"/>
       <c r="E59" t="s" s="2">
@@ -8556,13 +8561,13 @@
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="C60" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="D60" s="2"/>
       <c r="E60" t="s" s="2">
@@ -8602,7 +8607,7 @@
       </c>
       <c r="R60" s="2"/>
       <c r="S60" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="T60" t="s" s="2">
         <v>78</v>
@@ -8661,13 +8666,13 @@
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="C61" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="D61" s="2"/>
       <c r="E61" t="s" s="2">
@@ -8690,7 +8695,7 @@
         <v>78</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="M61" t="s" s="2">
         <v>161</v>
@@ -8764,16 +8769,16 @@
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="C62" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="D62" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="E62" t="s" s="2">
         <v>78</v>
@@ -8795,13 +8800,13 @@
         <v>78</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="N62" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="O62" s="2"/>
       <c r="P62" s="2"/>
@@ -8869,16 +8874,16 @@
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="C63" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="D63" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="E63" t="s" s="2">
         <v>78</v>
@@ -8900,16 +8905,16 @@
         <v>78</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="N63" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="O63" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="P63" s="2"/>
       <c r="Q63" t="s" s="2">
@@ -8976,16 +8981,16 @@
     </row>
     <row r="64">
       <c r="A64" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="C64" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="D64" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="E64" t="s" s="2">
         <v>78</v>
@@ -9007,13 +9012,13 @@
         <v>78</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="N64" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="O64" s="2"/>
       <c r="P64" s="2"/>
@@ -9081,16 +9086,16 @@
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="C65" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="D65" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="E65" t="s" s="2">
         <v>78</v>
@@ -9112,13 +9117,13 @@
         <v>78</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="N65" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="O65" s="2"/>
       <c r="P65" s="2"/>
@@ -9186,16 +9191,16 @@
     </row>
     <row r="66">
       <c r="A66" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="C66" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="D66" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="E66" t="s" s="2">
         <v>78</v>
@@ -9217,13 +9222,13 @@
         <v>78</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="N66" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="O66" s="2"/>
       <c r="P66" s="2"/>
@@ -9291,16 +9296,16 @@
     </row>
     <row r="67">
       <c r="A67" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="C67" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="D67" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="E67" t="s" s="2">
         <v>78</v>
@@ -9322,16 +9327,16 @@
         <v>78</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="N67" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="O67" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="P67" s="2"/>
       <c r="Q67" t="s" s="2">
@@ -9398,13 +9403,13 @@
     </row>
     <row r="68">
       <c r="A68" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="C68" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="D68" s="2"/>
       <c r="E68" t="s" s="2">
@@ -9505,13 +9510,13 @@
     </row>
     <row r="69">
       <c r="A69" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="C69" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="D69" s="2"/>
       <c r="E69" t="s" s="2">
@@ -9537,14 +9542,14 @@
         <v>178</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="N69" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="O69" s="2"/>
       <c r="P69" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="Q69" t="s" s="2">
         <v>78</v>
@@ -9593,7 +9598,7 @@
         <v>78</v>
       </c>
       <c r="AG69" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="AH69" t="s" s="2">
         <v>76</v>
@@ -9610,13 +9615,13 @@
     </row>
     <row r="70">
       <c r="A70" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="C70" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="D70" s="2"/>
       <c r="E70" t="s" s="2">
@@ -9639,70 +9644,70 @@
         <v>86</v>
       </c>
       <c r="L70" t="s" s="2">
+        <v>404</v>
+      </c>
+      <c r="M70" t="s" s="2">
+        <v>405</v>
+      </c>
+      <c r="N70" t="s" s="2">
+        <v>406</v>
+      </c>
+      <c r="O70" t="s" s="2">
+        <v>407</v>
+      </c>
+      <c r="P70" t="s" s="2">
+        <v>408</v>
+      </c>
+      <c r="Q70" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="R70" t="s" s="2">
+        <v>409</v>
+      </c>
+      <c r="S70" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T70" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U70" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V70" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W70" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X70" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y70" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z70" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA70" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB70" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC70" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD70" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE70" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF70" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AG70" t="s" s="2">
         <v>403</v>
-      </c>
-      <c r="M70" t="s" s="2">
-        <v>404</v>
-      </c>
-      <c r="N70" t="s" s="2">
-        <v>405</v>
-      </c>
-      <c r="O70" t="s" s="2">
-        <v>406</v>
-      </c>
-      <c r="P70" t="s" s="2">
-        <v>407</v>
-      </c>
-      <c r="Q70" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="R70" t="s" s="2">
-        <v>408</v>
-      </c>
-      <c r="S70" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="T70" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="U70" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="V70" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="W70" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="X70" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y70" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Z70" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AA70" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB70" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC70" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD70" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE70" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF70" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AG70" t="s" s="2">
-        <v>402</v>
       </c>
       <c r="AH70" t="s" s="2">
         <v>76</v>
@@ -9719,13 +9724,13 @@
     </row>
     <row r="71">
       <c r="A71" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="C71" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="D71" s="2"/>
       <c r="E71" t="s" s="2">
@@ -9748,19 +9753,19 @@
         <v>86</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="N71" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="O71" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="P71" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="Q71" t="s" s="2">
         <v>78</v>
@@ -9809,7 +9814,7 @@
         <v>78</v>
       </c>
       <c r="AG71" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="AH71" t="s" s="2">
         <v>76</v>
@@ -9821,18 +9826,18 @@
         <v>78</v>
       </c>
       <c r="AK71" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="C72" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="D72" s="2"/>
       <c r="E72" t="s" s="2">
@@ -9855,7 +9860,7 @@
         <v>78</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="M72" t="s" s="2">
         <v>143</v>
@@ -9929,13 +9934,13 @@
     </row>
     <row r="73">
       <c r="A73" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="C73" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="D73" s="2"/>
       <c r="E73" t="s" s="2">
@@ -9961,10 +9966,10 @@
         <v>128</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="N73" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="O73" t="s" s="2">
         <v>174</v>
@@ -10034,13 +10039,13 @@
     </row>
     <row r="74">
       <c r="A74" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="C74" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="D74" s="2"/>
       <c r="E74" t="s" s="2">
@@ -10066,16 +10071,16 @@
         <v>105</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="N74" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="O74" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="P74" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="Q74" t="s" s="2">
         <v>78</v>
@@ -10103,10 +10108,10 @@
         <v>188</v>
       </c>
       <c r="Z74" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="AA74" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="AB74" t="s" s="2">
         <v>78</v>
@@ -10124,7 +10129,7 @@
         <v>78</v>
       </c>
       <c r="AG74" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="AH74" t="s" s="2">
         <v>76</v>
@@ -10141,13 +10146,13 @@
     </row>
     <row r="75">
       <c r="A75" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="C75" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="D75" s="2"/>
       <c r="E75" t="s" s="2">
@@ -10170,19 +10175,19 @@
         <v>86</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="N75" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="O75" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="P75" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="Q75" t="s" s="2">
         <v>78</v>
@@ -10231,7 +10236,7 @@
         <v>78</v>
       </c>
       <c r="AG75" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="AH75" t="s" s="2">
         <v>76</v>
@@ -10248,17 +10253,17 @@
     </row>
     <row r="76">
       <c r="A76" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="C76" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="D76" s="2"/>
       <c r="E76" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="F76" s="2"/>
       <c r="G76" t="s" s="2">
@@ -10277,16 +10282,16 @@
         <v>86</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="N76" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="O76" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="P76" s="2"/>
       <c r="Q76" t="s" s="2">
@@ -10300,7 +10305,7 @@
         <v>78</v>
       </c>
       <c r="U76" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="V76" t="s" s="2">
         <v>78</v>
@@ -10336,7 +10341,7 @@
         <v>78</v>
       </c>
       <c r="AG76" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="AH76" t="s" s="2">
         <v>76</v>
@@ -10353,17 +10358,17 @@
     </row>
     <row r="77">
       <c r="A77" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="C77" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="D77" s="2"/>
       <c r="E77" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="F77" s="2"/>
       <c r="G77" t="s" s="2">
@@ -10382,16 +10387,16 @@
         <v>86</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="N77" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="O77" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="P77" s="2"/>
       <c r="Q77" t="s" s="2">
@@ -10441,7 +10446,7 @@
         <v>78</v>
       </c>
       <c r="AG77" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="AH77" t="s" s="2">
         <v>76</v>
@@ -10458,13 +10463,13 @@
     </row>
     <row r="78">
       <c r="A78" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="C78" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="D78" s="2"/>
       <c r="E78" t="s" s="2">
@@ -10487,13 +10492,13 @@
         <v>86</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="N78" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="O78" s="2"/>
       <c r="P78" s="2"/>
@@ -10544,7 +10549,7 @@
         <v>78</v>
       </c>
       <c r="AG78" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="AH78" t="s" s="2">
         <v>76</v>
@@ -10561,13 +10566,13 @@
     </row>
     <row r="79">
       <c r="A79" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="C79" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="D79" s="2"/>
       <c r="E79" t="s" s="2">
@@ -10590,13 +10595,13 @@
         <v>86</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="N79" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="O79" s="2"/>
       <c r="P79" s="2"/>
@@ -10647,7 +10652,7 @@
         <v>78</v>
       </c>
       <c r="AG79" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="AH79" t="s" s="2">
         <v>76</v>
@@ -10664,13 +10669,13 @@
     </row>
     <row r="80">
       <c r="A80" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="C80" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="D80" s="2"/>
       <c r="E80" t="s" s="2">
@@ -10693,17 +10698,17 @@
         <v>86</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="N80" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="O80" s="2"/>
       <c r="P80" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="Q80" t="s" s="2">
         <v>78</v>
@@ -10752,7 +10757,7 @@
         <v>78</v>
       </c>
       <c r="AG80" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="AH80" t="s" s="2">
         <v>76</v>
@@ -10769,13 +10774,13 @@
     </row>
     <row r="81">
       <c r="A81" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="C81" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="D81" s="2"/>
       <c r="E81" t="s" s="2">
@@ -10798,19 +10803,19 @@
         <v>86</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="N81" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="O81" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="P81" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="Q81" t="s" s="2">
         <v>78</v>
@@ -10859,7 +10864,7 @@
         <v>78</v>
       </c>
       <c r="AG81" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="AH81" t="s" s="2">
         <v>76</v>
@@ -10876,13 +10881,13 @@
     </row>
     <row r="82">
       <c r="A82" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="C82" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="D82" s="2"/>
       <c r="E82" t="s" s="2">
@@ -10908,16 +10913,16 @@
         <v>105</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="N82" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="O82" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="P82" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="Q82" t="s" s="2">
         <v>78</v>
@@ -10945,10 +10950,10 @@
         <v>188</v>
       </c>
       <c r="Z82" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="AA82" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="AB82" t="s" s="2">
         <v>78</v>
@@ -10966,7 +10971,7 @@
         <v>78</v>
       </c>
       <c r="AG82" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="AH82" t="s" s="2">
         <v>76</v>
@@ -10983,13 +10988,13 @@
     </row>
     <row r="83">
       <c r="A83" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="C83" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="D83" s="2"/>
       <c r="E83" t="s" s="2">
@@ -11012,19 +11017,19 @@
         <v>86</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="N83" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="O83" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="P83" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="Q83" t="s" s="2">
         <v>78</v>
@@ -11073,7 +11078,7 @@
         <v>78</v>
       </c>
       <c r="AG83" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="AH83" t="s" s="2">
         <v>76</v>
@@ -11090,13 +11095,13 @@
     </row>
     <row r="84">
       <c r="A84" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="C84" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="D84" s="2"/>
       <c r="E84" t="s" s="2">
@@ -11119,19 +11124,19 @@
         <v>86</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="N84" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="O84" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="P84" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="Q84" t="s" s="2">
         <v>78</v>
@@ -11180,7 +11185,7 @@
         <v>78</v>
       </c>
       <c r="AG84" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="AH84" t="s" s="2">
         <v>76</v>
@@ -11197,13 +11202,13 @@
     </row>
     <row r="85">
       <c r="A85" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="C85" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="D85" s="2"/>
       <c r="E85" t="s" s="2">
@@ -11226,19 +11231,19 @@
         <v>86</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="N85" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="O85" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="P85" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="Q85" t="s" s="2">
         <v>78</v>
@@ -11287,7 +11292,7 @@
         <v>78</v>
       </c>
       <c r="AG85" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="AH85" t="s" s="2">
         <v>76</v>
@@ -11304,13 +11309,13 @@
     </row>
     <row r="86">
       <c r="A86" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="C86" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="D86" s="2"/>
       <c r="E86" t="s" s="2">
@@ -11336,14 +11341,14 @@
         <v>184</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="N86" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="O86" s="2"/>
       <c r="P86" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="Q86" t="s" s="2">
         <v>78</v>
@@ -11368,13 +11373,13 @@
         <v>78</v>
       </c>
       <c r="Y86" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="Z86" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="AA86" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="AB86" t="s" s="2">
         <v>78</v>
@@ -11392,7 +11397,7 @@
         <v>78</v>
       </c>
       <c r="AG86" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="AH86" t="s" s="2">
         <v>76</v>
@@ -11409,13 +11414,13 @@
     </row>
     <row r="87">
       <c r="A87" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="C87" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="D87" s="2"/>
       <c r="E87" t="s" s="2">
@@ -11438,19 +11443,19 @@
         <v>78</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="N87" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="O87" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="P87" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="Q87" t="s" s="2">
         <v>78</v>
@@ -11499,7 +11504,7 @@
         <v>78</v>
       </c>
       <c r="AG87" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="AH87" t="s" s="2">
         <v>76</v>
@@ -11516,13 +11521,13 @@
     </row>
     <row r="88">
       <c r="A88" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="C88" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="D88" s="2"/>
       <c r="E88" t="s" s="2">
@@ -11545,19 +11550,19 @@
         <v>78</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="N88" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="O88" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="P88" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="Q88" t="s" s="2">
         <v>78</v>
@@ -11606,7 +11611,7 @@
         <v>78</v>
       </c>
       <c r="AG88" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="AH88" t="s" s="2">
         <v>76</v>
@@ -11623,13 +11628,13 @@
     </row>
     <row r="89">
       <c r="A89" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="C89" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="D89" s="2"/>
       <c r="E89" t="s" s="2">
@@ -11652,19 +11657,19 @@
         <v>78</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="N89" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="O89" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="P89" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="Q89" t="s" s="2">
         <v>78</v>
@@ -11713,7 +11718,7 @@
         <v>78</v>
       </c>
       <c r="AG89" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="AH89" t="s" s="2">
         <v>76</v>
@@ -11725,18 +11730,18 @@
         <v>78</v>
       </c>
       <c r="AK89" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="C90" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="D90" s="2"/>
       <c r="E90" t="s" s="2">
@@ -11759,7 +11764,7 @@
         <v>78</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="M90" t="s" s="2">
         <v>143</v>
@@ -11833,13 +11838,13 @@
     </row>
     <row r="91">
       <c r="A91" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="C91" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="D91" s="2"/>
       <c r="E91" t="s" s="2">
@@ -11865,10 +11870,10 @@
         <v>128</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="N91" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="O91" t="s" s="2">
         <v>174</v>
@@ -11938,17 +11943,17 @@
     </row>
     <row r="92">
       <c r="A92" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="C92" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="D92" s="2"/>
       <c r="E92" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="F92" s="2"/>
       <c r="G92" t="s" s="2">
@@ -11970,10 +11975,10 @@
         <v>128</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="N92" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="O92" t="s" s="2">
         <v>174</v>
@@ -12028,7 +12033,7 @@
         <v>78</v>
       </c>
       <c r="AG92" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="AH92" t="s" s="2">
         <v>76</v>
@@ -12045,13 +12050,13 @@
     </row>
     <row r="93">
       <c r="A93" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="C93" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="D93" s="2"/>
       <c r="E93" t="s" s="2">
@@ -12077,14 +12082,14 @@
         <v>184</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="N93" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="O93" s="2"/>
       <c r="P93" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="Q93" t="s" s="2">
         <v>78</v>
@@ -12109,13 +12114,13 @@
         <v>78</v>
       </c>
       <c r="Y93" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="Z93" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="AA93" t="s" s="2">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="AB93" t="s" s="2">
         <v>78</v>
@@ -12133,7 +12138,7 @@
         <v>78</v>
       </c>
       <c r="AG93" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="AH93" t="s" s="2">
         <v>76</v>
@@ -12150,13 +12155,13 @@
     </row>
     <row r="94">
       <c r="A94" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="C94" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="D94" s="2"/>
       <c r="E94" t="s" s="2">
@@ -12179,17 +12184,17 @@
         <v>78</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="N94" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="O94" s="2"/>
       <c r="P94" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="Q94" t="s" s="2">
         <v>78</v>
@@ -12238,7 +12243,7 @@
         <v>78</v>
       </c>
       <c r="AG94" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="AH94" t="s" s="2">
         <v>76</v>
@@ -12255,13 +12260,13 @@
     </row>
     <row r="95">
       <c r="A95" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="C95" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="D95" s="2"/>
       <c r="E95" t="s" s="2">
@@ -12284,19 +12289,19 @@
         <v>78</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="N95" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="O95" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="P95" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="Q95" t="s" s="2">
         <v>78</v>
@@ -12345,7 +12350,7 @@
         <v>78</v>
       </c>
       <c r="AG95" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="AH95" t="s" s="2">
         <v>76</v>
@@ -12362,13 +12367,13 @@
     </row>
     <row r="96">
       <c r="A96" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="C96" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="D96" s="2"/>
       <c r="E96" t="s" s="2">
@@ -12391,17 +12396,17 @@
         <v>78</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="N96" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="O96" s="2"/>
       <c r="P96" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="Q96" t="s" s="2">
         <v>78</v>
@@ -12450,7 +12455,7 @@
         <v>78</v>
       </c>
       <c r="AG96" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="AH96" t="s" s="2">
         <v>76</v>
@@ -12467,13 +12472,13 @@
     </row>
     <row r="97">
       <c r="A97" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="C97" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="D97" s="2"/>
       <c r="E97" t="s" s="2">
@@ -12499,14 +12504,14 @@
         <v>105</v>
       </c>
       <c r="M97" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="N97" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="O97" s="2"/>
       <c r="P97" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="Q97" t="s" s="2">
         <v>78</v>
@@ -12534,10 +12539,10 @@
         <v>188</v>
       </c>
       <c r="Z97" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="AA97" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="AB97" t="s" s="2">
         <v>78</v>
@@ -12555,7 +12560,7 @@
         <v>78</v>
       </c>
       <c r="AG97" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="AH97" t="s" s="2">
         <v>76</v>
@@ -12572,13 +12577,13 @@
     </row>
     <row r="98">
       <c r="A98" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="C98" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="D98" s="2"/>
       <c r="E98" t="s" s="2">
@@ -12601,17 +12606,17 @@
         <v>78</v>
       </c>
       <c r="L98" t="s" s="2">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="M98" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="N98" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="O98" s="2"/>
       <c r="P98" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="Q98" t="s" s="2">
         <v>78</v>
@@ -12660,7 +12665,7 @@
         <v>78</v>
       </c>
       <c r="AG98" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="AH98" t="s" s="2">
         <v>76</v>
@@ -12669,7 +12674,7 @@
         <v>85</v>
       </c>
       <c r="AJ98" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="AK98" t="s" s="2">
         <v>97</v>
@@ -12677,13 +12682,13 @@
     </row>
     <row r="99">
       <c r="A99" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="C99" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="D99" s="2"/>
       <c r="E99" t="s" s="2">
@@ -12706,13 +12711,13 @@
         <v>78</v>
       </c>
       <c r="L99" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="M99" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="N99" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="O99" s="2"/>
       <c r="P99" s="2"/>
@@ -12763,7 +12768,7 @@
         <v>78</v>
       </c>
       <c r="AG99" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="AH99" t="s" s="2">
         <v>76</v>
@@ -12780,13 +12785,13 @@
     </row>
     <row r="100">
       <c r="A100" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="C100" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="D100" s="2"/>
       <c r="E100" t="s" s="2">
@@ -12809,19 +12814,19 @@
         <v>78</v>
       </c>
       <c r="L100" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="M100" t="s" s="2">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="N100" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="O100" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="P100" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="Q100" t="s" s="2">
         <v>78</v>
@@ -12870,7 +12875,7 @@
         <v>78</v>
       </c>
       <c r="AG100" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="AH100" t="s" s="2">
         <v>76</v>
@@ -12887,13 +12892,13 @@
     </row>
     <row r="101">
       <c r="A101" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="C101" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="D101" s="2"/>
       <c r="E101" t="s" s="2">
@@ -12916,7 +12921,7 @@
         <v>78</v>
       </c>
       <c r="L101" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="M101" t="s" s="2">
         <v>143</v>
@@ -12990,13 +12995,13 @@
     </row>
     <row r="102">
       <c r="A102" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="C102" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="D102" s="2"/>
       <c r="E102" t="s" s="2">
@@ -13022,10 +13027,10 @@
         <v>128</v>
       </c>
       <c r="M102" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="N102" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="O102" t="s" s="2">
         <v>174</v>
@@ -13095,17 +13100,17 @@
     </row>
     <row r="103">
       <c r="A103" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="C103" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="D103" s="2"/>
       <c r="E103" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="F103" s="2"/>
       <c r="G103" t="s" s="2">
@@ -13127,10 +13132,10 @@
         <v>128</v>
       </c>
       <c r="M103" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="N103" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="O103" t="s" s="2">
         <v>174</v>
@@ -13185,7 +13190,7 @@
         <v>78</v>
       </c>
       <c r="AG103" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="AH103" t="s" s="2">
         <v>76</v>
@@ -13202,13 +13207,13 @@
     </row>
     <row r="104">
       <c r="A104" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="C104" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="D104" s="2"/>
       <c r="E104" t="s" s="2">
@@ -13234,16 +13239,16 @@
         <v>184</v>
       </c>
       <c r="M104" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="N104" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="O104" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="P104" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="Q104" t="s" s="2">
         <v>78</v>
@@ -13292,7 +13297,7 @@
         <v>78</v>
       </c>
       <c r="AG104" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="AH104" t="s" s="2">
         <v>85</v>
@@ -13309,13 +13314,13 @@
     </row>
     <row r="105">
       <c r="A105" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="C105" t="s" s="2">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="D105" s="2"/>
       <c r="E105" t="s" s="2">
@@ -13338,19 +13343,19 @@
         <v>78</v>
       </c>
       <c r="L105" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="M105" t="s" s="2">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="N105" t="s" s="2">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="O105" t="s" s="2">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="P105" t="s" s="2">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="Q105" t="s" s="2">
         <v>78</v>
@@ -13399,7 +13404,7 @@
         <v>78</v>
       </c>
       <c r="AG105" t="s" s="2">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="AH105" t="s" s="2">
         <v>76</v>
@@ -13416,17 +13421,17 @@
     </row>
     <row r="106">
       <c r="A106" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="C106" t="s" s="2">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="D106" s="2"/>
       <c r="E106" t="s" s="2">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="F106" s="2"/>
       <c r="G106" t="s" s="2">
@@ -13445,16 +13450,16 @@
         <v>78</v>
       </c>
       <c r="L106" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="M106" t="s" s="2">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="N106" t="s" s="2">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="O106" t="s" s="2">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="P106" s="2"/>
       <c r="Q106" t="s" s="2">
@@ -13504,7 +13509,7 @@
         <v>78</v>
       </c>
       <c r="AG106" t="s" s="2">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="AH106" t="s" s="2">
         <v>76</v>
@@ -13521,13 +13526,13 @@
     </row>
     <row r="107">
       <c r="A107" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="C107" t="s" s="2">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="D107" s="2"/>
       <c r="E107" t="s" s="2">
@@ -13550,19 +13555,19 @@
         <v>86</v>
       </c>
       <c r="L107" t="s" s="2">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="M107" t="s" s="2">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="N107" t="s" s="2">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="O107" t="s" s="2">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="P107" t="s" s="2">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="Q107" t="s" s="2">
         <v>78</v>
@@ -13611,7 +13616,7 @@
         <v>78</v>
       </c>
       <c r="AG107" t="s" s="2">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="AH107" t="s" s="2">
         <v>76</v>
@@ -13628,13 +13633,13 @@
     </row>
     <row r="108">
       <c r="A108" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="C108" t="s" s="2">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="D108" s="2"/>
       <c r="E108" t="s" s="2">
@@ -13657,19 +13662,19 @@
         <v>86</v>
       </c>
       <c r="L108" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="M108" t="s" s="2">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="N108" t="s" s="2">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="O108" t="s" s="2">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="P108" t="s" s="2">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="Q108" t="s" s="2">
         <v>78</v>
@@ -13718,7 +13723,7 @@
         <v>78</v>
       </c>
       <c r="AG108" t="s" s="2">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="AH108" t="s" s="2">
         <v>76</v>
@@ -13735,13 +13740,13 @@
     </row>
     <row r="109">
       <c r="A109" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="C109" t="s" s="2">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="D109" s="2"/>
       <c r="E109" t="s" s="2">
@@ -13764,7 +13769,7 @@
         <v>78</v>
       </c>
       <c r="L109" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="M109" t="s" s="2">
         <v>143</v>
@@ -13838,13 +13843,13 @@
     </row>
     <row r="110">
       <c r="A110" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="C110" t="s" s="2">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="D110" s="2"/>
       <c r="E110" t="s" s="2">
@@ -13870,10 +13875,10 @@
         <v>128</v>
       </c>
       <c r="M110" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="N110" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="O110" t="s" s="2">
         <v>174</v>
@@ -13943,17 +13948,17 @@
     </row>
     <row r="111">
       <c r="A111" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="C111" t="s" s="2">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="D111" s="2"/>
       <c r="E111" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="F111" s="2"/>
       <c r="G111" t="s" s="2">
@@ -13975,10 +13980,10 @@
         <v>128</v>
       </c>
       <c r="M111" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="N111" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="O111" t="s" s="2">
         <v>174</v>
@@ -14033,7 +14038,7 @@
         <v>78</v>
       </c>
       <c r="AG111" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="AH111" t="s" s="2">
         <v>76</v>
@@ -14050,13 +14055,13 @@
     </row>
     <row r="112">
       <c r="A112" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="C112" t="s" s="2">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="D112" s="2"/>
       <c r="E112" t="s" s="2">
@@ -14079,16 +14084,16 @@
         <v>86</v>
       </c>
       <c r="L112" t="s" s="2">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="M112" t="s" s="2">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="N112" t="s" s="2">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="O112" t="s" s="2">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="P112" s="2"/>
       <c r="Q112" t="s" s="2">
@@ -14138,7 +14143,7 @@
         <v>78</v>
       </c>
       <c r="AG112" t="s" s="2">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="AH112" t="s" s="2">
         <v>85</v>
@@ -14155,13 +14160,13 @@
     </row>
     <row r="113">
       <c r="A113" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="C113" t="s" s="2">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="D113" s="2"/>
       <c r="E113" t="s" s="2">
@@ -14187,10 +14192,10 @@
         <v>105</v>
       </c>
       <c r="M113" t="s" s="2">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="N113" t="s" s="2">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="O113" s="2"/>
       <c r="P113" s="2"/>
@@ -14220,10 +14225,10 @@
         <v>188</v>
       </c>
       <c r="Z113" t="s" s="2">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="AA113" t="s" s="2">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="AB113" t="s" s="2">
         <v>78</v>
@@ -14241,7 +14246,7 @@
         <v>78</v>
       </c>
       <c r="AG113" t="s" s="2">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="AH113" t="s" s="2">
         <v>85</v>

--- a/currentbuild/all-profiles.xlsx
+++ b/currentbuild/all-profiles.xlsx
@@ -36,7 +36,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.1.0</t>
+    <t>0.1.1</t>
   </si>
   <si>
     <t>Name</t>
@@ -69,13 +69,13 @@
     <t>Publisher</t>
   </si>
   <si>
-    <t>HL7 Norge</t>
+    <t>Helsedirektoratet</t>
   </si>
   <si>
     <t>Contact</t>
   </si>
   <si>
-    <t>HL7 Norge (https://www.hl7.no)</t>
+    <t>Helsedirektoratet (https://www.helsedirektoratet.no)</t>
   </si>
   <si>
     <t>Jurisdiction</t>
@@ -5264,10 +5264,10 @@
       <c r="N28" t="s" s="2">
         <v>242</v>
       </c>
-      <c r="O28" t="s" s="2">
+      <c r="O28" s="2"/>
+      <c r="P28" t="s" s="2">
         <v>243</v>
       </c>
-      <c r="P28" s="2"/>
       <c r="Q28" t="s" s="2">
         <v>78</v>
       </c>

--- a/currentbuild/all-profiles.xlsx
+++ b/currentbuild/all-profiles.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3841" uniqueCount="595">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3840" uniqueCount="594">
   <si>
     <t>Property</t>
   </si>
@@ -719,10 +719,7 @@
 The 'substanceExposureRisk' extension is available as a structured and more flexible alternative to the 'code' element for making positive or negative allergy or intolerance statements.  This extension provides the capability to make "no known allergy" (or "no risk of adverse reaction") statements regarding any coded substance/product (including cases when a pre-coordinated "no allergy to x" concept for that substance/product does not exist).  If the 'substanceExposureRisk' extension is present, the AllergyIntolerance.code element SHALL be omitted.</t>
   </si>
   <si>
-    <t>Type of the substance/product, allergy or intolerance condition or a code for absent/unknown allergy.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/uv/ips/ValueSet/allergies-intolerances-uv-ips</t>
+    <t>http://hl7.no/fhir/ig/demo-at/ValueSet/annen-allergi-som-kritisk-informasjon-7514</t>
   </si>
   <si>
     <t>AllergyIntolerance.patient</t>
@@ -2202,7 +2199,7 @@
         <v>2</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>332</v>
+        <v>331</v>
       </c>
     </row>
     <row r="24">
@@ -2210,7 +2207,7 @@
         <v>4</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>333</v>
+        <v>332</v>
       </c>
     </row>
     <row r="25">
@@ -2226,7 +2223,7 @@
         <v>8</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>334</v>
+        <v>333</v>
       </c>
     </row>
     <row r="27">
@@ -2234,7 +2231,7 @@
         <v>10</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>335</v>
+        <v>334</v>
       </c>
     </row>
     <row r="28">
@@ -2288,7 +2285,7 @@
         <v>23</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>336</v>
+        <v>335</v>
       </c>
     </row>
     <row r="35">
@@ -2324,7 +2321,7 @@
         <v>31</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>337</v>
+        <v>336</v>
       </c>
     </row>
     <row r="40">
@@ -2332,7 +2329,7 @@
         <v>33</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>338</v>
+        <v>337</v>
       </c>
     </row>
     <row r="41">
@@ -2387,7 +2384,7 @@
     <col min="24" max="24" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="16.16796875" customWidth="true" bestFit="true"/>
     <col min="26" max="26" width="106.67578125" customWidth="true" bestFit="true"/>
-    <col min="27" max="27" width="50.62109375" customWidth="true" bestFit="true"/>
+    <col min="27" max="27" width="64.96484375" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="19.4765625" customWidth="true" bestFit="true"/>
     <col min="30" max="30" width="36.0390625" customWidth="true" bestFit="true"/>
@@ -4776,11 +4773,9 @@
       <c r="Y23" t="s" s="2">
         <v>109</v>
       </c>
-      <c r="Z23" t="s" s="2">
+      <c r="Z23" s="2"/>
+      <c r="AA23" t="s" s="2">
         <v>223</v>
-      </c>
-      <c r="AA23" t="s" s="2">
-        <v>224</v>
       </c>
       <c r="AB23" t="s" s="2">
         <v>78</v>
@@ -4818,14 +4813,14 @@
         <v>3</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="C24" t="s" s="2">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="D24" s="2"/>
       <c r="E24" t="s" s="2">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="F24" s="2"/>
       <c r="G24" t="s" s="2">
@@ -4844,13 +4839,13 @@
         <v>86</v>
       </c>
       <c r="L24" t="s" s="2">
+        <v>226</v>
+      </c>
+      <c r="M24" t="s" s="2">
         <v>227</v>
       </c>
-      <c r="M24" t="s" s="2">
+      <c r="N24" t="s" s="2">
         <v>228</v>
-      </c>
-      <c r="N24" t="s" s="2">
-        <v>229</v>
       </c>
       <c r="O24" s="2"/>
       <c r="P24" s="2"/>
@@ -4901,7 +4896,7 @@
         <v>78</v>
       </c>
       <c r="AG24" t="s" s="2">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="AH24" t="s" s="2">
         <v>85</v>
@@ -4921,10 +4916,10 @@
         <v>3</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="C25" t="s" s="2">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="D25" s="2"/>
       <c r="E25" t="s" s="2">
@@ -4947,13 +4942,13 @@
         <v>78</v>
       </c>
       <c r="L25" t="s" s="2">
+        <v>230</v>
+      </c>
+      <c r="M25" t="s" s="2">
         <v>231</v>
       </c>
-      <c r="M25" t="s" s="2">
+      <c r="N25" t="s" s="2">
         <v>232</v>
-      </c>
-      <c r="N25" t="s" s="2">
-        <v>233</v>
       </c>
       <c r="O25" s="2"/>
       <c r="P25" s="2"/>
@@ -5004,7 +4999,7 @@
         <v>78</v>
       </c>
       <c r="AG25" t="s" s="2">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="AH25" t="s" s="2">
         <v>76</v>
@@ -5024,10 +5019,10 @@
         <v>3</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="C26" t="s" s="2">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="D26" s="2"/>
       <c r="E26" t="s" s="2">
@@ -5053,10 +5048,10 @@
         <v>160</v>
       </c>
       <c r="M26" t="s" s="2">
+        <v>234</v>
+      </c>
+      <c r="N26" t="s" s="2">
         <v>235</v>
-      </c>
-      <c r="N26" t="s" s="2">
-        <v>236</v>
       </c>
       <c r="O26" s="2"/>
       <c r="P26" s="2"/>
@@ -5105,7 +5100,7 @@
         <v>132</v>
       </c>
       <c r="AG26" t="s" s="2">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="AH26" t="s" s="2">
         <v>76</v>
@@ -5125,13 +5120,13 @@
         <v>3</v>
       </c>
       <c r="B27" t="s" s="2">
+        <v>236</v>
+      </c>
+      <c r="C27" t="s" s="2">
+        <v>233</v>
+      </c>
+      <c r="D27" t="s" s="2">
         <v>237</v>
-      </c>
-      <c r="C27" t="s" s="2">
-        <v>234</v>
-      </c>
-      <c r="D27" t="s" s="2">
-        <v>238</v>
       </c>
       <c r="E27" t="s" s="2">
         <v>78</v>
@@ -5156,10 +5151,10 @@
         <v>168</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="N27" t="s" s="2">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="O27" s="2"/>
       <c r="P27" s="2"/>
@@ -5210,7 +5205,7 @@
         <v>78</v>
       </c>
       <c r="AG27" t="s" s="2">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="AH27" t="s" s="2">
         <v>76</v>
@@ -5230,10 +5225,10 @@
         <v>3</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="C28" t="s" s="2">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="D28" s="2"/>
       <c r="E28" t="s" s="2">
@@ -5259,14 +5254,14 @@
         <v>168</v>
       </c>
       <c r="M28" t="s" s="2">
+        <v>240</v>
+      </c>
+      <c r="N28" t="s" s="2">
         <v>241</v>
-      </c>
-      <c r="N28" t="s" s="2">
-        <v>242</v>
       </c>
       <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="Q28" t="s" s="2">
         <v>78</v>
@@ -5315,7 +5310,7 @@
         <v>78</v>
       </c>
       <c r="AG28" t="s" s="2">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="AH28" t="s" s="2">
         <v>76</v>
@@ -5335,14 +5330,14 @@
         <v>3</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="C29" t="s" s="2">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="D29" s="2"/>
       <c r="E29" t="s" s="2">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="F29" s="2"/>
       <c r="G29" t="s" s="2">
@@ -5361,13 +5356,13 @@
         <v>78</v>
       </c>
       <c r="L29" t="s" s="2">
+        <v>245</v>
+      </c>
+      <c r="M29" t="s" s="2">
         <v>246</v>
       </c>
-      <c r="M29" t="s" s="2">
+      <c r="N29" t="s" s="2">
         <v>247</v>
-      </c>
-      <c r="N29" t="s" s="2">
-        <v>248</v>
       </c>
       <c r="O29" s="2"/>
       <c r="P29" s="2"/>
@@ -5418,7 +5413,7 @@
         <v>78</v>
       </c>
       <c r="AG29" t="s" s="2">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="AH29" t="s" s="2">
         <v>76</v>
@@ -5438,14 +5433,14 @@
         <v>3</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="C30" t="s" s="2">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="D30" s="2"/>
       <c r="E30" t="s" s="2">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="F30" s="2"/>
       <c r="G30" t="s" s="2">
@@ -5464,16 +5459,16 @@
         <v>86</v>
       </c>
       <c r="L30" t="s" s="2">
+        <v>250</v>
+      </c>
+      <c r="M30" t="s" s="2">
         <v>251</v>
       </c>
-      <c r="M30" t="s" s="2">
+      <c r="N30" t="s" s="2">
         <v>252</v>
       </c>
-      <c r="N30" t="s" s="2">
+      <c r="O30" t="s" s="2">
         <v>253</v>
-      </c>
-      <c r="O30" t="s" s="2">
-        <v>254</v>
       </c>
       <c r="P30" s="2"/>
       <c r="Q30" t="s" s="2">
@@ -5523,7 +5518,7 @@
         <v>78</v>
       </c>
       <c r="AG30" t="s" s="2">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="AH30" t="s" s="2">
         <v>76</v>
@@ -5543,10 +5538,10 @@
         <v>3</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="C31" t="s" s="2">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="D31" s="2"/>
       <c r="E31" t="s" s="2">
@@ -5572,13 +5567,13 @@
         <v>168</v>
       </c>
       <c r="M31" t="s" s="2">
+        <v>255</v>
+      </c>
+      <c r="N31" t="s" s="2">
         <v>256</v>
       </c>
-      <c r="N31" t="s" s="2">
+      <c r="O31" t="s" s="2">
         <v>257</v>
-      </c>
-      <c r="O31" t="s" s="2">
-        <v>258</v>
       </c>
       <c r="P31" s="2"/>
       <c r="Q31" t="s" s="2">
@@ -5628,7 +5623,7 @@
         <v>78</v>
       </c>
       <c r="AG31" t="s" s="2">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="AH31" t="s" s="2">
         <v>76</v>
@@ -5648,10 +5643,10 @@
         <v>3</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="C32" t="s" s="2">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="D32" s="2"/>
       <c r="E32" t="s" s="2">
@@ -5674,16 +5669,16 @@
         <v>78</v>
       </c>
       <c r="L32" t="s" s="2">
+        <v>259</v>
+      </c>
+      <c r="M32" t="s" s="2">
         <v>260</v>
       </c>
-      <c r="M32" t="s" s="2">
+      <c r="N32" t="s" s="2">
         <v>261</v>
       </c>
-      <c r="N32" t="s" s="2">
+      <c r="O32" t="s" s="2">
         <v>262</v>
-      </c>
-      <c r="O32" t="s" s="2">
-        <v>263</v>
       </c>
       <c r="P32" s="2"/>
       <c r="Q32" t="s" s="2">
@@ -5733,7 +5728,7 @@
         <v>78</v>
       </c>
       <c r="AG32" t="s" s="2">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="AH32" t="s" s="2">
         <v>76</v>
@@ -5753,10 +5748,10 @@
         <v>3</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="C33" t="s" s="2">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="D33" s="2"/>
       <c r="E33" t="s" s="2">
@@ -5779,7 +5774,7 @@
         <v>78</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="M33" t="s" s="2">
         <v>143</v>
@@ -5856,10 +5851,10 @@
         <v>3</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="C34" t="s" s="2">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="D34" s="2"/>
       <c r="E34" t="s" s="2">
@@ -5885,10 +5880,10 @@
         <v>128</v>
       </c>
       <c r="M34" t="s" s="2">
+        <v>266</v>
+      </c>
+      <c r="N34" t="s" s="2">
         <v>267</v>
-      </c>
-      <c r="N34" t="s" s="2">
-        <v>268</v>
       </c>
       <c r="O34" t="s" s="2">
         <v>174</v>
@@ -5961,10 +5956,10 @@
         <v>3</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="C35" t="s" s="2">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="D35" s="2"/>
       <c r="E35" t="s" s="2">
@@ -5987,16 +5982,16 @@
         <v>86</v>
       </c>
       <c r="L35" t="s" s="2">
+        <v>269</v>
+      </c>
+      <c r="M35" t="s" s="2">
         <v>270</v>
       </c>
-      <c r="M35" t="s" s="2">
+      <c r="N35" t="s" s="2">
         <v>271</v>
       </c>
-      <c r="N35" t="s" s="2">
+      <c r="O35" t="s" s="2">
         <v>272</v>
-      </c>
-      <c r="O35" t="s" s="2">
-        <v>273</v>
       </c>
       <c r="P35" s="2"/>
       <c r="Q35" t="s" s="2">
@@ -6046,7 +6041,7 @@
         <v>78</v>
       </c>
       <c r="AG35" t="s" s="2">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="AH35" t="s" s="2">
         <v>76</v>
@@ -6066,10 +6061,10 @@
         <v>3</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="C36" t="s" s="2">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="D36" s="2"/>
       <c r="E36" t="s" s="2">
@@ -6095,10 +6090,10 @@
         <v>168</v>
       </c>
       <c r="M36" t="s" s="2">
+        <v>275</v>
+      </c>
+      <c r="N36" t="s" s="2">
         <v>276</v>
-      </c>
-      <c r="N36" t="s" s="2">
-        <v>277</v>
       </c>
       <c r="O36" s="2"/>
       <c r="P36" s="2"/>
@@ -6149,7 +6144,7 @@
         <v>78</v>
       </c>
       <c r="AG36" t="s" s="2">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="AH36" t="s" s="2">
         <v>76</v>
@@ -6169,10 +6164,10 @@
         <v>3</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="C37" t="s" s="2">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="D37" s="2"/>
       <c r="E37" t="s" s="2">
@@ -6195,13 +6190,13 @@
         <v>86</v>
       </c>
       <c r="L37" t="s" s="2">
+        <v>279</v>
+      </c>
+      <c r="M37" t="s" s="2">
         <v>280</v>
       </c>
-      <c r="M37" t="s" s="2">
+      <c r="N37" t="s" s="2">
         <v>281</v>
-      </c>
-      <c r="N37" t="s" s="2">
-        <v>282</v>
       </c>
       <c r="O37" s="2"/>
       <c r="P37" s="2"/>
@@ -6252,7 +6247,7 @@
         <v>78</v>
       </c>
       <c r="AG37" t="s" s="2">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="AH37" t="s" s="2">
         <v>85</v>
@@ -6272,10 +6267,10 @@
         <v>3</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="C38" t="s" s="2">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="D38" s="2"/>
       <c r="E38" t="s" s="2">
@@ -6298,13 +6293,13 @@
         <v>78</v>
       </c>
       <c r="L38" t="s" s="2">
+        <v>284</v>
+      </c>
+      <c r="M38" t="s" s="2">
         <v>285</v>
       </c>
-      <c r="M38" t="s" s="2">
+      <c r="N38" t="s" s="2">
         <v>286</v>
-      </c>
-      <c r="N38" t="s" s="2">
-        <v>287</v>
       </c>
       <c r="O38" s="2"/>
       <c r="P38" s="2"/>
@@ -6355,7 +6350,7 @@
         <v>78</v>
       </c>
       <c r="AG38" t="s" s="2">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="AH38" t="s" s="2">
         <v>76</v>
@@ -6375,10 +6370,10 @@
         <v>3</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="C39" t="s" s="2">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="D39" s="2"/>
       <c r="E39" t="s" s="2">
@@ -6401,7 +6396,7 @@
         <v>78</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="M39" t="s" s="2">
         <v>143</v>
@@ -6478,10 +6473,10 @@
         <v>3</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="C40" t="s" s="2">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="D40" s="2"/>
       <c r="E40" t="s" s="2">
@@ -6507,10 +6502,10 @@
         <v>128</v>
       </c>
       <c r="M40" t="s" s="2">
+        <v>266</v>
+      </c>
+      <c r="N40" t="s" s="2">
         <v>267</v>
-      </c>
-      <c r="N40" t="s" s="2">
-        <v>268</v>
       </c>
       <c r="O40" t="s" s="2">
         <v>174</v>
@@ -6583,14 +6578,14 @@
         <v>3</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="C41" t="s" s="2">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="D41" s="2"/>
       <c r="E41" t="s" s="2">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="F41" s="2"/>
       <c r="G41" t="s" s="2">
@@ -6612,10 +6607,10 @@
         <v>128</v>
       </c>
       <c r="M41" t="s" s="2">
+        <v>291</v>
+      </c>
+      <c r="N41" t="s" s="2">
         <v>292</v>
-      </c>
-      <c r="N41" t="s" s="2">
-        <v>293</v>
       </c>
       <c r="O41" t="s" s="2">
         <v>174</v>
@@ -6670,7 +6665,7 @@
         <v>78</v>
       </c>
       <c r="AG41" t="s" s="2">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="AH41" t="s" s="2">
         <v>76</v>
@@ -6690,10 +6685,10 @@
         <v>3</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="C42" t="s" s="2">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="D42" s="2"/>
       <c r="E42" t="s" s="2">
@@ -6719,13 +6714,13 @@
         <v>184</v>
       </c>
       <c r="M42" t="s" s="2">
+        <v>295</v>
+      </c>
+      <c r="N42" t="s" s="2">
         <v>296</v>
       </c>
-      <c r="N42" t="s" s="2">
+      <c r="O42" t="s" s="2">
         <v>297</v>
-      </c>
-      <c r="O42" t="s" s="2">
-        <v>298</v>
       </c>
       <c r="P42" s="2"/>
       <c r="Q42" t="s" s="2">
@@ -6751,11 +6746,11 @@
         <v>78</v>
       </c>
       <c r="Y42" t="s" s="2">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="Z42" s="2"/>
       <c r="AA42" t="s" s="2">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="AB42" t="s" s="2">
         <v>78</v>
@@ -6773,7 +6768,7 @@
         <v>78</v>
       </c>
       <c r="AG42" t="s" s="2">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="AH42" t="s" s="2">
         <v>76</v>
@@ -6793,14 +6788,14 @@
         <v>3</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="C43" t="s" s="2">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="D43" s="2"/>
       <c r="E43" t="s" s="2">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="F43" s="2"/>
       <c r="G43" t="s" s="2">
@@ -6822,13 +6817,13 @@
         <v>184</v>
       </c>
       <c r="M43" t="s" s="2">
+        <v>302</v>
+      </c>
+      <c r="N43" t="s" s="2">
         <v>303</v>
       </c>
-      <c r="N43" t="s" s="2">
+      <c r="O43" t="s" s="2">
         <v>304</v>
-      </c>
-      <c r="O43" t="s" s="2">
-        <v>305</v>
       </c>
       <c r="P43" s="2"/>
       <c r="Q43" t="s" s="2">
@@ -6857,11 +6852,11 @@
         <v>109</v>
       </c>
       <c r="Z43" t="s" s="2">
+        <v>305</v>
+      </c>
+      <c r="AA43" t="s" s="2">
         <v>306</v>
       </c>
-      <c r="AA43" t="s" s="2">
-        <v>307</v>
-      </c>
       <c r="AB43" t="s" s="2">
         <v>78</v>
       </c>
@@ -6878,7 +6873,7 @@
         <v>78</v>
       </c>
       <c r="AG43" t="s" s="2">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="AH43" t="s" s="2">
         <v>85</v>
@@ -6898,14 +6893,14 @@
         <v>3</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="C44" t="s" s="2">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="D44" s="2"/>
       <c r="E44" t="s" s="2">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="F44" s="2"/>
       <c r="G44" t="s" s="2">
@@ -6924,16 +6919,16 @@
         <v>78</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="M44" t="s" s="2">
+        <v>309</v>
+      </c>
+      <c r="N44" t="s" s="2">
         <v>310</v>
       </c>
-      <c r="N44" t="s" s="2">
+      <c r="O44" t="s" s="2">
         <v>311</v>
-      </c>
-      <c r="O44" t="s" s="2">
-        <v>312</v>
       </c>
       <c r="P44" s="2"/>
       <c r="Q44" t="s" s="2">
@@ -6983,7 +6978,7 @@
         <v>78</v>
       </c>
       <c r="AG44" t="s" s="2">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="AH44" t="s" s="2">
         <v>76</v>
@@ -7003,10 +6998,10 @@
         <v>3</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="C45" t="s" s="2">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="D45" s="2"/>
       <c r="E45" t="s" s="2">
@@ -7032,10 +7027,10 @@
         <v>168</v>
       </c>
       <c r="M45" t="s" s="2">
+        <v>313</v>
+      </c>
+      <c r="N45" t="s" s="2">
         <v>314</v>
-      </c>
-      <c r="N45" t="s" s="2">
-        <v>315</v>
       </c>
       <c r="O45" s="2"/>
       <c r="P45" s="2"/>
@@ -7086,7 +7081,7 @@
         <v>78</v>
       </c>
       <c r="AG45" t="s" s="2">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="AH45" t="s" s="2">
         <v>76</v>
@@ -7106,10 +7101,10 @@
         <v>3</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="C46" t="s" s="2">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="D46" s="2"/>
       <c r="E46" t="s" s="2">
@@ -7135,13 +7130,13 @@
         <v>105</v>
       </c>
       <c r="M46" t="s" s="2">
+        <v>316</v>
+      </c>
+      <c r="N46" t="s" s="2">
         <v>317</v>
       </c>
-      <c r="N46" t="s" s="2">
+      <c r="O46" t="s" s="2">
         <v>318</v>
-      </c>
-      <c r="O46" t="s" s="2">
-        <v>319</v>
       </c>
       <c r="P46" s="2"/>
       <c r="Q46" t="s" s="2">
@@ -7170,11 +7165,11 @@
         <v>188</v>
       </c>
       <c r="Z46" t="s" s="2">
+        <v>319</v>
+      </c>
+      <c r="AA46" t="s" s="2">
         <v>320</v>
       </c>
-      <c r="AA46" t="s" s="2">
-        <v>321</v>
-      </c>
       <c r="AB46" t="s" s="2">
         <v>78</v>
       </c>
@@ -7191,7 +7186,7 @@
         <v>78</v>
       </c>
       <c r="AG46" t="s" s="2">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="AH46" t="s" s="2">
         <v>76</v>
@@ -7211,10 +7206,10 @@
         <v>3</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="C47" t="s" s="2">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="D47" s="2"/>
       <c r="E47" t="s" s="2">
@@ -7240,13 +7235,13 @@
         <v>184</v>
       </c>
       <c r="M47" t="s" s="2">
+        <v>322</v>
+      </c>
+      <c r="N47" t="s" s="2">
         <v>323</v>
       </c>
-      <c r="N47" t="s" s="2">
+      <c r="O47" t="s" s="2">
         <v>324</v>
-      </c>
-      <c r="O47" t="s" s="2">
-        <v>325</v>
       </c>
       <c r="P47" s="2"/>
       <c r="Q47" t="s" s="2">
@@ -7272,14 +7267,14 @@
         <v>78</v>
       </c>
       <c r="Y47" t="s" s="2">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="Z47" t="s" s="2">
+        <v>325</v>
+      </c>
+      <c r="AA47" t="s" s="2">
         <v>326</v>
       </c>
-      <c r="AA47" t="s" s="2">
-        <v>327</v>
-      </c>
       <c r="AB47" t="s" s="2">
         <v>78</v>
       </c>
@@ -7296,7 +7291,7 @@
         <v>78</v>
       </c>
       <c r="AG47" t="s" s="2">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="AH47" t="s" s="2">
         <v>76</v>
@@ -7316,10 +7311,10 @@
         <v>3</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="C48" t="s" s="2">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="D48" s="2"/>
       <c r="E48" t="s" s="2">
@@ -7342,16 +7337,16 @@
         <v>78</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="M48" t="s" s="2">
+        <v>328</v>
+      </c>
+      <c r="N48" t="s" s="2">
         <v>329</v>
       </c>
-      <c r="N48" t="s" s="2">
+      <c r="O48" t="s" s="2">
         <v>330</v>
-      </c>
-      <c r="O48" t="s" s="2">
-        <v>331</v>
       </c>
       <c r="P48" s="2"/>
       <c r="Q48" t="s" s="2">
@@ -7401,7 +7396,7 @@
         <v>78</v>
       </c>
       <c r="AG48" t="s" s="2">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="AH48" t="s" s="2">
         <v>76</v>
@@ -7418,17 +7413,17 @@
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="C49" t="s" s="2">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="D49" s="2"/>
       <c r="E49" t="s" s="2">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="F49" s="2"/>
       <c r="G49" t="s" s="2">
@@ -7450,10 +7445,10 @@
         <v>79</v>
       </c>
       <c r="M49" t="s" s="2">
+        <v>339</v>
+      </c>
+      <c r="N49" t="s" s="2">
         <v>340</v>
-      </c>
-      <c r="N49" t="s" s="2">
-        <v>341</v>
       </c>
       <c r="O49" s="2"/>
       <c r="P49" s="2"/>
@@ -7504,7 +7499,7 @@
         <v>78</v>
       </c>
       <c r="AG49" t="s" s="2">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="AH49" t="s" s="2">
         <v>76</v>
@@ -7516,18 +7511,18 @@
         <v>78</v>
       </c>
       <c r="AK49" t="s" s="2">
-        <v>342</v>
+        <v>341</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="C50" t="s" s="2">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="D50" s="2"/>
       <c r="E50" t="s" s="2">
@@ -7626,13 +7621,13 @@
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="C51" t="s" s="2">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="D51" s="2"/>
       <c r="E51" t="s" s="2">
@@ -7729,13 +7724,13 @@
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="C52" t="s" s="2">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="D52" s="2"/>
       <c r="E52" t="s" s="2">
@@ -7834,13 +7829,13 @@
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="C53" t="s" s="2">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="D53" s="2"/>
       <c r="E53" t="s" s="2">
@@ -7866,7 +7861,7 @@
         <v>105</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="N53" t="s" s="2">
         <v>107</v>
@@ -7939,13 +7934,13 @@
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="C54" t="s" s="2">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="D54" s="2"/>
       <c r="E54" t="s" s="2">
@@ -8044,13 +8039,13 @@
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="C55" t="s" s="2">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="D55" s="2"/>
       <c r="E55" t="s" s="2">
@@ -8149,13 +8144,13 @@
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="C56" t="s" s="2">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="D56" s="2"/>
       <c r="E56" t="s" s="2">
@@ -8250,16 +8245,16 @@
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B57" t="s" s="2">
+        <v>350</v>
+      </c>
+      <c r="C57" t="s" s="2">
+        <v>349</v>
+      </c>
+      <c r="D57" t="s" s="2">
         <v>351</v>
-      </c>
-      <c r="C57" t="s" s="2">
-        <v>350</v>
-      </c>
-      <c r="D57" t="s" s="2">
-        <v>352</v>
       </c>
       <c r="E57" t="s" s="2">
         <v>78</v>
@@ -8281,13 +8276,13 @@
         <v>78</v>
       </c>
       <c r="L57" t="s" s="2">
+        <v>352</v>
+      </c>
+      <c r="M57" t="s" s="2">
         <v>353</v>
       </c>
-      <c r="M57" t="s" s="2">
+      <c r="N57" t="s" s="2">
         <v>354</v>
-      </c>
-      <c r="N57" t="s" s="2">
-        <v>355</v>
       </c>
       <c r="O57" s="2"/>
       <c r="P57" s="2"/>
@@ -8355,13 +8350,13 @@
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B58" t="s" s="2">
+        <v>355</v>
+      </c>
+      <c r="C58" t="s" s="2">
         <v>356</v>
-      </c>
-      <c r="C58" t="s" s="2">
-        <v>357</v>
       </c>
       <c r="D58" s="2"/>
       <c r="E58" t="s" s="2">
@@ -8458,13 +8453,13 @@
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B59" t="s" s="2">
+        <v>357</v>
+      </c>
+      <c r="C59" t="s" s="2">
         <v>358</v>
-      </c>
-      <c r="C59" t="s" s="2">
-        <v>359</v>
       </c>
       <c r="D59" s="2"/>
       <c r="E59" t="s" s="2">
@@ -8561,13 +8556,13 @@
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B60" t="s" s="2">
+        <v>359</v>
+      </c>
+      <c r="C60" t="s" s="2">
         <v>360</v>
-      </c>
-      <c r="C60" t="s" s="2">
-        <v>361</v>
       </c>
       <c r="D60" s="2"/>
       <c r="E60" t="s" s="2">
@@ -8607,7 +8602,7 @@
       </c>
       <c r="R60" s="2"/>
       <c r="S60" t="s" s="2">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="T60" t="s" s="2">
         <v>78</v>
@@ -8666,13 +8661,13 @@
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B61" t="s" s="2">
+        <v>362</v>
+      </c>
+      <c r="C61" t="s" s="2">
         <v>363</v>
-      </c>
-      <c r="C61" t="s" s="2">
-        <v>364</v>
       </c>
       <c r="D61" s="2"/>
       <c r="E61" t="s" s="2">
@@ -8695,7 +8690,7 @@
         <v>78</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="M61" t="s" s="2">
         <v>161</v>
@@ -8769,16 +8764,16 @@
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B62" t="s" s="2">
+        <v>365</v>
+      </c>
+      <c r="C62" t="s" s="2">
+        <v>349</v>
+      </c>
+      <c r="D62" t="s" s="2">
         <v>366</v>
-      </c>
-      <c r="C62" t="s" s="2">
-        <v>350</v>
-      </c>
-      <c r="D62" t="s" s="2">
-        <v>367</v>
       </c>
       <c r="E62" t="s" s="2">
         <v>78</v>
@@ -8800,13 +8795,13 @@
         <v>78</v>
       </c>
       <c r="L62" t="s" s="2">
+        <v>367</v>
+      </c>
+      <c r="M62" t="s" s="2">
         <v>368</v>
       </c>
-      <c r="M62" t="s" s="2">
+      <c r="N62" t="s" s="2">
         <v>369</v>
-      </c>
-      <c r="N62" t="s" s="2">
-        <v>370</v>
       </c>
       <c r="O62" s="2"/>
       <c r="P62" s="2"/>
@@ -8874,16 +8869,16 @@
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B63" t="s" s="2">
+        <v>370</v>
+      </c>
+      <c r="C63" t="s" s="2">
+        <v>349</v>
+      </c>
+      <c r="D63" t="s" s="2">
         <v>371</v>
-      </c>
-      <c r="C63" t="s" s="2">
-        <v>350</v>
-      </c>
-      <c r="D63" t="s" s="2">
-        <v>372</v>
       </c>
       <c r="E63" t="s" s="2">
         <v>78</v>
@@ -8905,16 +8900,16 @@
         <v>78</v>
       </c>
       <c r="L63" t="s" s="2">
+        <v>372</v>
+      </c>
+      <c r="M63" t="s" s="2">
         <v>373</v>
       </c>
-      <c r="M63" t="s" s="2">
+      <c r="N63" t="s" s="2">
         <v>374</v>
       </c>
-      <c r="N63" t="s" s="2">
+      <c r="O63" t="s" s="2">
         <v>375</v>
-      </c>
-      <c r="O63" t="s" s="2">
-        <v>376</v>
       </c>
       <c r="P63" s="2"/>
       <c r="Q63" t="s" s="2">
@@ -8981,16 +8976,16 @@
     </row>
     <row r="64">
       <c r="A64" t="s" s="2">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B64" t="s" s="2">
+        <v>376</v>
+      </c>
+      <c r="C64" t="s" s="2">
+        <v>349</v>
+      </c>
+      <c r="D64" t="s" s="2">
         <v>377</v>
-      </c>
-      <c r="C64" t="s" s="2">
-        <v>350</v>
-      </c>
-      <c r="D64" t="s" s="2">
-        <v>378</v>
       </c>
       <c r="E64" t="s" s="2">
         <v>78</v>
@@ -9012,13 +9007,13 @@
         <v>78</v>
       </c>
       <c r="L64" t="s" s="2">
+        <v>378</v>
+      </c>
+      <c r="M64" t="s" s="2">
         <v>379</v>
       </c>
-      <c r="M64" t="s" s="2">
+      <c r="N64" t="s" s="2">
         <v>380</v>
-      </c>
-      <c r="N64" t="s" s="2">
-        <v>381</v>
       </c>
       <c r="O64" s="2"/>
       <c r="P64" s="2"/>
@@ -9086,16 +9081,16 @@
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B65" t="s" s="2">
+        <v>381</v>
+      </c>
+      <c r="C65" t="s" s="2">
+        <v>349</v>
+      </c>
+      <c r="D65" t="s" s="2">
         <v>382</v>
-      </c>
-      <c r="C65" t="s" s="2">
-        <v>350</v>
-      </c>
-      <c r="D65" t="s" s="2">
-        <v>383</v>
       </c>
       <c r="E65" t="s" s="2">
         <v>78</v>
@@ -9117,13 +9112,13 @@
         <v>78</v>
       </c>
       <c r="L65" t="s" s="2">
+        <v>383</v>
+      </c>
+      <c r="M65" t="s" s="2">
         <v>384</v>
       </c>
-      <c r="M65" t="s" s="2">
+      <c r="N65" t="s" s="2">
         <v>385</v>
-      </c>
-      <c r="N65" t="s" s="2">
-        <v>386</v>
       </c>
       <c r="O65" s="2"/>
       <c r="P65" s="2"/>
@@ -9191,16 +9186,16 @@
     </row>
     <row r="66">
       <c r="A66" t="s" s="2">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B66" t="s" s="2">
+        <v>386</v>
+      </c>
+      <c r="C66" t="s" s="2">
+        <v>349</v>
+      </c>
+      <c r="D66" t="s" s="2">
         <v>387</v>
-      </c>
-      <c r="C66" t="s" s="2">
-        <v>350</v>
-      </c>
-      <c r="D66" t="s" s="2">
-        <v>388</v>
       </c>
       <c r="E66" t="s" s="2">
         <v>78</v>
@@ -9222,13 +9217,13 @@
         <v>78</v>
       </c>
       <c r="L66" t="s" s="2">
+        <v>388</v>
+      </c>
+      <c r="M66" t="s" s="2">
         <v>389</v>
       </c>
-      <c r="M66" t="s" s="2">
+      <c r="N66" t="s" s="2">
         <v>390</v>
-      </c>
-      <c r="N66" t="s" s="2">
-        <v>391</v>
       </c>
       <c r="O66" s="2"/>
       <c r="P66" s="2"/>
@@ -9296,16 +9291,16 @@
     </row>
     <row r="67">
       <c r="A67" t="s" s="2">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B67" t="s" s="2">
+        <v>391</v>
+      </c>
+      <c r="C67" t="s" s="2">
+        <v>349</v>
+      </c>
+      <c r="D67" t="s" s="2">
         <v>392</v>
-      </c>
-      <c r="C67" t="s" s="2">
-        <v>350</v>
-      </c>
-      <c r="D67" t="s" s="2">
-        <v>393</v>
       </c>
       <c r="E67" t="s" s="2">
         <v>78</v>
@@ -9327,16 +9322,16 @@
         <v>78</v>
       </c>
       <c r="L67" t="s" s="2">
+        <v>393</v>
+      </c>
+      <c r="M67" t="s" s="2">
         <v>394</v>
       </c>
-      <c r="M67" t="s" s="2">
+      <c r="N67" t="s" s="2">
         <v>395</v>
       </c>
-      <c r="N67" t="s" s="2">
+      <c r="O67" t="s" s="2">
         <v>396</v>
-      </c>
-      <c r="O67" t="s" s="2">
-        <v>397</v>
       </c>
       <c r="P67" s="2"/>
       <c r="Q67" t="s" s="2">
@@ -9403,13 +9398,13 @@
     </row>
     <row r="68">
       <c r="A68" t="s" s="2">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="C68" t="s" s="2">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="D68" s="2"/>
       <c r="E68" t="s" s="2">
@@ -9510,13 +9505,13 @@
     </row>
     <row r="69">
       <c r="A69" t="s" s="2">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="C69" t="s" s="2">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="D69" s="2"/>
       <c r="E69" t="s" s="2">
@@ -9542,14 +9537,14 @@
         <v>178</v>
       </c>
       <c r="M69" t="s" s="2">
+        <v>399</v>
+      </c>
+      <c r="N69" t="s" s="2">
         <v>400</v>
-      </c>
-      <c r="N69" t="s" s="2">
-        <v>401</v>
       </c>
       <c r="O69" s="2"/>
       <c r="P69" t="s" s="2">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="Q69" t="s" s="2">
         <v>78</v>
@@ -9598,7 +9593,7 @@
         <v>78</v>
       </c>
       <c r="AG69" t="s" s="2">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="AH69" t="s" s="2">
         <v>76</v>
@@ -9615,13 +9610,13 @@
     </row>
     <row r="70">
       <c r="A70" t="s" s="2">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="C70" t="s" s="2">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="D70" s="2"/>
       <c r="E70" t="s" s="2">
@@ -9644,26 +9639,26 @@
         <v>86</v>
       </c>
       <c r="L70" t="s" s="2">
+        <v>403</v>
+      </c>
+      <c r="M70" t="s" s="2">
         <v>404</v>
       </c>
-      <c r="M70" t="s" s="2">
+      <c r="N70" t="s" s="2">
         <v>405</v>
       </c>
-      <c r="N70" t="s" s="2">
+      <c r="O70" t="s" s="2">
         <v>406</v>
       </c>
-      <c r="O70" t="s" s="2">
+      <c r="P70" t="s" s="2">
         <v>407</v>
       </c>
-      <c r="P70" t="s" s="2">
+      <c r="Q70" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="R70" t="s" s="2">
         <v>408</v>
       </c>
-      <c r="Q70" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="R70" t="s" s="2">
-        <v>409</v>
-      </c>
       <c r="S70" t="s" s="2">
         <v>78</v>
       </c>
@@ -9707,7 +9702,7 @@
         <v>78</v>
       </c>
       <c r="AG70" t="s" s="2">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="AH70" t="s" s="2">
         <v>76</v>
@@ -9724,13 +9719,13 @@
     </row>
     <row r="71">
       <c r="A71" t="s" s="2">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="C71" t="s" s="2">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="D71" s="2"/>
       <c r="E71" t="s" s="2">
@@ -9753,19 +9748,19 @@
         <v>86</v>
       </c>
       <c r="L71" t="s" s="2">
+        <v>410</v>
+      </c>
+      <c r="M71" t="s" s="2">
         <v>411</v>
       </c>
-      <c r="M71" t="s" s="2">
+      <c r="N71" t="s" s="2">
         <v>412</v>
       </c>
-      <c r="N71" t="s" s="2">
+      <c r="O71" t="s" s="2">
         <v>413</v>
       </c>
-      <c r="O71" t="s" s="2">
+      <c r="P71" t="s" s="2">
         <v>414</v>
-      </c>
-      <c r="P71" t="s" s="2">
-        <v>415</v>
       </c>
       <c r="Q71" t="s" s="2">
         <v>78</v>
@@ -9814,7 +9809,7 @@
         <v>78</v>
       </c>
       <c r="AG71" t="s" s="2">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="AH71" t="s" s="2">
         <v>76</v>
@@ -9826,18 +9821,18 @@
         <v>78</v>
       </c>
       <c r="AK71" t="s" s="2">
-        <v>416</v>
+        <v>415</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="s" s="2">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="C72" t="s" s="2">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="D72" s="2"/>
       <c r="E72" t="s" s="2">
@@ -9860,7 +9855,7 @@
         <v>78</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="M72" t="s" s="2">
         <v>143</v>
@@ -9934,13 +9929,13 @@
     </row>
     <row r="73">
       <c r="A73" t="s" s="2">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="C73" t="s" s="2">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="D73" s="2"/>
       <c r="E73" t="s" s="2">
@@ -9966,10 +9961,10 @@
         <v>128</v>
       </c>
       <c r="M73" t="s" s="2">
+        <v>266</v>
+      </c>
+      <c r="N73" t="s" s="2">
         <v>267</v>
-      </c>
-      <c r="N73" t="s" s="2">
-        <v>268</v>
       </c>
       <c r="O73" t="s" s="2">
         <v>174</v>
@@ -10039,13 +10034,13 @@
     </row>
     <row r="74">
       <c r="A74" t="s" s="2">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="C74" t="s" s="2">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="D74" s="2"/>
       <c r="E74" t="s" s="2">
@@ -10071,16 +10066,16 @@
         <v>105</v>
       </c>
       <c r="M74" t="s" s="2">
+        <v>419</v>
+      </c>
+      <c r="N74" t="s" s="2">
         <v>420</v>
       </c>
-      <c r="N74" t="s" s="2">
+      <c r="O74" t="s" s="2">
         <v>421</v>
       </c>
-      <c r="O74" t="s" s="2">
+      <c r="P74" t="s" s="2">
         <v>422</v>
-      </c>
-      <c r="P74" t="s" s="2">
-        <v>423</v>
       </c>
       <c r="Q74" t="s" s="2">
         <v>78</v>
@@ -10108,28 +10103,28 @@
         <v>188</v>
       </c>
       <c r="Z74" t="s" s="2">
+        <v>423</v>
+      </c>
+      <c r="AA74" t="s" s="2">
         <v>424</v>
       </c>
-      <c r="AA74" t="s" s="2">
+      <c r="AB74" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC74" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD74" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE74" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF74" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AG74" t="s" s="2">
         <v>425</v>
-      </c>
-      <c r="AB74" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC74" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD74" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE74" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF74" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AG74" t="s" s="2">
-        <v>426</v>
       </c>
       <c r="AH74" t="s" s="2">
         <v>76</v>
@@ -10146,13 +10141,13 @@
     </row>
     <row r="75">
       <c r="A75" t="s" s="2">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="C75" t="s" s="2">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="D75" s="2"/>
       <c r="E75" t="s" s="2">
@@ -10175,19 +10170,19 @@
         <v>86</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="M75" t="s" s="2">
+        <v>427</v>
+      </c>
+      <c r="N75" t="s" s="2">
         <v>428</v>
       </c>
-      <c r="N75" t="s" s="2">
+      <c r="O75" t="s" s="2">
         <v>429</v>
       </c>
-      <c r="O75" t="s" s="2">
+      <c r="P75" t="s" s="2">
         <v>430</v>
-      </c>
-      <c r="P75" t="s" s="2">
-        <v>431</v>
       </c>
       <c r="Q75" t="s" s="2">
         <v>78</v>
@@ -10236,7 +10231,7 @@
         <v>78</v>
       </c>
       <c r="AG75" t="s" s="2">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="AH75" t="s" s="2">
         <v>76</v>
@@ -10253,17 +10248,17 @@
     </row>
     <row r="76">
       <c r="A76" t="s" s="2">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="C76" t="s" s="2">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="D76" s="2"/>
       <c r="E76" t="s" s="2">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="F76" s="2"/>
       <c r="G76" t="s" s="2">
@@ -10282,16 +10277,16 @@
         <v>86</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="M76" t="s" s="2">
+        <v>434</v>
+      </c>
+      <c r="N76" t="s" s="2">
         <v>435</v>
       </c>
-      <c r="N76" t="s" s="2">
+      <c r="O76" t="s" s="2">
         <v>436</v>
-      </c>
-      <c r="O76" t="s" s="2">
-        <v>437</v>
       </c>
       <c r="P76" s="2"/>
       <c r="Q76" t="s" s="2">
@@ -10305,43 +10300,43 @@
         <v>78</v>
       </c>
       <c r="U76" t="s" s="2">
+        <v>437</v>
+      </c>
+      <c r="V76" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W76" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X76" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y76" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z76" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA76" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB76" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC76" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD76" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE76" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF76" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AG76" t="s" s="2">
         <v>438</v>
-      </c>
-      <c r="V76" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="W76" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="X76" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y76" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Z76" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AA76" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB76" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC76" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD76" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE76" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF76" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AG76" t="s" s="2">
-        <v>439</v>
       </c>
       <c r="AH76" t="s" s="2">
         <v>76</v>
@@ -10358,17 +10353,17 @@
     </row>
     <row r="77">
       <c r="A77" t="s" s="2">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="C77" t="s" s="2">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="D77" s="2"/>
       <c r="E77" t="s" s="2">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="F77" s="2"/>
       <c r="G77" t="s" s="2">
@@ -10387,16 +10382,16 @@
         <v>86</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="M77" t="s" s="2">
+        <v>441</v>
+      </c>
+      <c r="N77" t="s" s="2">
         <v>442</v>
       </c>
-      <c r="N77" t="s" s="2">
+      <c r="O77" t="s" s="2">
         <v>443</v>
-      </c>
-      <c r="O77" t="s" s="2">
-        <v>444</v>
       </c>
       <c r="P77" s="2"/>
       <c r="Q77" t="s" s="2">
@@ -10446,7 +10441,7 @@
         <v>78</v>
       </c>
       <c r="AG77" t="s" s="2">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="AH77" t="s" s="2">
         <v>76</v>
@@ -10463,13 +10458,13 @@
     </row>
     <row r="78">
       <c r="A78" t="s" s="2">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="C78" t="s" s="2">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="D78" s="2"/>
       <c r="E78" t="s" s="2">
@@ -10492,13 +10487,13 @@
         <v>86</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="M78" t="s" s="2">
+        <v>446</v>
+      </c>
+      <c r="N78" t="s" s="2">
         <v>447</v>
-      </c>
-      <c r="N78" t="s" s="2">
-        <v>448</v>
       </c>
       <c r="O78" s="2"/>
       <c r="P78" s="2"/>
@@ -10549,7 +10544,7 @@
         <v>78</v>
       </c>
       <c r="AG78" t="s" s="2">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="AH78" t="s" s="2">
         <v>76</v>
@@ -10566,13 +10561,13 @@
     </row>
     <row r="79">
       <c r="A79" t="s" s="2">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="C79" t="s" s="2">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="D79" s="2"/>
       <c r="E79" t="s" s="2">
@@ -10595,13 +10590,13 @@
         <v>86</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="M79" t="s" s="2">
+        <v>450</v>
+      </c>
+      <c r="N79" t="s" s="2">
         <v>451</v>
-      </c>
-      <c r="N79" t="s" s="2">
-        <v>452</v>
       </c>
       <c r="O79" s="2"/>
       <c r="P79" s="2"/>
@@ -10652,7 +10647,7 @@
         <v>78</v>
       </c>
       <c r="AG79" t="s" s="2">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="AH79" t="s" s="2">
         <v>76</v>
@@ -10669,13 +10664,13 @@
     </row>
     <row r="80">
       <c r="A80" t="s" s="2">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="C80" t="s" s="2">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="D80" s="2"/>
       <c r="E80" t="s" s="2">
@@ -10698,17 +10693,17 @@
         <v>86</v>
       </c>
       <c r="L80" t="s" s="2">
+        <v>454</v>
+      </c>
+      <c r="M80" t="s" s="2">
         <v>455</v>
       </c>
-      <c r="M80" t="s" s="2">
+      <c r="N80" t="s" s="2">
         <v>456</v>
-      </c>
-      <c r="N80" t="s" s="2">
-        <v>457</v>
       </c>
       <c r="O80" s="2"/>
       <c r="P80" t="s" s="2">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="Q80" t="s" s="2">
         <v>78</v>
@@ -10757,7 +10752,7 @@
         <v>78</v>
       </c>
       <c r="AG80" t="s" s="2">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="AH80" t="s" s="2">
         <v>76</v>
@@ -10774,13 +10769,13 @@
     </row>
     <row r="81">
       <c r="A81" t="s" s="2">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="C81" t="s" s="2">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="D81" s="2"/>
       <c r="E81" t="s" s="2">
@@ -10803,19 +10798,19 @@
         <v>86</v>
       </c>
       <c r="L81" t="s" s="2">
+        <v>460</v>
+      </c>
+      <c r="M81" t="s" s="2">
         <v>461</v>
       </c>
-      <c r="M81" t="s" s="2">
+      <c r="N81" t="s" s="2">
         <v>462</v>
       </c>
-      <c r="N81" t="s" s="2">
+      <c r="O81" t="s" s="2">
         <v>463</v>
       </c>
-      <c r="O81" t="s" s="2">
+      <c r="P81" t="s" s="2">
         <v>464</v>
-      </c>
-      <c r="P81" t="s" s="2">
-        <v>465</v>
       </c>
       <c r="Q81" t="s" s="2">
         <v>78</v>
@@ -10864,7 +10859,7 @@
         <v>78</v>
       </c>
       <c r="AG81" t="s" s="2">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="AH81" t="s" s="2">
         <v>76</v>
@@ -10881,13 +10876,13 @@
     </row>
     <row r="82">
       <c r="A82" t="s" s="2">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="C82" t="s" s="2">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="D82" s="2"/>
       <c r="E82" t="s" s="2">
@@ -10913,16 +10908,16 @@
         <v>105</v>
       </c>
       <c r="M82" t="s" s="2">
+        <v>466</v>
+      </c>
+      <c r="N82" t="s" s="2">
         <v>467</v>
       </c>
-      <c r="N82" t="s" s="2">
+      <c r="O82" t="s" s="2">
         <v>468</v>
       </c>
-      <c r="O82" t="s" s="2">
+      <c r="P82" t="s" s="2">
         <v>469</v>
-      </c>
-      <c r="P82" t="s" s="2">
-        <v>470</v>
       </c>
       <c r="Q82" t="s" s="2">
         <v>78</v>
@@ -10950,11 +10945,11 @@
         <v>188</v>
       </c>
       <c r="Z82" t="s" s="2">
+        <v>470</v>
+      </c>
+      <c r="AA82" t="s" s="2">
         <v>471</v>
       </c>
-      <c r="AA82" t="s" s="2">
-        <v>472</v>
-      </c>
       <c r="AB82" t="s" s="2">
         <v>78</v>
       </c>
@@ -10971,7 +10966,7 @@
         <v>78</v>
       </c>
       <c r="AG82" t="s" s="2">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="AH82" t="s" s="2">
         <v>76</v>
@@ -10988,13 +10983,13 @@
     </row>
     <row r="83">
       <c r="A83" t="s" s="2">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="C83" t="s" s="2">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="D83" s="2"/>
       <c r="E83" t="s" s="2">
@@ -11017,19 +11012,19 @@
         <v>86</v>
       </c>
       <c r="L83" t="s" s="2">
+        <v>473</v>
+      </c>
+      <c r="M83" t="s" s="2">
         <v>474</v>
       </c>
-      <c r="M83" t="s" s="2">
+      <c r="N83" t="s" s="2">
         <v>475</v>
       </c>
-      <c r="N83" t="s" s="2">
+      <c r="O83" t="s" s="2">
         <v>476</v>
       </c>
-      <c r="O83" t="s" s="2">
+      <c r="P83" t="s" s="2">
         <v>477</v>
-      </c>
-      <c r="P83" t="s" s="2">
-        <v>478</v>
       </c>
       <c r="Q83" t="s" s="2">
         <v>78</v>
@@ -11078,7 +11073,7 @@
         <v>78</v>
       </c>
       <c r="AG83" t="s" s="2">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="AH83" t="s" s="2">
         <v>76</v>
@@ -11095,13 +11090,13 @@
     </row>
     <row r="84">
       <c r="A84" t="s" s="2">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="C84" t="s" s="2">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="D84" s="2"/>
       <c r="E84" t="s" s="2">
@@ -11124,19 +11119,19 @@
         <v>86</v>
       </c>
       <c r="L84" t="s" s="2">
+        <v>479</v>
+      </c>
+      <c r="M84" t="s" s="2">
         <v>480</v>
       </c>
-      <c r="M84" t="s" s="2">
+      <c r="N84" t="s" s="2">
         <v>481</v>
       </c>
-      <c r="N84" t="s" s="2">
+      <c r="O84" t="s" s="2">
         <v>482</v>
       </c>
-      <c r="O84" t="s" s="2">
+      <c r="P84" t="s" s="2">
         <v>483</v>
-      </c>
-      <c r="P84" t="s" s="2">
-        <v>484</v>
       </c>
       <c r="Q84" t="s" s="2">
         <v>78</v>
@@ -11185,7 +11180,7 @@
         <v>78</v>
       </c>
       <c r="AG84" t="s" s="2">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="AH84" t="s" s="2">
         <v>76</v>
@@ -11202,13 +11197,13 @@
     </row>
     <row r="85">
       <c r="A85" t="s" s="2">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="C85" t="s" s="2">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="D85" s="2"/>
       <c r="E85" t="s" s="2">
@@ -11231,19 +11226,19 @@
         <v>86</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="M85" t="s" s="2">
+        <v>485</v>
+      </c>
+      <c r="N85" t="s" s="2">
         <v>486</v>
       </c>
-      <c r="N85" t="s" s="2">
+      <c r="O85" t="s" s="2">
         <v>487</v>
       </c>
-      <c r="O85" t="s" s="2">
+      <c r="P85" t="s" s="2">
         <v>488</v>
-      </c>
-      <c r="P85" t="s" s="2">
-        <v>489</v>
       </c>
       <c r="Q85" t="s" s="2">
         <v>78</v>
@@ -11292,7 +11287,7 @@
         <v>78</v>
       </c>
       <c r="AG85" t="s" s="2">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="AH85" t="s" s="2">
         <v>76</v>
@@ -11309,13 +11304,13 @@
     </row>
     <row r="86">
       <c r="A86" t="s" s="2">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="C86" t="s" s="2">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="D86" s="2"/>
       <c r="E86" t="s" s="2">
@@ -11341,14 +11336,14 @@
         <v>184</v>
       </c>
       <c r="M86" t="s" s="2">
+        <v>490</v>
+      </c>
+      <c r="N86" t="s" s="2">
         <v>491</v>
-      </c>
-      <c r="N86" t="s" s="2">
-        <v>492</v>
       </c>
       <c r="O86" s="2"/>
       <c r="P86" t="s" s="2">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="Q86" t="s" s="2">
         <v>78</v>
@@ -11373,14 +11368,14 @@
         <v>78</v>
       </c>
       <c r="Y86" t="s" s="2">
+        <v>493</v>
+      </c>
+      <c r="Z86" t="s" s="2">
         <v>494</v>
       </c>
-      <c r="Z86" t="s" s="2">
+      <c r="AA86" t="s" s="2">
         <v>495</v>
       </c>
-      <c r="AA86" t="s" s="2">
-        <v>496</v>
-      </c>
       <c r="AB86" t="s" s="2">
         <v>78</v>
       </c>
@@ -11397,7 +11392,7 @@
         <v>78</v>
       </c>
       <c r="AG86" t="s" s="2">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="AH86" t="s" s="2">
         <v>76</v>
@@ -11414,13 +11409,13 @@
     </row>
     <row r="87">
       <c r="A87" t="s" s="2">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="C87" t="s" s="2">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="D87" s="2"/>
       <c r="E87" t="s" s="2">
@@ -11443,19 +11438,19 @@
         <v>78</v>
       </c>
       <c r="L87" t="s" s="2">
+        <v>497</v>
+      </c>
+      <c r="M87" t="s" s="2">
         <v>498</v>
       </c>
-      <c r="M87" t="s" s="2">
+      <c r="N87" t="s" s="2">
         <v>499</v>
       </c>
-      <c r="N87" t="s" s="2">
+      <c r="O87" t="s" s="2">
         <v>500</v>
       </c>
-      <c r="O87" t="s" s="2">
+      <c r="P87" t="s" s="2">
         <v>501</v>
-      </c>
-      <c r="P87" t="s" s="2">
-        <v>502</v>
       </c>
       <c r="Q87" t="s" s="2">
         <v>78</v>
@@ -11504,7 +11499,7 @@
         <v>78</v>
       </c>
       <c r="AG87" t="s" s="2">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="AH87" t="s" s="2">
         <v>76</v>
@@ -11521,13 +11516,13 @@
     </row>
     <row r="88">
       <c r="A88" t="s" s="2">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="C88" t="s" s="2">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="D88" s="2"/>
       <c r="E88" t="s" s="2">
@@ -11550,19 +11545,19 @@
         <v>78</v>
       </c>
       <c r="L88" t="s" s="2">
+        <v>503</v>
+      </c>
+      <c r="M88" t="s" s="2">
         <v>504</v>
       </c>
-      <c r="M88" t="s" s="2">
+      <c r="N88" t="s" s="2">
         <v>505</v>
       </c>
-      <c r="N88" t="s" s="2">
+      <c r="O88" t="s" s="2">
         <v>506</v>
       </c>
-      <c r="O88" t="s" s="2">
+      <c r="P88" t="s" s="2">
         <v>507</v>
-      </c>
-      <c r="P88" t="s" s="2">
-        <v>508</v>
       </c>
       <c r="Q88" t="s" s="2">
         <v>78</v>
@@ -11611,7 +11606,7 @@
         <v>78</v>
       </c>
       <c r="AG88" t="s" s="2">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="AH88" t="s" s="2">
         <v>76</v>
@@ -11628,13 +11623,13 @@
     </row>
     <row r="89">
       <c r="A89" t="s" s="2">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="C89" t="s" s="2">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="D89" s="2"/>
       <c r="E89" t="s" s="2">
@@ -11657,19 +11652,19 @@
         <v>78</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="M89" t="s" s="2">
+        <v>509</v>
+      </c>
+      <c r="N89" t="s" s="2">
         <v>510</v>
       </c>
-      <c r="N89" t="s" s="2">
+      <c r="O89" t="s" s="2">
         <v>511</v>
       </c>
-      <c r="O89" t="s" s="2">
+      <c r="P89" t="s" s="2">
         <v>512</v>
-      </c>
-      <c r="P89" t="s" s="2">
-        <v>513</v>
       </c>
       <c r="Q89" t="s" s="2">
         <v>78</v>
@@ -11718,7 +11713,7 @@
         <v>78</v>
       </c>
       <c r="AG89" t="s" s="2">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="AH89" t="s" s="2">
         <v>76</v>
@@ -11730,18 +11725,18 @@
         <v>78</v>
       </c>
       <c r="AK89" t="s" s="2">
-        <v>514</v>
+        <v>513</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="s" s="2">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="C90" t="s" s="2">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="D90" s="2"/>
       <c r="E90" t="s" s="2">
@@ -11764,7 +11759,7 @@
         <v>78</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="M90" t="s" s="2">
         <v>143</v>
@@ -11838,13 +11833,13 @@
     </row>
     <row r="91">
       <c r="A91" t="s" s="2">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="C91" t="s" s="2">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="D91" s="2"/>
       <c r="E91" t="s" s="2">
@@ -11870,10 +11865,10 @@
         <v>128</v>
       </c>
       <c r="M91" t="s" s="2">
+        <v>266</v>
+      </c>
+      <c r="N91" t="s" s="2">
         <v>267</v>
-      </c>
-      <c r="N91" t="s" s="2">
-        <v>268</v>
       </c>
       <c r="O91" t="s" s="2">
         <v>174</v>
@@ -11943,17 +11938,17 @@
     </row>
     <row r="92">
       <c r="A92" t="s" s="2">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="C92" t="s" s="2">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="D92" s="2"/>
       <c r="E92" t="s" s="2">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="F92" s="2"/>
       <c r="G92" t="s" s="2">
@@ -11975,10 +11970,10 @@
         <v>128</v>
       </c>
       <c r="M92" t="s" s="2">
+        <v>291</v>
+      </c>
+      <c r="N92" t="s" s="2">
         <v>292</v>
-      </c>
-      <c r="N92" t="s" s="2">
-        <v>293</v>
       </c>
       <c r="O92" t="s" s="2">
         <v>174</v>
@@ -12033,7 +12028,7 @@
         <v>78</v>
       </c>
       <c r="AG92" t="s" s="2">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="AH92" t="s" s="2">
         <v>76</v>
@@ -12050,13 +12045,13 @@
     </row>
     <row r="93">
       <c r="A93" t="s" s="2">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="C93" t="s" s="2">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="D93" s="2"/>
       <c r="E93" t="s" s="2">
@@ -12082,14 +12077,14 @@
         <v>184</v>
       </c>
       <c r="M93" t="s" s="2">
+        <v>518</v>
+      </c>
+      <c r="N93" t="s" s="2">
         <v>519</v>
-      </c>
-      <c r="N93" t="s" s="2">
-        <v>520</v>
       </c>
       <c r="O93" s="2"/>
       <c r="P93" t="s" s="2">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="Q93" t="s" s="2">
         <v>78</v>
@@ -12114,14 +12109,14 @@
         <v>78</v>
       </c>
       <c r="Y93" t="s" s="2">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="Z93" t="s" s="2">
+        <v>521</v>
+      </c>
+      <c r="AA93" t="s" s="2">
         <v>522</v>
       </c>
-      <c r="AA93" t="s" s="2">
-        <v>523</v>
-      </c>
       <c r="AB93" t="s" s="2">
         <v>78</v>
       </c>
@@ -12138,7 +12133,7 @@
         <v>78</v>
       </c>
       <c r="AG93" t="s" s="2">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="AH93" t="s" s="2">
         <v>76</v>
@@ -12155,13 +12150,13 @@
     </row>
     <row r="94">
       <c r="A94" t="s" s="2">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="C94" t="s" s="2">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="D94" s="2"/>
       <c r="E94" t="s" s="2">
@@ -12184,17 +12179,17 @@
         <v>78</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="M94" t="s" s="2">
+        <v>524</v>
+      </c>
+      <c r="N94" t="s" s="2">
         <v>525</v>
-      </c>
-      <c r="N94" t="s" s="2">
-        <v>526</v>
       </c>
       <c r="O94" s="2"/>
       <c r="P94" t="s" s="2">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="Q94" t="s" s="2">
         <v>78</v>
@@ -12243,7 +12238,7 @@
         <v>78</v>
       </c>
       <c r="AG94" t="s" s="2">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="AH94" t="s" s="2">
         <v>76</v>
@@ -12260,13 +12255,13 @@
     </row>
     <row r="95">
       <c r="A95" t="s" s="2">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="C95" t="s" s="2">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="D95" s="2"/>
       <c r="E95" t="s" s="2">
@@ -12289,19 +12284,19 @@
         <v>78</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="M95" t="s" s="2">
+        <v>528</v>
+      </c>
+      <c r="N95" t="s" s="2">
         <v>529</v>
       </c>
-      <c r="N95" t="s" s="2">
+      <c r="O95" t="s" s="2">
         <v>530</v>
       </c>
-      <c r="O95" t="s" s="2">
-        <v>531</v>
-      </c>
       <c r="P95" t="s" s="2">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="Q95" t="s" s="2">
         <v>78</v>
@@ -12350,7 +12345,7 @@
         <v>78</v>
       </c>
       <c r="AG95" t="s" s="2">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="AH95" t="s" s="2">
         <v>76</v>
@@ -12367,13 +12362,13 @@
     </row>
     <row r="96">
       <c r="A96" t="s" s="2">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="C96" t="s" s="2">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="D96" s="2"/>
       <c r="E96" t="s" s="2">
@@ -12396,17 +12391,17 @@
         <v>78</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="M96" t="s" s="2">
+        <v>532</v>
+      </c>
+      <c r="N96" t="s" s="2">
         <v>533</v>
-      </c>
-      <c r="N96" t="s" s="2">
-        <v>534</v>
       </c>
       <c r="O96" s="2"/>
       <c r="P96" t="s" s="2">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="Q96" t="s" s="2">
         <v>78</v>
@@ -12455,7 +12450,7 @@
         <v>78</v>
       </c>
       <c r="AG96" t="s" s="2">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="AH96" t="s" s="2">
         <v>76</v>
@@ -12472,13 +12467,13 @@
     </row>
     <row r="97">
       <c r="A97" t="s" s="2">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="C97" t="s" s="2">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="D97" s="2"/>
       <c r="E97" t="s" s="2">
@@ -12504,14 +12499,14 @@
         <v>105</v>
       </c>
       <c r="M97" t="s" s="2">
+        <v>536</v>
+      </c>
+      <c r="N97" t="s" s="2">
         <v>537</v>
-      </c>
-      <c r="N97" t="s" s="2">
-        <v>538</v>
       </c>
       <c r="O97" s="2"/>
       <c r="P97" t="s" s="2">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="Q97" t="s" s="2">
         <v>78</v>
@@ -12539,11 +12534,11 @@
         <v>188</v>
       </c>
       <c r="Z97" t="s" s="2">
+        <v>470</v>
+      </c>
+      <c r="AA97" t="s" s="2">
         <v>471</v>
       </c>
-      <c r="AA97" t="s" s="2">
-        <v>472</v>
-      </c>
       <c r="AB97" t="s" s="2">
         <v>78</v>
       </c>
@@ -12560,7 +12555,7 @@
         <v>78</v>
       </c>
       <c r="AG97" t="s" s="2">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="AH97" t="s" s="2">
         <v>76</v>
@@ -12577,13 +12572,13 @@
     </row>
     <row r="98">
       <c r="A98" t="s" s="2">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="C98" t="s" s="2">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="D98" s="2"/>
       <c r="E98" t="s" s="2">
@@ -12606,17 +12601,17 @@
         <v>78</v>
       </c>
       <c r="L98" t="s" s="2">
+        <v>540</v>
+      </c>
+      <c r="M98" t="s" s="2">
         <v>541</v>
       </c>
-      <c r="M98" t="s" s="2">
+      <c r="N98" t="s" s="2">
         <v>542</v>
-      </c>
-      <c r="N98" t="s" s="2">
-        <v>543</v>
       </c>
       <c r="O98" s="2"/>
       <c r="P98" t="s" s="2">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="Q98" t="s" s="2">
         <v>78</v>
@@ -12665,7 +12660,7 @@
         <v>78</v>
       </c>
       <c r="AG98" t="s" s="2">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="AH98" t="s" s="2">
         <v>76</v>
@@ -12674,7 +12669,7 @@
         <v>85</v>
       </c>
       <c r="AJ98" t="s" s="2">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="AK98" t="s" s="2">
         <v>97</v>
@@ -12682,13 +12677,13 @@
     </row>
     <row r="99">
       <c r="A99" t="s" s="2">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="C99" t="s" s="2">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="D99" s="2"/>
       <c r="E99" t="s" s="2">
@@ -12711,13 +12706,13 @@
         <v>78</v>
       </c>
       <c r="L99" t="s" s="2">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="M99" t="s" s="2">
+        <v>546</v>
+      </c>
+      <c r="N99" t="s" s="2">
         <v>547</v>
-      </c>
-      <c r="N99" t="s" s="2">
-        <v>548</v>
       </c>
       <c r="O99" s="2"/>
       <c r="P99" s="2"/>
@@ -12768,7 +12763,7 @@
         <v>78</v>
       </c>
       <c r="AG99" t="s" s="2">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="AH99" t="s" s="2">
         <v>76</v>
@@ -12785,13 +12780,13 @@
     </row>
     <row r="100">
       <c r="A100" t="s" s="2">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="C100" t="s" s="2">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="D100" s="2"/>
       <c r="E100" t="s" s="2">
@@ -12814,19 +12809,19 @@
         <v>78</v>
       </c>
       <c r="L100" t="s" s="2">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="M100" t="s" s="2">
+        <v>549</v>
+      </c>
+      <c r="N100" t="s" s="2">
         <v>550</v>
       </c>
-      <c r="N100" t="s" s="2">
+      <c r="O100" t="s" s="2">
         <v>551</v>
       </c>
-      <c r="O100" t="s" s="2">
+      <c r="P100" t="s" s="2">
         <v>552</v>
-      </c>
-      <c r="P100" t="s" s="2">
-        <v>553</v>
       </c>
       <c r="Q100" t="s" s="2">
         <v>78</v>
@@ -12875,7 +12870,7 @@
         <v>78</v>
       </c>
       <c r="AG100" t="s" s="2">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="AH100" t="s" s="2">
         <v>76</v>
@@ -12892,13 +12887,13 @@
     </row>
     <row r="101">
       <c r="A101" t="s" s="2">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="C101" t="s" s="2">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="D101" s="2"/>
       <c r="E101" t="s" s="2">
@@ -12921,7 +12916,7 @@
         <v>78</v>
       </c>
       <c r="L101" t="s" s="2">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="M101" t="s" s="2">
         <v>143</v>
@@ -12995,13 +12990,13 @@
     </row>
     <row r="102">
       <c r="A102" t="s" s="2">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="C102" t="s" s="2">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="D102" s="2"/>
       <c r="E102" t="s" s="2">
@@ -13027,10 +13022,10 @@
         <v>128</v>
       </c>
       <c r="M102" t="s" s="2">
+        <v>266</v>
+      </c>
+      <c r="N102" t="s" s="2">
         <v>267</v>
-      </c>
-      <c r="N102" t="s" s="2">
-        <v>268</v>
       </c>
       <c r="O102" t="s" s="2">
         <v>174</v>
@@ -13100,17 +13095,17 @@
     </row>
     <row r="103">
       <c r="A103" t="s" s="2">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="C103" t="s" s="2">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="D103" s="2"/>
       <c r="E103" t="s" s="2">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="F103" s="2"/>
       <c r="G103" t="s" s="2">
@@ -13132,10 +13127,10 @@
         <v>128</v>
       </c>
       <c r="M103" t="s" s="2">
+        <v>291</v>
+      </c>
+      <c r="N103" t="s" s="2">
         <v>292</v>
-      </c>
-      <c r="N103" t="s" s="2">
-        <v>293</v>
       </c>
       <c r="O103" t="s" s="2">
         <v>174</v>
@@ -13190,7 +13185,7 @@
         <v>78</v>
       </c>
       <c r="AG103" t="s" s="2">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="AH103" t="s" s="2">
         <v>76</v>
@@ -13207,13 +13202,13 @@
     </row>
     <row r="104">
       <c r="A104" t="s" s="2">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="C104" t="s" s="2">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="D104" s="2"/>
       <c r="E104" t="s" s="2">
@@ -13239,16 +13234,16 @@
         <v>184</v>
       </c>
       <c r="M104" t="s" s="2">
+        <v>557</v>
+      </c>
+      <c r="N104" t="s" s="2">
         <v>558</v>
       </c>
-      <c r="N104" t="s" s="2">
+      <c r="O104" t="s" s="2">
         <v>559</v>
       </c>
-      <c r="O104" t="s" s="2">
+      <c r="P104" t="s" s="2">
         <v>560</v>
-      </c>
-      <c r="P104" t="s" s="2">
-        <v>561</v>
       </c>
       <c r="Q104" t="s" s="2">
         <v>78</v>
@@ -13297,7 +13292,7 @@
         <v>78</v>
       </c>
       <c r="AG104" t="s" s="2">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="AH104" t="s" s="2">
         <v>85</v>
@@ -13314,13 +13309,13 @@
     </row>
     <row r="105">
       <c r="A105" t="s" s="2">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="C105" t="s" s="2">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="D105" s="2"/>
       <c r="E105" t="s" s="2">
@@ -13343,19 +13338,19 @@
         <v>78</v>
       </c>
       <c r="L105" t="s" s="2">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="M105" t="s" s="2">
+        <v>562</v>
+      </c>
+      <c r="N105" t="s" s="2">
         <v>563</v>
       </c>
-      <c r="N105" t="s" s="2">
+      <c r="O105" t="s" s="2">
         <v>564</v>
       </c>
-      <c r="O105" t="s" s="2">
+      <c r="P105" t="s" s="2">
         <v>565</v>
-      </c>
-      <c r="P105" t="s" s="2">
-        <v>566</v>
       </c>
       <c r="Q105" t="s" s="2">
         <v>78</v>
@@ -13404,7 +13399,7 @@
         <v>78</v>
       </c>
       <c r="AG105" t="s" s="2">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="AH105" t="s" s="2">
         <v>76</v>
@@ -13421,17 +13416,17 @@
     </row>
     <row r="106">
       <c r="A106" t="s" s="2">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="C106" t="s" s="2">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="D106" s="2"/>
       <c r="E106" t="s" s="2">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="F106" s="2"/>
       <c r="G106" t="s" s="2">
@@ -13450,16 +13445,16 @@
         <v>78</v>
       </c>
       <c r="L106" t="s" s="2">
+        <v>568</v>
+      </c>
+      <c r="M106" t="s" s="2">
         <v>569</v>
       </c>
-      <c r="M106" t="s" s="2">
+      <c r="N106" t="s" s="2">
         <v>570</v>
       </c>
-      <c r="N106" t="s" s="2">
+      <c r="O106" t="s" s="2">
         <v>571</v>
-      </c>
-      <c r="O106" t="s" s="2">
-        <v>572</v>
       </c>
       <c r="P106" s="2"/>
       <c r="Q106" t="s" s="2">
@@ -13509,7 +13504,7 @@
         <v>78</v>
       </c>
       <c r="AG106" t="s" s="2">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="AH106" t="s" s="2">
         <v>76</v>
@@ -13526,13 +13521,13 @@
     </row>
     <row r="107">
       <c r="A107" t="s" s="2">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="C107" t="s" s="2">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="D107" s="2"/>
       <c r="E107" t="s" s="2">
@@ -13555,19 +13550,19 @@
         <v>86</v>
       </c>
       <c r="L107" t="s" s="2">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="M107" t="s" s="2">
+        <v>573</v>
+      </c>
+      <c r="N107" t="s" s="2">
         <v>574</v>
       </c>
-      <c r="N107" t="s" s="2">
+      <c r="O107" t="s" s="2">
         <v>575</v>
       </c>
-      <c r="O107" t="s" s="2">
+      <c r="P107" t="s" s="2">
         <v>576</v>
-      </c>
-      <c r="P107" t="s" s="2">
-        <v>577</v>
       </c>
       <c r="Q107" t="s" s="2">
         <v>78</v>
@@ -13616,7 +13611,7 @@
         <v>78</v>
       </c>
       <c r="AG107" t="s" s="2">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="AH107" t="s" s="2">
         <v>76</v>
@@ -13633,13 +13628,13 @@
     </row>
     <row r="108">
       <c r="A108" t="s" s="2">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="C108" t="s" s="2">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="D108" s="2"/>
       <c r="E108" t="s" s="2">
@@ -13662,19 +13657,19 @@
         <v>86</v>
       </c>
       <c r="L108" t="s" s="2">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="M108" t="s" s="2">
+        <v>578</v>
+      </c>
+      <c r="N108" t="s" s="2">
         <v>579</v>
       </c>
-      <c r="N108" t="s" s="2">
+      <c r="O108" t="s" s="2">
         <v>580</v>
       </c>
-      <c r="O108" t="s" s="2">
+      <c r="P108" t="s" s="2">
         <v>581</v>
-      </c>
-      <c r="P108" t="s" s="2">
-        <v>582</v>
       </c>
       <c r="Q108" t="s" s="2">
         <v>78</v>
@@ -13723,7 +13718,7 @@
         <v>78</v>
       </c>
       <c r="AG108" t="s" s="2">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="AH108" t="s" s="2">
         <v>76</v>
@@ -13740,13 +13735,13 @@
     </row>
     <row r="109">
       <c r="A109" t="s" s="2">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="C109" t="s" s="2">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="D109" s="2"/>
       <c r="E109" t="s" s="2">
@@ -13769,7 +13764,7 @@
         <v>78</v>
       </c>
       <c r="L109" t="s" s="2">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="M109" t="s" s="2">
         <v>143</v>
@@ -13843,13 +13838,13 @@
     </row>
     <row r="110">
       <c r="A110" t="s" s="2">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="C110" t="s" s="2">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="D110" s="2"/>
       <c r="E110" t="s" s="2">
@@ -13875,10 +13870,10 @@
         <v>128</v>
       </c>
       <c r="M110" t="s" s="2">
+        <v>266</v>
+      </c>
+      <c r="N110" t="s" s="2">
         <v>267</v>
-      </c>
-      <c r="N110" t="s" s="2">
-        <v>268</v>
       </c>
       <c r="O110" t="s" s="2">
         <v>174</v>
@@ -13948,17 +13943,17 @@
     </row>
     <row r="111">
       <c r="A111" t="s" s="2">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="C111" t="s" s="2">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="D111" s="2"/>
       <c r="E111" t="s" s="2">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="F111" s="2"/>
       <c r="G111" t="s" s="2">
@@ -13980,10 +13975,10 @@
         <v>128</v>
       </c>
       <c r="M111" t="s" s="2">
+        <v>291</v>
+      </c>
+      <c r="N111" t="s" s="2">
         <v>292</v>
-      </c>
-      <c r="N111" t="s" s="2">
-        <v>293</v>
       </c>
       <c r="O111" t="s" s="2">
         <v>174</v>
@@ -14038,7 +14033,7 @@
         <v>78</v>
       </c>
       <c r="AG111" t="s" s="2">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="AH111" t="s" s="2">
         <v>76</v>
@@ -14055,13 +14050,13 @@
     </row>
     <row r="112">
       <c r="A112" t="s" s="2">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="C112" t="s" s="2">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="D112" s="2"/>
       <c r="E112" t="s" s="2">
@@ -14084,16 +14079,16 @@
         <v>86</v>
       </c>
       <c r="L112" t="s" s="2">
+        <v>586</v>
+      </c>
+      <c r="M112" t="s" s="2">
         <v>587</v>
       </c>
-      <c r="M112" t="s" s="2">
+      <c r="N112" t="s" s="2">
         <v>588</v>
       </c>
-      <c r="N112" t="s" s="2">
+      <c r="O112" t="s" s="2">
         <v>589</v>
-      </c>
-      <c r="O112" t="s" s="2">
-        <v>590</v>
       </c>
       <c r="P112" s="2"/>
       <c r="Q112" t="s" s="2">
@@ -14143,7 +14138,7 @@
         <v>78</v>
       </c>
       <c r="AG112" t="s" s="2">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="AH112" t="s" s="2">
         <v>85</v>
@@ -14160,13 +14155,13 @@
     </row>
     <row r="113">
       <c r="A113" t="s" s="2">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="C113" t="s" s="2">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="D113" s="2"/>
       <c r="E113" t="s" s="2">
@@ -14192,10 +14187,10 @@
         <v>105</v>
       </c>
       <c r="M113" t="s" s="2">
+        <v>591</v>
+      </c>
+      <c r="N113" t="s" s="2">
         <v>592</v>
-      </c>
-      <c r="N113" t="s" s="2">
-        <v>593</v>
       </c>
       <c r="O113" s="2"/>
       <c r="P113" s="2"/>
@@ -14225,11 +14220,11 @@
         <v>188</v>
       </c>
       <c r="Z113" t="s" s="2">
+        <v>592</v>
+      </c>
+      <c r="AA113" t="s" s="2">
         <v>593</v>
       </c>
-      <c r="AA113" t="s" s="2">
-        <v>594</v>
-      </c>
       <c r="AB113" t="s" s="2">
         <v>78</v>
       </c>
@@ -14246,7 +14241,7 @@
         <v>78</v>
       </c>
       <c r="AG113" t="s" s="2">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="AH113" t="s" s="2">
         <v>85</v>

--- a/currentbuild/all-profiles.xlsx
+++ b/currentbuild/all-profiles.xlsx
@@ -36,7 +36,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.1.1</t>
+    <t>0.1.2</t>
   </si>
   <si>
     <t>Name</t>
@@ -718,7 +718,7 @@
     <t>Merk: Det vil bli endringer i anbefaling til koding av legemidler og substanser (agens) når ny standard for identifisering av legemidler implementeres i Norge (IDMP).</t>
   </si>
   <si>
-    <t>http://hl7.no/fhir/ig/demo-at/ValueSet/allergener-7852</t>
+    <t>http://hl7.no/fhir/ig/demo-at/ValueSet/annen-allergi-som-kritisk-informasjon-7514</t>
   </si>
   <si>
     <t>AllergyIntolerance.patient</t>
@@ -2385,7 +2385,7 @@
     <col min="24" max="24" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="16.16796875" customWidth="true" bestFit="true"/>
     <col min="26" max="26" width="106.67578125" customWidth="true" bestFit="true"/>
-    <col min="27" max="27" width="50.62109375" customWidth="true" bestFit="true"/>
+    <col min="27" max="27" width="64.96484375" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="19.4765625" customWidth="true" bestFit="true"/>
     <col min="30" max="30" width="36.0390625" customWidth="true" bestFit="true"/>

--- a/currentbuild/all-profiles.xlsx
+++ b/currentbuild/all-profiles.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3841" uniqueCount="595">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3842" uniqueCount="598">
   <si>
     <t>Property</t>
   </si>
@@ -36,7 +36,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.1.2</t>
+    <t>0.1.3</t>
   </si>
   <si>
     <t>Name</t>
@@ -760,13 +760,22 @@
     <t>Estimated or actual date,  date-time, or age when allergy or intolerance was identified.</t>
   </si>
   <si>
+    <t>closed</t>
+  </si>
+  <si>
     <t>AllergyIntolerance.onset[x]:onsetDateTime</t>
   </si>
   <si>
     <t>onsetDateTime</t>
   </si>
   <si>
-    <t>Onset date</t>
+    <t>Starttidspunkt</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tidspunkt da overfølsomheten eller den uønskede reaksjonen ble konstatert. Tidspunkt kan være spesifikk (dag-tidspunkt) eller uspesifikk (årstall, tiår). </t>
+  </si>
+  <si>
+    <t>EHDS krever dato/tid, alder må konverteres.</t>
   </si>
   <si>
     <t>AllergyIntolerance.recordedDate</t>
@@ -775,7 +784,7 @@
     <t>Registreringsdato</t>
   </si>
   <si>
-    <t xml:space="preserve">Tidspunkt da overfølsomheten eller den uønskede reaksjonen ble konstatert. Tidspunkt kan være spesifikk (dag-tidspunkt) eller uspesifikk (årstall, tiår). </t>
+    <t>The recordedDate represents when this particular AllergyIntolerance record was created in the system, which is often a system-generated date.</t>
   </si>
   <si>
     <t>Obligatorisk i Kjernejournal</t>
@@ -2200,7 +2209,7 @@
         <v>2</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>332</v>
+        <v>335</v>
       </c>
     </row>
     <row r="24">
@@ -2208,7 +2217,7 @@
         <v>4</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>333</v>
+        <v>336</v>
       </c>
     </row>
     <row r="25">
@@ -2224,7 +2233,7 @@
         <v>8</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>334</v>
+        <v>337</v>
       </c>
     </row>
     <row r="27">
@@ -2232,7 +2241,7 @@
         <v>10</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>335</v>
+        <v>338</v>
       </c>
     </row>
     <row r="28">
@@ -2286,7 +2295,7 @@
         <v>24</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>336</v>
+        <v>339</v>
       </c>
     </row>
     <row r="35">
@@ -2322,7 +2331,7 @@
         <v>32</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>337</v>
+        <v>340</v>
       </c>
     </row>
     <row r="40">
@@ -2330,7 +2339,7 @@
         <v>34</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>338</v>
+        <v>341</v>
       </c>
     </row>
     <row r="41">
@@ -4203,7 +4212,7 @@
         <v>86</v>
       </c>
       <c r="I18" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="J18" t="s" s="2">
         <v>87</v>
@@ -4308,7 +4317,7 @@
         <v>86</v>
       </c>
       <c r="I19" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="J19" t="s" s="2">
         <v>87</v>
@@ -4728,7 +4737,7 @@
         <v>86</v>
       </c>
       <c r="I23" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="J23" t="s" s="2">
         <v>79</v>
@@ -5098,7 +5107,7 @@
         <v>79</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>133</v>
+        <v>237</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>234</v>
@@ -5121,13 +5130,13 @@
         <v>3</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="C27" t="s" s="2">
         <v>234</v>
       </c>
       <c r="D27" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="E27" t="s" s="2">
         <v>79</v>
@@ -5152,13 +5161,15 @@
         <v>169</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="N27" t="s" s="2">
-        <v>236</v>
+        <v>241</v>
       </c>
       <c r="O27" s="2"/>
-      <c r="P27" s="2"/>
+      <c r="P27" t="s" s="2">
+        <v>242</v>
+      </c>
       <c r="Q27" t="s" s="2">
         <v>79</v>
       </c>
@@ -5226,10 +5237,10 @@
         <v>3</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="C28" t="s" s="2">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="D28" s="2"/>
       <c r="E28" t="s" s="2">
@@ -5255,14 +5266,14 @@
         <v>169</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="Q28" t="s" s="2">
         <v>79</v>
@@ -5311,7 +5322,7 @@
         <v>79</v>
       </c>
       <c r="AG28" t="s" s="2">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="AH28" t="s" s="2">
         <v>77</v>
@@ -5331,14 +5342,14 @@
         <v>3</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="C29" t="s" s="2">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="D29" s="2"/>
       <c r="E29" t="s" s="2">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="F29" s="2"/>
       <c r="G29" t="s" s="2">
@@ -5357,13 +5368,13 @@
         <v>79</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="O29" s="2"/>
       <c r="P29" s="2"/>
@@ -5414,7 +5425,7 @@
         <v>79</v>
       </c>
       <c r="AG29" t="s" s="2">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="AH29" t="s" s="2">
         <v>77</v>
@@ -5434,14 +5445,14 @@
         <v>3</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="C30" t="s" s="2">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="D30" s="2"/>
       <c r="E30" t="s" s="2">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="F30" s="2"/>
       <c r="G30" t="s" s="2">
@@ -5460,16 +5471,16 @@
         <v>87</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="O30" t="s" s="2">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="P30" s="2"/>
       <c r="Q30" t="s" s="2">
@@ -5519,7 +5530,7 @@
         <v>79</v>
       </c>
       <c r="AG30" t="s" s="2">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="AH30" t="s" s="2">
         <v>77</v>
@@ -5539,10 +5550,10 @@
         <v>3</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="C31" t="s" s="2">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="D31" s="2"/>
       <c r="E31" t="s" s="2">
@@ -5568,13 +5579,13 @@
         <v>169</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="O31" t="s" s="2">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="P31" s="2"/>
       <c r="Q31" t="s" s="2">
@@ -5624,7 +5635,7 @@
         <v>79</v>
       </c>
       <c r="AG31" t="s" s="2">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="AH31" t="s" s="2">
         <v>77</v>
@@ -5644,10 +5655,10 @@
         <v>3</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="C32" t="s" s="2">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D32" s="2"/>
       <c r="E32" t="s" s="2">
@@ -5670,16 +5681,16 @@
         <v>79</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="O32" t="s" s="2">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="P32" s="2"/>
       <c r="Q32" t="s" s="2">
@@ -5729,7 +5740,7 @@
         <v>79</v>
       </c>
       <c r="AG32" t="s" s="2">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="AH32" t="s" s="2">
         <v>77</v>
@@ -5749,10 +5760,10 @@
         <v>3</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="C33" t="s" s="2">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="D33" s="2"/>
       <c r="E33" t="s" s="2">
@@ -5775,7 +5786,7 @@
         <v>79</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="M33" t="s" s="2">
         <v>144</v>
@@ -5852,10 +5863,10 @@
         <v>3</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="C34" t="s" s="2">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="D34" s="2"/>
       <c r="E34" t="s" s="2">
@@ -5881,10 +5892,10 @@
         <v>129</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="O34" t="s" s="2">
         <v>175</v>
@@ -5957,10 +5968,10 @@
         <v>3</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="C35" t="s" s="2">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="D35" s="2"/>
       <c r="E35" t="s" s="2">
@@ -5983,16 +5994,16 @@
         <v>87</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="O35" t="s" s="2">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="P35" s="2"/>
       <c r="Q35" t="s" s="2">
@@ -6042,7 +6053,7 @@
         <v>79</v>
       </c>
       <c r="AG35" t="s" s="2">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="AH35" t="s" s="2">
         <v>77</v>
@@ -6062,10 +6073,10 @@
         <v>3</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="C36" t="s" s="2">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="D36" s="2"/>
       <c r="E36" t="s" s="2">
@@ -6091,10 +6102,10 @@
         <v>169</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="N36" t="s" s="2">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="O36" s="2"/>
       <c r="P36" s="2"/>
@@ -6145,7 +6156,7 @@
         <v>79</v>
       </c>
       <c r="AG36" t="s" s="2">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="AH36" t="s" s="2">
         <v>77</v>
@@ -6165,10 +6176,10 @@
         <v>3</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="C37" t="s" s="2">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="D37" s="2"/>
       <c r="E37" t="s" s="2">
@@ -6191,13 +6202,13 @@
         <v>87</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="O37" s="2"/>
       <c r="P37" s="2"/>
@@ -6248,7 +6259,7 @@
         <v>79</v>
       </c>
       <c r="AG37" t="s" s="2">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="AH37" t="s" s="2">
         <v>86</v>
@@ -6268,10 +6279,10 @@
         <v>3</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="C38" t="s" s="2">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="D38" s="2"/>
       <c r="E38" t="s" s="2">
@@ -6294,13 +6305,13 @@
         <v>79</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="O38" s="2"/>
       <c r="P38" s="2"/>
@@ -6351,7 +6362,7 @@
         <v>79</v>
       </c>
       <c r="AG38" t="s" s="2">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="AH38" t="s" s="2">
         <v>77</v>
@@ -6371,10 +6382,10 @@
         <v>3</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="C39" t="s" s="2">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="D39" s="2"/>
       <c r="E39" t="s" s="2">
@@ -6397,7 +6408,7 @@
         <v>79</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="M39" t="s" s="2">
         <v>144</v>
@@ -6474,10 +6485,10 @@
         <v>3</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="C40" t="s" s="2">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="D40" s="2"/>
       <c r="E40" t="s" s="2">
@@ -6503,10 +6514,10 @@
         <v>129</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="O40" t="s" s="2">
         <v>175</v>
@@ -6579,14 +6590,14 @@
         <v>3</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="C41" t="s" s="2">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="D41" s="2"/>
       <c r="E41" t="s" s="2">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="F41" s="2"/>
       <c r="G41" t="s" s="2">
@@ -6608,10 +6619,10 @@
         <v>129</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="O41" t="s" s="2">
         <v>175</v>
@@ -6666,7 +6677,7 @@
         <v>79</v>
       </c>
       <c r="AG41" t="s" s="2">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="AH41" t="s" s="2">
         <v>77</v>
@@ -6686,10 +6697,10 @@
         <v>3</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="C42" t="s" s="2">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="D42" s="2"/>
       <c r="E42" t="s" s="2">
@@ -6715,13 +6726,13 @@
         <v>185</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="O42" t="s" s="2">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="P42" s="2"/>
       <c r="Q42" t="s" s="2">
@@ -6747,11 +6758,11 @@
         <v>79</v>
       </c>
       <c r="Y42" t="s" s="2">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="Z42" s="2"/>
       <c r="AA42" t="s" s="2">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="AB42" t="s" s="2">
         <v>79</v>
@@ -6769,7 +6780,7 @@
         <v>79</v>
       </c>
       <c r="AG42" t="s" s="2">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="AH42" t="s" s="2">
         <v>77</v>
@@ -6789,14 +6800,14 @@
         <v>3</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="C43" t="s" s="2">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="D43" s="2"/>
       <c r="E43" t="s" s="2">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="F43" s="2"/>
       <c r="G43" t="s" s="2">
@@ -6818,13 +6829,13 @@
         <v>185</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="O43" t="s" s="2">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="P43" s="2"/>
       <c r="Q43" t="s" s="2">
@@ -6853,10 +6864,10 @@
         <v>110</v>
       </c>
       <c r="Z43" t="s" s="2">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="AA43" t="s" s="2">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="AB43" t="s" s="2">
         <v>79</v>
@@ -6874,7 +6885,7 @@
         <v>79</v>
       </c>
       <c r="AG43" t="s" s="2">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="AH43" t="s" s="2">
         <v>86</v>
@@ -6894,14 +6905,14 @@
         <v>3</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="C44" t="s" s="2">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="D44" s="2"/>
       <c r="E44" t="s" s="2">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="F44" s="2"/>
       <c r="G44" t="s" s="2">
@@ -6920,16 +6931,16 @@
         <v>79</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c r="O44" t="s" s="2">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="P44" s="2"/>
       <c r="Q44" t="s" s="2">
@@ -6979,7 +6990,7 @@
         <v>79</v>
       </c>
       <c r="AG44" t="s" s="2">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="AH44" t="s" s="2">
         <v>77</v>
@@ -6999,10 +7010,10 @@
         <v>3</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="C45" t="s" s="2">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="D45" s="2"/>
       <c r="E45" t="s" s="2">
@@ -7028,10 +7039,10 @@
         <v>169</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="O45" s="2"/>
       <c r="P45" s="2"/>
@@ -7082,7 +7093,7 @@
         <v>79</v>
       </c>
       <c r="AG45" t="s" s="2">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="AH45" t="s" s="2">
         <v>77</v>
@@ -7102,10 +7113,10 @@
         <v>3</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="C46" t="s" s="2">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="D46" s="2"/>
       <c r="E46" t="s" s="2">
@@ -7131,13 +7142,13 @@
         <v>106</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="O46" t="s" s="2">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="P46" s="2"/>
       <c r="Q46" t="s" s="2">
@@ -7166,10 +7177,10 @@
         <v>189</v>
       </c>
       <c r="Z46" t="s" s="2">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="AA46" t="s" s="2">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="AB46" t="s" s="2">
         <v>79</v>
@@ -7187,7 +7198,7 @@
         <v>79</v>
       </c>
       <c r="AG46" t="s" s="2">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="AH46" t="s" s="2">
         <v>77</v>
@@ -7207,10 +7218,10 @@
         <v>3</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="C47" t="s" s="2">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="D47" s="2"/>
       <c r="E47" t="s" s="2">
@@ -7236,13 +7247,13 @@
         <v>185</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="O47" t="s" s="2">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="P47" s="2"/>
       <c r="Q47" t="s" s="2">
@@ -7268,13 +7279,13 @@
         <v>79</v>
       </c>
       <c r="Y47" t="s" s="2">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="Z47" t="s" s="2">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="AA47" t="s" s="2">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="AB47" t="s" s="2">
         <v>79</v>
@@ -7292,7 +7303,7 @@
         <v>79</v>
       </c>
       <c r="AG47" t="s" s="2">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="AH47" t="s" s="2">
         <v>77</v>
@@ -7312,10 +7323,10 @@
         <v>3</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="C48" t="s" s="2">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="D48" s="2"/>
       <c r="E48" t="s" s="2">
@@ -7338,16 +7349,16 @@
         <v>79</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="O48" t="s" s="2">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="P48" s="2"/>
       <c r="Q48" t="s" s="2">
@@ -7397,7 +7408,7 @@
         <v>79</v>
       </c>
       <c r="AG48" t="s" s="2">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="AH48" t="s" s="2">
         <v>77</v>
@@ -7414,17 +7425,17 @@
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="C49" t="s" s="2">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="D49" s="2"/>
       <c r="E49" t="s" s="2">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c r="F49" s="2"/>
       <c r="G49" t="s" s="2">
@@ -7446,10 +7457,10 @@
         <v>80</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="O49" s="2"/>
       <c r="P49" s="2"/>
@@ -7500,7 +7511,7 @@
         <v>79</v>
       </c>
       <c r="AG49" t="s" s="2">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="AH49" t="s" s="2">
         <v>77</v>
@@ -7512,18 +7523,18 @@
         <v>79</v>
       </c>
       <c r="AK49" t="s" s="2">
-        <v>342</v>
+        <v>345</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="C50" t="s" s="2">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="D50" s="2"/>
       <c r="E50" t="s" s="2">
@@ -7622,13 +7633,13 @@
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="C51" t="s" s="2">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="D51" s="2"/>
       <c r="E51" t="s" s="2">
@@ -7725,13 +7736,13 @@
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="C52" t="s" s="2">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="D52" s="2"/>
       <c r="E52" t="s" s="2">
@@ -7830,13 +7841,13 @@
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="C53" t="s" s="2">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="D53" s="2"/>
       <c r="E53" t="s" s="2">
@@ -7862,7 +7873,7 @@
         <v>106</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="N53" t="s" s="2">
         <v>108</v>
@@ -7935,13 +7946,13 @@
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="C54" t="s" s="2">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="D54" s="2"/>
       <c r="E54" t="s" s="2">
@@ -8040,13 +8051,13 @@
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="C55" t="s" s="2">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="D55" s="2"/>
       <c r="E55" t="s" s="2">
@@ -8145,13 +8156,13 @@
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="C56" t="s" s="2">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="D56" s="2"/>
       <c r="E56" t="s" s="2">
@@ -8246,16 +8257,16 @@
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="C57" t="s" s="2">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="D57" t="s" s="2">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c r="E57" t="s" s="2">
         <v>79</v>
@@ -8277,13 +8288,13 @@
         <v>79</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>354</v>
+        <v>357</v>
       </c>
       <c r="N57" t="s" s="2">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="O57" s="2"/>
       <c r="P57" s="2"/>
@@ -8351,13 +8362,13 @@
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="C58" t="s" s="2">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="D58" s="2"/>
       <c r="E58" t="s" s="2">
@@ -8454,13 +8465,13 @@
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="C59" t="s" s="2">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="D59" s="2"/>
       <c r="E59" t="s" s="2">
@@ -8557,13 +8568,13 @@
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="C60" t="s" s="2">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="D60" s="2"/>
       <c r="E60" t="s" s="2">
@@ -8603,7 +8614,7 @@
       </c>
       <c r="R60" s="2"/>
       <c r="S60" t="s" s="2">
-        <v>362</v>
+        <v>365</v>
       </c>
       <c r="T60" t="s" s="2">
         <v>79</v>
@@ -8662,13 +8673,13 @@
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="C61" t="s" s="2">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="D61" s="2"/>
       <c r="E61" t="s" s="2">
@@ -8691,7 +8702,7 @@
         <v>79</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="M61" t="s" s="2">
         <v>162</v>
@@ -8765,16 +8776,16 @@
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="C62" t="s" s="2">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="D62" t="s" s="2">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="E62" t="s" s="2">
         <v>79</v>
@@ -8796,13 +8807,13 @@
         <v>79</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>368</v>
+        <v>371</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="N62" t="s" s="2">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="O62" s="2"/>
       <c r="P62" s="2"/>
@@ -8870,16 +8881,16 @@
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c r="C63" t="s" s="2">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="D63" t="s" s="2">
-        <v>372</v>
+        <v>375</v>
       </c>
       <c r="E63" t="s" s="2">
         <v>79</v>
@@ -8901,16 +8912,16 @@
         <v>79</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="N63" t="s" s="2">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="O63" t="s" s="2">
-        <v>376</v>
+        <v>379</v>
       </c>
       <c r="P63" s="2"/>
       <c r="Q63" t="s" s="2">
@@ -8977,16 +8988,16 @@
     </row>
     <row r="64">
       <c r="A64" t="s" s="2">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>377</v>
+        <v>380</v>
       </c>
       <c r="C64" t="s" s="2">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="D64" t="s" s="2">
-        <v>378</v>
+        <v>381</v>
       </c>
       <c r="E64" t="s" s="2">
         <v>79</v>
@@ -9008,13 +9019,13 @@
         <v>79</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>379</v>
+        <v>382</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>380</v>
+        <v>383</v>
       </c>
       <c r="N64" t="s" s="2">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="O64" s="2"/>
       <c r="P64" s="2"/>
@@ -9082,16 +9093,16 @@
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="C65" t="s" s="2">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="D65" t="s" s="2">
-        <v>383</v>
+        <v>386</v>
       </c>
       <c r="E65" t="s" s="2">
         <v>79</v>
@@ -9113,13 +9124,13 @@
         <v>79</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="N65" t="s" s="2">
-        <v>386</v>
+        <v>389</v>
       </c>
       <c r="O65" s="2"/>
       <c r="P65" s="2"/>
@@ -9187,16 +9198,16 @@
     </row>
     <row r="66">
       <c r="A66" t="s" s="2">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="C66" t="s" s="2">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="D66" t="s" s="2">
-        <v>388</v>
+        <v>391</v>
       </c>
       <c r="E66" t="s" s="2">
         <v>79</v>
@@ -9218,13 +9229,13 @@
         <v>79</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>389</v>
+        <v>392</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>390</v>
+        <v>393</v>
       </c>
       <c r="N66" t="s" s="2">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="O66" s="2"/>
       <c r="P66" s="2"/>
@@ -9292,16 +9303,16 @@
     </row>
     <row r="67">
       <c r="A67" t="s" s="2">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>392</v>
+        <v>395</v>
       </c>
       <c r="C67" t="s" s="2">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="D67" t="s" s="2">
-        <v>393</v>
+        <v>396</v>
       </c>
       <c r="E67" t="s" s="2">
         <v>79</v>
@@ -9323,16 +9334,16 @@
         <v>79</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>394</v>
+        <v>397</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>395</v>
+        <v>398</v>
       </c>
       <c r="N67" t="s" s="2">
-        <v>396</v>
+        <v>399</v>
       </c>
       <c r="O67" t="s" s="2">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="P67" s="2"/>
       <c r="Q67" t="s" s="2">
@@ -9399,13 +9410,13 @@
     </row>
     <row r="68">
       <c r="A68" t="s" s="2">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>398</v>
+        <v>401</v>
       </c>
       <c r="C68" t="s" s="2">
-        <v>398</v>
+        <v>401</v>
       </c>
       <c r="D68" s="2"/>
       <c r="E68" t="s" s="2">
@@ -9506,13 +9517,13 @@
     </row>
     <row r="69">
       <c r="A69" t="s" s="2">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>399</v>
+        <v>402</v>
       </c>
       <c r="C69" t="s" s="2">
-        <v>399</v>
+        <v>402</v>
       </c>
       <c r="D69" s="2"/>
       <c r="E69" t="s" s="2">
@@ -9538,14 +9549,14 @@
         <v>179</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>400</v>
+        <v>403</v>
       </c>
       <c r="N69" t="s" s="2">
-        <v>401</v>
+        <v>404</v>
       </c>
       <c r="O69" s="2"/>
       <c r="P69" t="s" s="2">
-        <v>402</v>
+        <v>405</v>
       </c>
       <c r="Q69" t="s" s="2">
         <v>79</v>
@@ -9594,7 +9605,7 @@
         <v>79</v>
       </c>
       <c r="AG69" t="s" s="2">
-        <v>399</v>
+        <v>402</v>
       </c>
       <c r="AH69" t="s" s="2">
         <v>77</v>
@@ -9611,13 +9622,13 @@
     </row>
     <row r="70">
       <c r="A70" t="s" s="2">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>403</v>
+        <v>406</v>
       </c>
       <c r="C70" t="s" s="2">
-        <v>403</v>
+        <v>406</v>
       </c>
       <c r="D70" s="2"/>
       <c r="E70" t="s" s="2">
@@ -9640,70 +9651,70 @@
         <v>87</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>404</v>
+        <v>407</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>405</v>
+        <v>408</v>
       </c>
       <c r="N70" t="s" s="2">
+        <v>409</v>
+      </c>
+      <c r="O70" t="s" s="2">
+        <v>410</v>
+      </c>
+      <c r="P70" t="s" s="2">
+        <v>411</v>
+      </c>
+      <c r="Q70" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="R70" t="s" s="2">
+        <v>412</v>
+      </c>
+      <c r="S70" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="T70" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="U70" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="V70" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="W70" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="X70" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Y70" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Z70" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AA70" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB70" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC70" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD70" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE70" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF70" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AG70" t="s" s="2">
         <v>406</v>
-      </c>
-      <c r="O70" t="s" s="2">
-        <v>407</v>
-      </c>
-      <c r="P70" t="s" s="2">
-        <v>408</v>
-      </c>
-      <c r="Q70" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="R70" t="s" s="2">
-        <v>409</v>
-      </c>
-      <c r="S70" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="T70" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="U70" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="V70" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="W70" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="X70" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Y70" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Z70" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AA70" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB70" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC70" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD70" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE70" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF70" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AG70" t="s" s="2">
-        <v>403</v>
       </c>
       <c r="AH70" t="s" s="2">
         <v>77</v>
@@ -9720,13 +9731,13 @@
     </row>
     <row r="71">
       <c r="A71" t="s" s="2">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>410</v>
+        <v>413</v>
       </c>
       <c r="C71" t="s" s="2">
-        <v>410</v>
+        <v>413</v>
       </c>
       <c r="D71" s="2"/>
       <c r="E71" t="s" s="2">
@@ -9749,19 +9760,19 @@
         <v>87</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>411</v>
+        <v>414</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="N71" t="s" s="2">
-        <v>413</v>
+        <v>416</v>
       </c>
       <c r="O71" t="s" s="2">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="P71" t="s" s="2">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="Q71" t="s" s="2">
         <v>79</v>
@@ -9810,7 +9821,7 @@
         <v>79</v>
       </c>
       <c r="AG71" t="s" s="2">
-        <v>410</v>
+        <v>413</v>
       </c>
       <c r="AH71" t="s" s="2">
         <v>77</v>
@@ -9822,18 +9833,18 @@
         <v>79</v>
       </c>
       <c r="AK71" t="s" s="2">
-        <v>416</v>
+        <v>419</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="s" s="2">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>417</v>
+        <v>420</v>
       </c>
       <c r="C72" t="s" s="2">
-        <v>417</v>
+        <v>420</v>
       </c>
       <c r="D72" s="2"/>
       <c r="E72" t="s" s="2">
@@ -9856,7 +9867,7 @@
         <v>79</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="M72" t="s" s="2">
         <v>144</v>
@@ -9930,13 +9941,13 @@
     </row>
     <row r="73">
       <c r="A73" t="s" s="2">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>418</v>
+        <v>421</v>
       </c>
       <c r="C73" t="s" s="2">
-        <v>418</v>
+        <v>421</v>
       </c>
       <c r="D73" s="2"/>
       <c r="E73" t="s" s="2">
@@ -9962,10 +9973,10 @@
         <v>129</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="N73" t="s" s="2">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="O73" t="s" s="2">
         <v>175</v>
@@ -10035,13 +10046,13 @@
     </row>
     <row r="74">
       <c r="A74" t="s" s="2">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>419</v>
+        <v>422</v>
       </c>
       <c r="C74" t="s" s="2">
-        <v>419</v>
+        <v>422</v>
       </c>
       <c r="D74" s="2"/>
       <c r="E74" t="s" s="2">
@@ -10067,16 +10078,16 @@
         <v>106</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>420</v>
+        <v>423</v>
       </c>
       <c r="N74" t="s" s="2">
-        <v>421</v>
+        <v>424</v>
       </c>
       <c r="O74" t="s" s="2">
-        <v>422</v>
+        <v>425</v>
       </c>
       <c r="P74" t="s" s="2">
-        <v>423</v>
+        <v>426</v>
       </c>
       <c r="Q74" t="s" s="2">
         <v>79</v>
@@ -10104,10 +10115,10 @@
         <v>189</v>
       </c>
       <c r="Z74" t="s" s="2">
-        <v>424</v>
+        <v>427</v>
       </c>
       <c r="AA74" t="s" s="2">
-        <v>425</v>
+        <v>428</v>
       </c>
       <c r="AB74" t="s" s="2">
         <v>79</v>
@@ -10125,7 +10136,7 @@
         <v>79</v>
       </c>
       <c r="AG74" t="s" s="2">
-        <v>426</v>
+        <v>429</v>
       </c>
       <c r="AH74" t="s" s="2">
         <v>77</v>
@@ -10142,13 +10153,13 @@
     </row>
     <row r="75">
       <c r="A75" t="s" s="2">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>427</v>
+        <v>430</v>
       </c>
       <c r="C75" t="s" s="2">
-        <v>427</v>
+        <v>430</v>
       </c>
       <c r="D75" s="2"/>
       <c r="E75" t="s" s="2">
@@ -10171,19 +10182,19 @@
         <v>87</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>428</v>
+        <v>431</v>
       </c>
       <c r="N75" t="s" s="2">
-        <v>429</v>
+        <v>432</v>
       </c>
       <c r="O75" t="s" s="2">
-        <v>430</v>
+        <v>433</v>
       </c>
       <c r="P75" t="s" s="2">
-        <v>431</v>
+        <v>434</v>
       </c>
       <c r="Q75" t="s" s="2">
         <v>79</v>
@@ -10232,7 +10243,7 @@
         <v>79</v>
       </c>
       <c r="AG75" t="s" s="2">
-        <v>432</v>
+        <v>435</v>
       </c>
       <c r="AH75" t="s" s="2">
         <v>77</v>
@@ -10249,17 +10260,17 @@
     </row>
     <row r="76">
       <c r="A76" t="s" s="2">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>433</v>
+        <v>436</v>
       </c>
       <c r="C76" t="s" s="2">
-        <v>433</v>
+        <v>436</v>
       </c>
       <c r="D76" s="2"/>
       <c r="E76" t="s" s="2">
-        <v>434</v>
+        <v>437</v>
       </c>
       <c r="F76" s="2"/>
       <c r="G76" t="s" s="2">
@@ -10278,16 +10289,16 @@
         <v>87</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>435</v>
+        <v>438</v>
       </c>
       <c r="N76" t="s" s="2">
-        <v>436</v>
+        <v>439</v>
       </c>
       <c r="O76" t="s" s="2">
-        <v>437</v>
+        <v>440</v>
       </c>
       <c r="P76" s="2"/>
       <c r="Q76" t="s" s="2">
@@ -10301,7 +10312,7 @@
         <v>79</v>
       </c>
       <c r="U76" t="s" s="2">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="V76" t="s" s="2">
         <v>79</v>
@@ -10337,7 +10348,7 @@
         <v>79</v>
       </c>
       <c r="AG76" t="s" s="2">
-        <v>439</v>
+        <v>442</v>
       </c>
       <c r="AH76" t="s" s="2">
         <v>77</v>
@@ -10354,17 +10365,17 @@
     </row>
     <row r="77">
       <c r="A77" t="s" s="2">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>440</v>
+        <v>443</v>
       </c>
       <c r="C77" t="s" s="2">
-        <v>440</v>
+        <v>443</v>
       </c>
       <c r="D77" s="2"/>
       <c r="E77" t="s" s="2">
-        <v>441</v>
+        <v>444</v>
       </c>
       <c r="F77" s="2"/>
       <c r="G77" t="s" s="2">
@@ -10383,16 +10394,16 @@
         <v>87</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>442</v>
+        <v>445</v>
       </c>
       <c r="N77" t="s" s="2">
-        <v>443</v>
+        <v>446</v>
       </c>
       <c r="O77" t="s" s="2">
-        <v>444</v>
+        <v>447</v>
       </c>
       <c r="P77" s="2"/>
       <c r="Q77" t="s" s="2">
@@ -10442,7 +10453,7 @@
         <v>79</v>
       </c>
       <c r="AG77" t="s" s="2">
-        <v>445</v>
+        <v>448</v>
       </c>
       <c r="AH77" t="s" s="2">
         <v>77</v>
@@ -10459,13 +10470,13 @@
     </row>
     <row r="78">
       <c r="A78" t="s" s="2">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>446</v>
+        <v>449</v>
       </c>
       <c r="C78" t="s" s="2">
-        <v>446</v>
+        <v>449</v>
       </c>
       <c r="D78" s="2"/>
       <c r="E78" t="s" s="2">
@@ -10488,13 +10499,13 @@
         <v>87</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>447</v>
+        <v>450</v>
       </c>
       <c r="N78" t="s" s="2">
-        <v>448</v>
+        <v>451</v>
       </c>
       <c r="O78" s="2"/>
       <c r="P78" s="2"/>
@@ -10545,7 +10556,7 @@
         <v>79</v>
       </c>
       <c r="AG78" t="s" s="2">
-        <v>449</v>
+        <v>452</v>
       </c>
       <c r="AH78" t="s" s="2">
         <v>77</v>
@@ -10562,13 +10573,13 @@
     </row>
     <row r="79">
       <c r="A79" t="s" s="2">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>450</v>
+        <v>453</v>
       </c>
       <c r="C79" t="s" s="2">
-        <v>450</v>
+        <v>453</v>
       </c>
       <c r="D79" s="2"/>
       <c r="E79" t="s" s="2">
@@ -10591,13 +10602,13 @@
         <v>87</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>451</v>
+        <v>454</v>
       </c>
       <c r="N79" t="s" s="2">
-        <v>452</v>
+        <v>455</v>
       </c>
       <c r="O79" s="2"/>
       <c r="P79" s="2"/>
@@ -10648,7 +10659,7 @@
         <v>79</v>
       </c>
       <c r="AG79" t="s" s="2">
-        <v>453</v>
+        <v>456</v>
       </c>
       <c r="AH79" t="s" s="2">
         <v>77</v>
@@ -10665,13 +10676,13 @@
     </row>
     <row r="80">
       <c r="A80" t="s" s="2">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>454</v>
+        <v>457</v>
       </c>
       <c r="C80" t="s" s="2">
-        <v>454</v>
+        <v>457</v>
       </c>
       <c r="D80" s="2"/>
       <c r="E80" t="s" s="2">
@@ -10694,17 +10705,17 @@
         <v>87</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>456</v>
+        <v>459</v>
       </c>
       <c r="N80" t="s" s="2">
-        <v>457</v>
+        <v>460</v>
       </c>
       <c r="O80" s="2"/>
       <c r="P80" t="s" s="2">
-        <v>458</v>
+        <v>461</v>
       </c>
       <c r="Q80" t="s" s="2">
         <v>79</v>
@@ -10753,7 +10764,7 @@
         <v>79</v>
       </c>
       <c r="AG80" t="s" s="2">
-        <v>459</v>
+        <v>462</v>
       </c>
       <c r="AH80" t="s" s="2">
         <v>77</v>
@@ -10770,13 +10781,13 @@
     </row>
     <row r="81">
       <c r="A81" t="s" s="2">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>460</v>
+        <v>463</v>
       </c>
       <c r="C81" t="s" s="2">
-        <v>460</v>
+        <v>463</v>
       </c>
       <c r="D81" s="2"/>
       <c r="E81" t="s" s="2">
@@ -10799,19 +10810,19 @@
         <v>87</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>461</v>
+        <v>464</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>462</v>
+        <v>465</v>
       </c>
       <c r="N81" t="s" s="2">
-        <v>463</v>
+        <v>466</v>
       </c>
       <c r="O81" t="s" s="2">
-        <v>464</v>
+        <v>467</v>
       </c>
       <c r="P81" t="s" s="2">
-        <v>465</v>
+        <v>468</v>
       </c>
       <c r="Q81" t="s" s="2">
         <v>79</v>
@@ -10860,7 +10871,7 @@
         <v>79</v>
       </c>
       <c r="AG81" t="s" s="2">
-        <v>460</v>
+        <v>463</v>
       </c>
       <c r="AH81" t="s" s="2">
         <v>77</v>
@@ -10877,13 +10888,13 @@
     </row>
     <row r="82">
       <c r="A82" t="s" s="2">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>466</v>
+        <v>469</v>
       </c>
       <c r="C82" t="s" s="2">
-        <v>466</v>
+        <v>469</v>
       </c>
       <c r="D82" s="2"/>
       <c r="E82" t="s" s="2">
@@ -10909,16 +10920,16 @@
         <v>106</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>467</v>
+        <v>470</v>
       </c>
       <c r="N82" t="s" s="2">
-        <v>468</v>
+        <v>471</v>
       </c>
       <c r="O82" t="s" s="2">
-        <v>469</v>
+        <v>472</v>
       </c>
       <c r="P82" t="s" s="2">
-        <v>470</v>
+        <v>473</v>
       </c>
       <c r="Q82" t="s" s="2">
         <v>79</v>
@@ -10946,10 +10957,10 @@
         <v>189</v>
       </c>
       <c r="Z82" t="s" s="2">
-        <v>471</v>
+        <v>474</v>
       </c>
       <c r="AA82" t="s" s="2">
-        <v>472</v>
+        <v>475</v>
       </c>
       <c r="AB82" t="s" s="2">
         <v>79</v>
@@ -10967,7 +10978,7 @@
         <v>79</v>
       </c>
       <c r="AG82" t="s" s="2">
-        <v>466</v>
+        <v>469</v>
       </c>
       <c r="AH82" t="s" s="2">
         <v>77</v>
@@ -10984,13 +10995,13 @@
     </row>
     <row r="83">
       <c r="A83" t="s" s="2">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>473</v>
+        <v>476</v>
       </c>
       <c r="C83" t="s" s="2">
-        <v>473</v>
+        <v>476</v>
       </c>
       <c r="D83" s="2"/>
       <c r="E83" t="s" s="2">
@@ -11013,19 +11024,19 @@
         <v>87</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>474</v>
+        <v>477</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>475</v>
+        <v>478</v>
       </c>
       <c r="N83" t="s" s="2">
-        <v>476</v>
+        <v>479</v>
       </c>
       <c r="O83" t="s" s="2">
-        <v>477</v>
+        <v>480</v>
       </c>
       <c r="P83" t="s" s="2">
-        <v>478</v>
+        <v>481</v>
       </c>
       <c r="Q83" t="s" s="2">
         <v>79</v>
@@ -11074,7 +11085,7 @@
         <v>79</v>
       </c>
       <c r="AG83" t="s" s="2">
-        <v>473</v>
+        <v>476</v>
       </c>
       <c r="AH83" t="s" s="2">
         <v>77</v>
@@ -11091,13 +11102,13 @@
     </row>
     <row r="84">
       <c r="A84" t="s" s="2">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>479</v>
+        <v>482</v>
       </c>
       <c r="C84" t="s" s="2">
-        <v>479</v>
+        <v>482</v>
       </c>
       <c r="D84" s="2"/>
       <c r="E84" t="s" s="2">
@@ -11120,19 +11131,19 @@
         <v>87</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>480</v>
+        <v>483</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>481</v>
+        <v>484</v>
       </c>
       <c r="N84" t="s" s="2">
-        <v>482</v>
+        <v>485</v>
       </c>
       <c r="O84" t="s" s="2">
-        <v>483</v>
+        <v>486</v>
       </c>
       <c r="P84" t="s" s="2">
-        <v>484</v>
+        <v>487</v>
       </c>
       <c r="Q84" t="s" s="2">
         <v>79</v>
@@ -11181,7 +11192,7 @@
         <v>79</v>
       </c>
       <c r="AG84" t="s" s="2">
-        <v>479</v>
+        <v>482</v>
       </c>
       <c r="AH84" t="s" s="2">
         <v>77</v>
@@ -11198,13 +11209,13 @@
     </row>
     <row r="85">
       <c r="A85" t="s" s="2">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>485</v>
+        <v>488</v>
       </c>
       <c r="C85" t="s" s="2">
-        <v>485</v>
+        <v>488</v>
       </c>
       <c r="D85" s="2"/>
       <c r="E85" t="s" s="2">
@@ -11227,19 +11238,19 @@
         <v>87</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>486</v>
+        <v>489</v>
       </c>
       <c r="N85" t="s" s="2">
-        <v>487</v>
+        <v>490</v>
       </c>
       <c r="O85" t="s" s="2">
-        <v>488</v>
+        <v>491</v>
       </c>
       <c r="P85" t="s" s="2">
-        <v>489</v>
+        <v>492</v>
       </c>
       <c r="Q85" t="s" s="2">
         <v>79</v>
@@ -11288,7 +11299,7 @@
         <v>79</v>
       </c>
       <c r="AG85" t="s" s="2">
-        <v>485</v>
+        <v>488</v>
       </c>
       <c r="AH85" t="s" s="2">
         <v>77</v>
@@ -11305,13 +11316,13 @@
     </row>
     <row r="86">
       <c r="A86" t="s" s="2">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>490</v>
+        <v>493</v>
       </c>
       <c r="C86" t="s" s="2">
-        <v>490</v>
+        <v>493</v>
       </c>
       <c r="D86" s="2"/>
       <c r="E86" t="s" s="2">
@@ -11337,14 +11348,14 @@
         <v>185</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>491</v>
+        <v>494</v>
       </c>
       <c r="N86" t="s" s="2">
-        <v>492</v>
+        <v>495</v>
       </c>
       <c r="O86" s="2"/>
       <c r="P86" t="s" s="2">
-        <v>493</v>
+        <v>496</v>
       </c>
       <c r="Q86" t="s" s="2">
         <v>79</v>
@@ -11369,13 +11380,13 @@
         <v>79</v>
       </c>
       <c r="Y86" t="s" s="2">
-        <v>494</v>
+        <v>497</v>
       </c>
       <c r="Z86" t="s" s="2">
-        <v>495</v>
+        <v>498</v>
       </c>
       <c r="AA86" t="s" s="2">
-        <v>496</v>
+        <v>499</v>
       </c>
       <c r="AB86" t="s" s="2">
         <v>79</v>
@@ -11393,7 +11404,7 @@
         <v>79</v>
       </c>
       <c r="AG86" t="s" s="2">
-        <v>490</v>
+        <v>493</v>
       </c>
       <c r="AH86" t="s" s="2">
         <v>77</v>
@@ -11410,13 +11421,13 @@
     </row>
     <row r="87">
       <c r="A87" t="s" s="2">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>497</v>
+        <v>500</v>
       </c>
       <c r="C87" t="s" s="2">
-        <v>497</v>
+        <v>500</v>
       </c>
       <c r="D87" s="2"/>
       <c r="E87" t="s" s="2">
@@ -11439,19 +11450,19 @@
         <v>79</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>498</v>
+        <v>501</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>499</v>
+        <v>502</v>
       </c>
       <c r="N87" t="s" s="2">
-        <v>500</v>
+        <v>503</v>
       </c>
       <c r="O87" t="s" s="2">
-        <v>501</v>
+        <v>504</v>
       </c>
       <c r="P87" t="s" s="2">
-        <v>502</v>
+        <v>505</v>
       </c>
       <c r="Q87" t="s" s="2">
         <v>79</v>
@@ -11500,7 +11511,7 @@
         <v>79</v>
       </c>
       <c r="AG87" t="s" s="2">
-        <v>497</v>
+        <v>500</v>
       </c>
       <c r="AH87" t="s" s="2">
         <v>77</v>
@@ -11517,13 +11528,13 @@
     </row>
     <row r="88">
       <c r="A88" t="s" s="2">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>503</v>
+        <v>506</v>
       </c>
       <c r="C88" t="s" s="2">
-        <v>503</v>
+        <v>506</v>
       </c>
       <c r="D88" s="2"/>
       <c r="E88" t="s" s="2">
@@ -11546,19 +11557,19 @@
         <v>79</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>504</v>
+        <v>507</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>505</v>
+        <v>508</v>
       </c>
       <c r="N88" t="s" s="2">
-        <v>506</v>
+        <v>509</v>
       </c>
       <c r="O88" t="s" s="2">
-        <v>507</v>
+        <v>510</v>
       </c>
       <c r="P88" t="s" s="2">
-        <v>508</v>
+        <v>511</v>
       </c>
       <c r="Q88" t="s" s="2">
         <v>79</v>
@@ -11607,7 +11618,7 @@
         <v>79</v>
       </c>
       <c r="AG88" t="s" s="2">
-        <v>503</v>
+        <v>506</v>
       </c>
       <c r="AH88" t="s" s="2">
         <v>77</v>
@@ -11624,13 +11635,13 @@
     </row>
     <row r="89">
       <c r="A89" t="s" s="2">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>509</v>
+        <v>512</v>
       </c>
       <c r="C89" t="s" s="2">
-        <v>509</v>
+        <v>512</v>
       </c>
       <c r="D89" s="2"/>
       <c r="E89" t="s" s="2">
@@ -11653,19 +11664,19 @@
         <v>79</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>510</v>
+        <v>513</v>
       </c>
       <c r="N89" t="s" s="2">
-        <v>511</v>
+        <v>514</v>
       </c>
       <c r="O89" t="s" s="2">
-        <v>512</v>
+        <v>515</v>
       </c>
       <c r="P89" t="s" s="2">
-        <v>513</v>
+        <v>516</v>
       </c>
       <c r="Q89" t="s" s="2">
         <v>79</v>
@@ -11714,7 +11725,7 @@
         <v>79</v>
       </c>
       <c r="AG89" t="s" s="2">
-        <v>509</v>
+        <v>512</v>
       </c>
       <c r="AH89" t="s" s="2">
         <v>77</v>
@@ -11726,18 +11737,18 @@
         <v>79</v>
       </c>
       <c r="AK89" t="s" s="2">
-        <v>514</v>
+        <v>517</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="s" s="2">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>515</v>
+        <v>518</v>
       </c>
       <c r="C90" t="s" s="2">
-        <v>515</v>
+        <v>518</v>
       </c>
       <c r="D90" s="2"/>
       <c r="E90" t="s" s="2">
@@ -11760,7 +11771,7 @@
         <v>79</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="M90" t="s" s="2">
         <v>144</v>
@@ -11834,13 +11845,13 @@
     </row>
     <row r="91">
       <c r="A91" t="s" s="2">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>516</v>
+        <v>519</v>
       </c>
       <c r="C91" t="s" s="2">
-        <v>516</v>
+        <v>519</v>
       </c>
       <c r="D91" s="2"/>
       <c r="E91" t="s" s="2">
@@ -11866,10 +11877,10 @@
         <v>129</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="N91" t="s" s="2">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="O91" t="s" s="2">
         <v>175</v>
@@ -11939,17 +11950,17 @@
     </row>
     <row r="92">
       <c r="A92" t="s" s="2">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>517</v>
+        <v>520</v>
       </c>
       <c r="C92" t="s" s="2">
-        <v>517</v>
+        <v>520</v>
       </c>
       <c r="D92" s="2"/>
       <c r="E92" t="s" s="2">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="F92" s="2"/>
       <c r="G92" t="s" s="2">
@@ -11971,10 +11982,10 @@
         <v>129</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="N92" t="s" s="2">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="O92" t="s" s="2">
         <v>175</v>
@@ -12029,7 +12040,7 @@
         <v>79</v>
       </c>
       <c r="AG92" t="s" s="2">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="AH92" t="s" s="2">
         <v>77</v>
@@ -12046,13 +12057,13 @@
     </row>
     <row r="93">
       <c r="A93" t="s" s="2">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>518</v>
+        <v>521</v>
       </c>
       <c r="C93" t="s" s="2">
-        <v>518</v>
+        <v>521</v>
       </c>
       <c r="D93" s="2"/>
       <c r="E93" t="s" s="2">
@@ -12078,14 +12089,14 @@
         <v>185</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>519</v>
+        <v>522</v>
       </c>
       <c r="N93" t="s" s="2">
-        <v>520</v>
+        <v>523</v>
       </c>
       <c r="O93" s="2"/>
       <c r="P93" t="s" s="2">
-        <v>521</v>
+        <v>524</v>
       </c>
       <c r="Q93" t="s" s="2">
         <v>79</v>
@@ -12110,13 +12121,13 @@
         <v>79</v>
       </c>
       <c r="Y93" t="s" s="2">
-        <v>494</v>
+        <v>497</v>
       </c>
       <c r="Z93" t="s" s="2">
-        <v>522</v>
+        <v>525</v>
       </c>
       <c r="AA93" t="s" s="2">
-        <v>523</v>
+        <v>526</v>
       </c>
       <c r="AB93" t="s" s="2">
         <v>79</v>
@@ -12134,7 +12145,7 @@
         <v>79</v>
       </c>
       <c r="AG93" t="s" s="2">
-        <v>518</v>
+        <v>521</v>
       </c>
       <c r="AH93" t="s" s="2">
         <v>77</v>
@@ -12151,13 +12162,13 @@
     </row>
     <row r="94">
       <c r="A94" t="s" s="2">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>524</v>
+        <v>527</v>
       </c>
       <c r="C94" t="s" s="2">
-        <v>524</v>
+        <v>527</v>
       </c>
       <c r="D94" s="2"/>
       <c r="E94" t="s" s="2">
@@ -12180,17 +12191,17 @@
         <v>79</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>411</v>
+        <v>414</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>525</v>
+        <v>528</v>
       </c>
       <c r="N94" t="s" s="2">
-        <v>526</v>
+        <v>529</v>
       </c>
       <c r="O94" s="2"/>
       <c r="P94" t="s" s="2">
-        <v>527</v>
+        <v>530</v>
       </c>
       <c r="Q94" t="s" s="2">
         <v>79</v>
@@ -12239,7 +12250,7 @@
         <v>79</v>
       </c>
       <c r="AG94" t="s" s="2">
-        <v>524</v>
+        <v>527</v>
       </c>
       <c r="AH94" t="s" s="2">
         <v>77</v>
@@ -12256,13 +12267,13 @@
     </row>
     <row r="95">
       <c r="A95" t="s" s="2">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>528</v>
+        <v>531</v>
       </c>
       <c r="C95" t="s" s="2">
-        <v>528</v>
+        <v>531</v>
       </c>
       <c r="D95" s="2"/>
       <c r="E95" t="s" s="2">
@@ -12285,19 +12296,19 @@
         <v>79</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>461</v>
+        <v>464</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>529</v>
+        <v>532</v>
       </c>
       <c r="N95" t="s" s="2">
-        <v>530</v>
+        <v>533</v>
       </c>
       <c r="O95" t="s" s="2">
-        <v>531</v>
+        <v>534</v>
       </c>
       <c r="P95" t="s" s="2">
-        <v>465</v>
+        <v>468</v>
       </c>
       <c r="Q95" t="s" s="2">
         <v>79</v>
@@ -12346,7 +12357,7 @@
         <v>79</v>
       </c>
       <c r="AG95" t="s" s="2">
-        <v>528</v>
+        <v>531</v>
       </c>
       <c r="AH95" t="s" s="2">
         <v>77</v>
@@ -12363,13 +12374,13 @@
     </row>
     <row r="96">
       <c r="A96" t="s" s="2">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>532</v>
+        <v>535</v>
       </c>
       <c r="C96" t="s" s="2">
-        <v>532</v>
+        <v>535</v>
       </c>
       <c r="D96" s="2"/>
       <c r="E96" t="s" s="2">
@@ -12392,17 +12403,17 @@
         <v>79</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>533</v>
+        <v>536</v>
       </c>
       <c r="N96" t="s" s="2">
-        <v>534</v>
+        <v>537</v>
       </c>
       <c r="O96" s="2"/>
       <c r="P96" t="s" s="2">
-        <v>535</v>
+        <v>538</v>
       </c>
       <c r="Q96" t="s" s="2">
         <v>79</v>
@@ -12451,7 +12462,7 @@
         <v>79</v>
       </c>
       <c r="AG96" t="s" s="2">
-        <v>532</v>
+        <v>535</v>
       </c>
       <c r="AH96" t="s" s="2">
         <v>77</v>
@@ -12468,13 +12479,13 @@
     </row>
     <row r="97">
       <c r="A97" t="s" s="2">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>536</v>
+        <v>539</v>
       </c>
       <c r="C97" t="s" s="2">
-        <v>536</v>
+        <v>539</v>
       </c>
       <c r="D97" s="2"/>
       <c r="E97" t="s" s="2">
@@ -12500,14 +12511,14 @@
         <v>106</v>
       </c>
       <c r="M97" t="s" s="2">
-        <v>537</v>
+        <v>540</v>
       </c>
       <c r="N97" t="s" s="2">
-        <v>538</v>
+        <v>541</v>
       </c>
       <c r="O97" s="2"/>
       <c r="P97" t="s" s="2">
-        <v>539</v>
+        <v>542</v>
       </c>
       <c r="Q97" t="s" s="2">
         <v>79</v>
@@ -12535,10 +12546,10 @@
         <v>189</v>
       </c>
       <c r="Z97" t="s" s="2">
-        <v>471</v>
+        <v>474</v>
       </c>
       <c r="AA97" t="s" s="2">
-        <v>472</v>
+        <v>475</v>
       </c>
       <c r="AB97" t="s" s="2">
         <v>79</v>
@@ -12556,7 +12567,7 @@
         <v>79</v>
       </c>
       <c r="AG97" t="s" s="2">
-        <v>536</v>
+        <v>539</v>
       </c>
       <c r="AH97" t="s" s="2">
         <v>77</v>
@@ -12573,13 +12584,13 @@
     </row>
     <row r="98">
       <c r="A98" t="s" s="2">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>540</v>
+        <v>543</v>
       </c>
       <c r="C98" t="s" s="2">
-        <v>540</v>
+        <v>543</v>
       </c>
       <c r="D98" s="2"/>
       <c r="E98" t="s" s="2">
@@ -12602,17 +12613,17 @@
         <v>79</v>
       </c>
       <c r="L98" t="s" s="2">
-        <v>541</v>
+        <v>544</v>
       </c>
       <c r="M98" t="s" s="2">
-        <v>542</v>
+        <v>545</v>
       </c>
       <c r="N98" t="s" s="2">
-        <v>543</v>
+        <v>546</v>
       </c>
       <c r="O98" s="2"/>
       <c r="P98" t="s" s="2">
-        <v>544</v>
+        <v>547</v>
       </c>
       <c r="Q98" t="s" s="2">
         <v>79</v>
@@ -12661,7 +12672,7 @@
         <v>79</v>
       </c>
       <c r="AG98" t="s" s="2">
-        <v>540</v>
+        <v>543</v>
       </c>
       <c r="AH98" t="s" s="2">
         <v>77</v>
@@ -12670,7 +12681,7 @@
         <v>86</v>
       </c>
       <c r="AJ98" t="s" s="2">
-        <v>545</v>
+        <v>548</v>
       </c>
       <c r="AK98" t="s" s="2">
         <v>98</v>
@@ -12678,13 +12689,13 @@
     </row>
     <row r="99">
       <c r="A99" t="s" s="2">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>546</v>
+        <v>549</v>
       </c>
       <c r="C99" t="s" s="2">
-        <v>546</v>
+        <v>549</v>
       </c>
       <c r="D99" s="2"/>
       <c r="E99" t="s" s="2">
@@ -12707,13 +12718,13 @@
         <v>79</v>
       </c>
       <c r="L99" t="s" s="2">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c r="M99" t="s" s="2">
-        <v>547</v>
+        <v>550</v>
       </c>
       <c r="N99" t="s" s="2">
-        <v>548</v>
+        <v>551</v>
       </c>
       <c r="O99" s="2"/>
       <c r="P99" s="2"/>
@@ -12764,7 +12775,7 @@
         <v>79</v>
       </c>
       <c r="AG99" t="s" s="2">
-        <v>546</v>
+        <v>549</v>
       </c>
       <c r="AH99" t="s" s="2">
         <v>77</v>
@@ -12781,13 +12792,13 @@
     </row>
     <row r="100">
       <c r="A100" t="s" s="2">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>549</v>
+        <v>552</v>
       </c>
       <c r="C100" t="s" s="2">
-        <v>549</v>
+        <v>552</v>
       </c>
       <c r="D100" s="2"/>
       <c r="E100" t="s" s="2">
@@ -12810,19 +12821,19 @@
         <v>79</v>
       </c>
       <c r="L100" t="s" s="2">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="M100" t="s" s="2">
-        <v>550</v>
+        <v>553</v>
       </c>
       <c r="N100" t="s" s="2">
-        <v>551</v>
+        <v>554</v>
       </c>
       <c r="O100" t="s" s="2">
-        <v>552</v>
+        <v>555</v>
       </c>
       <c r="P100" t="s" s="2">
-        <v>553</v>
+        <v>556</v>
       </c>
       <c r="Q100" t="s" s="2">
         <v>79</v>
@@ -12871,7 +12882,7 @@
         <v>79</v>
       </c>
       <c r="AG100" t="s" s="2">
-        <v>549</v>
+        <v>552</v>
       </c>
       <c r="AH100" t="s" s="2">
         <v>77</v>
@@ -12888,13 +12899,13 @@
     </row>
     <row r="101">
       <c r="A101" t="s" s="2">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>554</v>
+        <v>557</v>
       </c>
       <c r="C101" t="s" s="2">
-        <v>554</v>
+        <v>557</v>
       </c>
       <c r="D101" s="2"/>
       <c r="E101" t="s" s="2">
@@ -12917,7 +12928,7 @@
         <v>79</v>
       </c>
       <c r="L101" t="s" s="2">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="M101" t="s" s="2">
         <v>144</v>
@@ -12991,13 +13002,13 @@
     </row>
     <row r="102">
       <c r="A102" t="s" s="2">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>555</v>
+        <v>558</v>
       </c>
       <c r="C102" t="s" s="2">
-        <v>555</v>
+        <v>558</v>
       </c>
       <c r="D102" s="2"/>
       <c r="E102" t="s" s="2">
@@ -13023,10 +13034,10 @@
         <v>129</v>
       </c>
       <c r="M102" t="s" s="2">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="N102" t="s" s="2">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="O102" t="s" s="2">
         <v>175</v>
@@ -13096,17 +13107,17 @@
     </row>
     <row r="103">
       <c r="A103" t="s" s="2">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>556</v>
+        <v>559</v>
       </c>
       <c r="C103" t="s" s="2">
-        <v>556</v>
+        <v>559</v>
       </c>
       <c r="D103" s="2"/>
       <c r="E103" t="s" s="2">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="F103" s="2"/>
       <c r="G103" t="s" s="2">
@@ -13128,10 +13139,10 @@
         <v>129</v>
       </c>
       <c r="M103" t="s" s="2">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="N103" t="s" s="2">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="O103" t="s" s="2">
         <v>175</v>
@@ -13186,7 +13197,7 @@
         <v>79</v>
       </c>
       <c r="AG103" t="s" s="2">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="AH103" t="s" s="2">
         <v>77</v>
@@ -13203,13 +13214,13 @@
     </row>
     <row r="104">
       <c r="A104" t="s" s="2">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>557</v>
+        <v>560</v>
       </c>
       <c r="C104" t="s" s="2">
-        <v>557</v>
+        <v>560</v>
       </c>
       <c r="D104" s="2"/>
       <c r="E104" t="s" s="2">
@@ -13235,16 +13246,16 @@
         <v>185</v>
       </c>
       <c r="M104" t="s" s="2">
-        <v>558</v>
+        <v>561</v>
       </c>
       <c r="N104" t="s" s="2">
-        <v>559</v>
+        <v>562</v>
       </c>
       <c r="O104" t="s" s="2">
-        <v>560</v>
+        <v>563</v>
       </c>
       <c r="P104" t="s" s="2">
-        <v>561</v>
+        <v>564</v>
       </c>
       <c r="Q104" t="s" s="2">
         <v>79</v>
@@ -13293,7 +13304,7 @@
         <v>79</v>
       </c>
       <c r="AG104" t="s" s="2">
-        <v>557</v>
+        <v>560</v>
       </c>
       <c r="AH104" t="s" s="2">
         <v>86</v>
@@ -13310,13 +13321,13 @@
     </row>
     <row r="105">
       <c r="A105" t="s" s="2">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>562</v>
+        <v>565</v>
       </c>
       <c r="C105" t="s" s="2">
-        <v>562</v>
+        <v>565</v>
       </c>
       <c r="D105" s="2"/>
       <c r="E105" t="s" s="2">
@@ -13339,19 +13350,19 @@
         <v>79</v>
       </c>
       <c r="L105" t="s" s="2">
-        <v>404</v>
+        <v>407</v>
       </c>
       <c r="M105" t="s" s="2">
-        <v>563</v>
+        <v>566</v>
       </c>
       <c r="N105" t="s" s="2">
-        <v>564</v>
+        <v>567</v>
       </c>
       <c r="O105" t="s" s="2">
-        <v>565</v>
+        <v>568</v>
       </c>
       <c r="P105" t="s" s="2">
-        <v>566</v>
+        <v>569</v>
       </c>
       <c r="Q105" t="s" s="2">
         <v>79</v>
@@ -13400,7 +13411,7 @@
         <v>79</v>
       </c>
       <c r="AG105" t="s" s="2">
-        <v>562</v>
+        <v>565</v>
       </c>
       <c r="AH105" t="s" s="2">
         <v>77</v>
@@ -13417,17 +13428,17 @@
     </row>
     <row r="106">
       <c r="A106" t="s" s="2">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>567</v>
+        <v>570</v>
       </c>
       <c r="C106" t="s" s="2">
-        <v>567</v>
+        <v>570</v>
       </c>
       <c r="D106" s="2"/>
       <c r="E106" t="s" s="2">
-        <v>568</v>
+        <v>571</v>
       </c>
       <c r="F106" s="2"/>
       <c r="G106" t="s" s="2">
@@ -13446,16 +13457,16 @@
         <v>79</v>
       </c>
       <c r="L106" t="s" s="2">
-        <v>569</v>
+        <v>572</v>
       </c>
       <c r="M106" t="s" s="2">
-        <v>570</v>
+        <v>573</v>
       </c>
       <c r="N106" t="s" s="2">
-        <v>571</v>
+        <v>574</v>
       </c>
       <c r="O106" t="s" s="2">
-        <v>572</v>
+        <v>575</v>
       </c>
       <c r="P106" s="2"/>
       <c r="Q106" t="s" s="2">
@@ -13505,7 +13516,7 @@
         <v>79</v>
       </c>
       <c r="AG106" t="s" s="2">
-        <v>567</v>
+        <v>570</v>
       </c>
       <c r="AH106" t="s" s="2">
         <v>77</v>
@@ -13522,13 +13533,13 @@
     </row>
     <row r="107">
       <c r="A107" t="s" s="2">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>573</v>
+        <v>576</v>
       </c>
       <c r="C107" t="s" s="2">
-        <v>573</v>
+        <v>576</v>
       </c>
       <c r="D107" s="2"/>
       <c r="E107" t="s" s="2">
@@ -13551,19 +13562,19 @@
         <v>87</v>
       </c>
       <c r="L107" t="s" s="2">
-        <v>541</v>
+        <v>544</v>
       </c>
       <c r="M107" t="s" s="2">
-        <v>574</v>
+        <v>577</v>
       </c>
       <c r="N107" t="s" s="2">
-        <v>575</v>
+        <v>578</v>
       </c>
       <c r="O107" t="s" s="2">
-        <v>576</v>
+        <v>579</v>
       </c>
       <c r="P107" t="s" s="2">
-        <v>577</v>
+        <v>580</v>
       </c>
       <c r="Q107" t="s" s="2">
         <v>79</v>
@@ -13612,7 +13623,7 @@
         <v>79</v>
       </c>
       <c r="AG107" t="s" s="2">
-        <v>573</v>
+        <v>576</v>
       </c>
       <c r="AH107" t="s" s="2">
         <v>77</v>
@@ -13629,13 +13640,13 @@
     </row>
     <row r="108">
       <c r="A108" t="s" s="2">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>578</v>
+        <v>581</v>
       </c>
       <c r="C108" t="s" s="2">
-        <v>578</v>
+        <v>581</v>
       </c>
       <c r="D108" s="2"/>
       <c r="E108" t="s" s="2">
@@ -13658,19 +13669,19 @@
         <v>87</v>
       </c>
       <c r="L108" t="s" s="2">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="M108" t="s" s="2">
-        <v>579</v>
+        <v>582</v>
       </c>
       <c r="N108" t="s" s="2">
-        <v>580</v>
+        <v>583</v>
       </c>
       <c r="O108" t="s" s="2">
-        <v>581</v>
+        <v>584</v>
       </c>
       <c r="P108" t="s" s="2">
-        <v>582</v>
+        <v>585</v>
       </c>
       <c r="Q108" t="s" s="2">
         <v>79</v>
@@ -13719,7 +13730,7 @@
         <v>79</v>
       </c>
       <c r="AG108" t="s" s="2">
-        <v>578</v>
+        <v>581</v>
       </c>
       <c r="AH108" t="s" s="2">
         <v>77</v>
@@ -13736,13 +13747,13 @@
     </row>
     <row r="109">
       <c r="A109" t="s" s="2">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>583</v>
+        <v>586</v>
       </c>
       <c r="C109" t="s" s="2">
-        <v>583</v>
+        <v>586</v>
       </c>
       <c r="D109" s="2"/>
       <c r="E109" t="s" s="2">
@@ -13765,7 +13776,7 @@
         <v>79</v>
       </c>
       <c r="L109" t="s" s="2">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="M109" t="s" s="2">
         <v>144</v>
@@ -13839,13 +13850,13 @@
     </row>
     <row r="110">
       <c r="A110" t="s" s="2">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>584</v>
+        <v>587</v>
       </c>
       <c r="C110" t="s" s="2">
-        <v>584</v>
+        <v>587</v>
       </c>
       <c r="D110" s="2"/>
       <c r="E110" t="s" s="2">
@@ -13871,10 +13882,10 @@
         <v>129</v>
       </c>
       <c r="M110" t="s" s="2">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="N110" t="s" s="2">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="O110" t="s" s="2">
         <v>175</v>
@@ -13944,17 +13955,17 @@
     </row>
     <row r="111">
       <c r="A111" t="s" s="2">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>585</v>
+        <v>588</v>
       </c>
       <c r="C111" t="s" s="2">
-        <v>585</v>
+        <v>588</v>
       </c>
       <c r="D111" s="2"/>
       <c r="E111" t="s" s="2">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="F111" s="2"/>
       <c r="G111" t="s" s="2">
@@ -13976,10 +13987,10 @@
         <v>129</v>
       </c>
       <c r="M111" t="s" s="2">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="N111" t="s" s="2">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="O111" t="s" s="2">
         <v>175</v>
@@ -14034,7 +14045,7 @@
         <v>79</v>
       </c>
       <c r="AG111" t="s" s="2">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="AH111" t="s" s="2">
         <v>77</v>
@@ -14051,13 +14062,13 @@
     </row>
     <row r="112">
       <c r="A112" t="s" s="2">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>586</v>
+        <v>589</v>
       </c>
       <c r="C112" t="s" s="2">
-        <v>586</v>
+        <v>589</v>
       </c>
       <c r="D112" s="2"/>
       <c r="E112" t="s" s="2">
@@ -14080,16 +14091,16 @@
         <v>87</v>
       </c>
       <c r="L112" t="s" s="2">
-        <v>587</v>
+        <v>590</v>
       </c>
       <c r="M112" t="s" s="2">
-        <v>588</v>
+        <v>591</v>
       </c>
       <c r="N112" t="s" s="2">
-        <v>589</v>
+        <v>592</v>
       </c>
       <c r="O112" t="s" s="2">
-        <v>590</v>
+        <v>593</v>
       </c>
       <c r="P112" s="2"/>
       <c r="Q112" t="s" s="2">
@@ -14139,7 +14150,7 @@
         <v>79</v>
       </c>
       <c r="AG112" t="s" s="2">
-        <v>586</v>
+        <v>589</v>
       </c>
       <c r="AH112" t="s" s="2">
         <v>86</v>
@@ -14156,13 +14167,13 @@
     </row>
     <row r="113">
       <c r="A113" t="s" s="2">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>591</v>
+        <v>594</v>
       </c>
       <c r="C113" t="s" s="2">
-        <v>591</v>
+        <v>594</v>
       </c>
       <c r="D113" s="2"/>
       <c r="E113" t="s" s="2">
@@ -14188,10 +14199,10 @@
         <v>106</v>
       </c>
       <c r="M113" t="s" s="2">
-        <v>592</v>
+        <v>595</v>
       </c>
       <c r="N113" t="s" s="2">
-        <v>593</v>
+        <v>596</v>
       </c>
       <c r="O113" s="2"/>
       <c r="P113" s="2"/>
@@ -14221,28 +14232,28 @@
         <v>189</v>
       </c>
       <c r="Z113" t="s" s="2">
-        <v>593</v>
+        <v>596</v>
       </c>
       <c r="AA113" t="s" s="2">
+        <v>597</v>
+      </c>
+      <c r="AB113" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC113" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD113" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE113" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF113" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AG113" t="s" s="2">
         <v>594</v>
-      </c>
-      <c r="AB113" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC113" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD113" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE113" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF113" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AG113" t="s" s="2">
-        <v>591</v>
       </c>
       <c r="AH113" t="s" s="2">
         <v>86</v>

--- a/currentbuild/all-profiles.xlsx
+++ b/currentbuild/all-profiles.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3842" uniqueCount="598">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3842" uniqueCount="597">
   <si>
     <t>Property</t>
   </si>
@@ -36,7 +36,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.1.3</t>
+    <t>0.1.4</t>
   </si>
   <si>
     <t>Name</t>
@@ -454,28 +454,32 @@
     <t>The date or estimated date that the allergy or intolerance resolved. This is called abatement because of the many overloaded connotations associated with resolution.</t>
   </si>
   <si>
-    <t>Age is generally used when the patient reports an age at which the allergy or intolerance abated. If there is no abatement element, the clinicalStatus can be used to convey whether allergy or intolerance has resolved or not. When abatementString exists, it conveys that the allergy or intolerance is abated.</t>
-  </si>
-  <si>
-    <t>AllergyIntolerance.extension:abatement.id</t>
-  </si>
-  <si>
-    <t>AllergyIntolerance.extension.id</t>
-  </si>
-  <si>
-    <t>Unique id for inter-element referencing</t>
-  </si>
-  <si>
-    <t>Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
-  </si>
-  <si>
-    <t>Element.id</t>
+    <t>Age is generally used when the patient reports an age at which the AllergyIntolerance was abated. Period is generally used to convey an imprecise abatement date that occurred within the time period. Range is generally used to convey an imprecise age range (e.g. 4 to 6 years old). If there is no abatement element, the clinicalStatus can be used to convey whether allergy or intolerance has resolved or not. When abatementString exists, it conveys that the allergy or intolerance is abated.</t>
   </si>
   <si>
     <t xml:space="preserve">ele-1
 </t>
   </si>
   <si>
+    <t>AllergyIntolerance.extension:abatement.id</t>
+  </si>
+  <si>
+    <t>AllergyIntolerance.extension.id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">string
+</t>
+  </si>
+  <si>
+    <t>Unique id for inter-element referencing</t>
+  </si>
+  <si>
+    <t>Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
+  </si>
+  <si>
+    <t>Element.id</t>
+  </si>
+  <si>
     <t>AllergyIntolerance.extension:abatement.extension</t>
   </si>
   <si>
@@ -522,7 +526,7 @@
     <t>Value of extension</t>
   </si>
   <si>
-    <t>Value of extension - must be one of a constrained set of the data types (see [Extensibility](http://hl7.org/fhir/R5/extensibility.html) for a list).</t>
+    <t>Value of extension - must be one of a constrained set of the data types (see [Extensibility](http://hl7.org/fhir/R4/extensibility.html) for a list).</t>
   </si>
   <si>
     <t xml:space="preserve">type:$this}
@@ -532,10 +536,6 @@
     <t>Extension.value[x]</t>
   </si>
   <si>
-    <t xml:space="preserve">ext-1
-</t>
-  </si>
-  <si>
     <t>AllergyIntolerance.extension:abatement.value[x]:valueDateTime</t>
   </si>
   <si>
@@ -627,7 +627,7 @@
     <t>Assertion about certainty associated with the propensity, or potential risk, of a reaction to the identified substance (including pharmaceutical product).</t>
   </si>
   <si>
-    <t>The data type is CodeableConcept because verificationStatus has some clinical judgment involved, such that there might need to be more specificity than the required FHIR value set allows. For example, a SNOMED coding might allow for additional specificity.</t>
+    <t>Import need to handle missing verificationStatus</t>
   </si>
   <si>
     <t>Assertion about certainty associated with a propensity, or potential risk, of a reaction to the identified substance.</t>
@@ -693,7 +693,7 @@
     <t>Estimate of the potential clinical harm, or seriousness, of the reaction to the identified substance.</t>
   </si>
   <si>
-    <t>The default criticality value for any propensity to an adverse reaction should be 'Low Risk', indicating at the very least a relative contraindication to deliberate or voluntary exposure to the substance. 'High Risk' is flagged if the clinician has identified a propensity for a more serious or potentially life-threatening reaction, such as anaphylaxis, and implies an absolute contraindication to deliberate or voluntary exposure to the substance. If this element is missing, the criticality is unknown (though it may be known elsewhere).  Systems that capture a severity at the condition level are actually representing the concept of criticality whereas the severity documented at the reaction level is representing the true reaction severity.  Existing systems that are capturing both condition criticality and reaction severity may use the term "severity" to represent both.  Criticality is the worst it could be in the future (i.e. situation-agnostic) whereas severity is situation-dependent.</t>
+    <t>Import need to handle missing criticality</t>
   </si>
   <si>
     <t>Estimate of the potential clinical harm, or seriousness, of a reaction to an identified substance.</t>
@@ -858,10 +858,6 @@
     <t>AllergyIntolerance.note.id</t>
   </si>
   <si>
-    <t xml:space="preserve">string
-</t>
-  </si>
-  <si>
     <t>AllergyIntolerance.note.extension</t>
   </si>
   <si>
@@ -1186,7 +1182,7 @@
     <t>Sex for clinical use</t>
   </si>
   <si>
-    <t>A parameter that provides guidance on how a recipient should apply settings or reference ranges that are derived from observable information such as an organ inventory, recent hormone lab tests, genetic testing, menstrual status, obstetric history, etc..</t>
+    <t>A parameter that provides guidance on how a recipient should apply settings or reference ranges that are derived from observable information such as an organ inventory, recent hormone lab tests, genetic testing, menstrual status, obstetric history, etc.</t>
   </si>
   <si>
     <t>Patient.extension:gender-identity</t>
@@ -2209,7 +2205,7 @@
         <v>2</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>335</v>
+        <v>334</v>
       </c>
     </row>
     <row r="24">
@@ -2217,7 +2213,7 @@
         <v>4</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>336</v>
+        <v>335</v>
       </c>
     </row>
     <row r="25">
@@ -2233,7 +2229,7 @@
         <v>8</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>337</v>
+        <v>336</v>
       </c>
     </row>
     <row r="27">
@@ -2241,7 +2237,7 @@
         <v>10</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>338</v>
+        <v>337</v>
       </c>
     </row>
     <row r="28">
@@ -2295,7 +2291,7 @@
         <v>24</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>339</v>
+        <v>338</v>
       </c>
     </row>
     <row r="35">
@@ -2331,7 +2327,7 @@
         <v>32</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>340</v>
+        <v>339</v>
       </c>
     </row>
     <row r="40">
@@ -2339,7 +2335,7 @@
         <v>34</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>341</v>
+        <v>340</v>
       </c>
     </row>
     <row r="41">
@@ -3453,7 +3449,7 @@
         <v>78</v>
       </c>
       <c r="AJ10" t="s" s="2">
-        <v>79</v>
+        <v>142</v>
       </c>
       <c r="AK10" t="s" s="2">
         <v>135</v>
@@ -3464,10 +3460,10 @@
         <v>3</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C11" t="s" s="2">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="D11" s="2"/>
       <c r="E11" t="s" s="2">
@@ -3490,13 +3486,13 @@
         <v>79</v>
       </c>
       <c r="L11" t="s" s="2">
-        <v>88</v>
+        <v>145</v>
       </c>
       <c r="M11" t="s" s="2">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="N11" t="s" s="2">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="O11" s="2"/>
       <c r="P11" s="2"/>
@@ -3547,7 +3543,7 @@
         <v>79</v>
       </c>
       <c r="AG11" t="s" s="2">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="AH11" t="s" s="2">
         <v>77</v>
@@ -3556,7 +3552,7 @@
         <v>86</v>
       </c>
       <c r="AJ11" t="s" s="2">
-        <v>147</v>
+        <v>79</v>
       </c>
       <c r="AK11" t="s" s="2">
         <v>79</v>
@@ -3567,10 +3563,10 @@
         <v>3</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="C12" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="D12" s="2"/>
       <c r="E12" t="s" s="2">
@@ -3641,7 +3637,7 @@
         <v>132</v>
       </c>
       <c r="AD12" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="AE12" t="s" s="2">
         <v>79</v>
@@ -3650,7 +3646,7 @@
         <v>133</v>
       </c>
       <c r="AG12" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="AH12" t="s" s="2">
         <v>77</v>
@@ -3670,10 +3666,10 @@
         <v>3</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C13" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="D13" s="2"/>
       <c r="E13" t="s" s="2">
@@ -3699,13 +3695,13 @@
         <v>100</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="N13" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="O13" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="P13" s="2"/>
       <c r="Q13" t="s" s="2">
@@ -3713,7 +3709,7 @@
       </c>
       <c r="R13" s="2"/>
       <c r="S13" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="T13" t="s" s="2">
         <v>79</v>
@@ -3755,7 +3751,7 @@
         <v>79</v>
       </c>
       <c r="AG13" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="AH13" t="s" s="2">
         <v>86</v>
@@ -3775,10 +3771,10 @@
         <v>3</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="C14" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="D14" s="2"/>
       <c r="E14" t="s" s="2">
@@ -3801,13 +3797,13 @@
         <v>79</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="N14" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="O14" s="2"/>
       <c r="P14" s="2"/>
@@ -3846,7 +3842,7 @@
         <v>79</v>
       </c>
       <c r="AC14" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="AD14" s="2"/>
       <c r="AE14" t="s" s="2">
@@ -3856,7 +3852,7 @@
         <v>133</v>
       </c>
       <c r="AG14" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="AH14" t="s" s="2">
         <v>77</v>
@@ -3865,7 +3861,7 @@
         <v>86</v>
       </c>
       <c r="AJ14" t="s" s="2">
-        <v>166</v>
+        <v>79</v>
       </c>
       <c r="AK14" t="s" s="2">
         <v>98</v>
@@ -3879,7 +3875,7 @@
         <v>167</v>
       </c>
       <c r="C15" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="D15" t="s" s="2">
         <v>168</v>
@@ -3910,7 +3906,7 @@
         <v>170</v>
       </c>
       <c r="N15" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="O15" s="2"/>
       <c r="P15" s="2"/>
@@ -3961,7 +3957,7 @@
         <v>79</v>
       </c>
       <c r="AG15" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="AH15" t="s" s="2">
         <v>77</v>
@@ -3970,7 +3966,7 @@
         <v>86</v>
       </c>
       <c r="AJ15" t="s" s="2">
-        <v>166</v>
+        <v>79</v>
       </c>
       <c r="AK15" t="s" s="2">
         <v>98</v>
@@ -4311,13 +4307,13 @@
       </c>
       <c r="F19" s="2"/>
       <c r="G19" t="s" s="2">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="H19" t="s" s="2">
         <v>86</v>
       </c>
       <c r="I19" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="J19" t="s" s="2">
         <v>87</v>
@@ -4626,7 +4622,7 @@
       </c>
       <c r="F22" s="2"/>
       <c r="G22" t="s" s="2">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="H22" t="s" s="2">
         <v>86</v>
@@ -5055,7 +5051,7 @@
         <v>79</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="M26" t="s" s="2">
         <v>235</v>
@@ -5100,7 +5096,7 @@
         <v>79</v>
       </c>
       <c r="AC26" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="AD26" s="2"/>
       <c r="AE26" t="s" s="2">
@@ -5786,13 +5782,13 @@
         <v>79</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>268</v>
+        <v>145</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="O33" s="2"/>
       <c r="P33" s="2"/>
@@ -5843,7 +5839,7 @@
         <v>79</v>
       </c>
       <c r="AG33" t="s" s="2">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="AH33" t="s" s="2">
         <v>77</v>
@@ -5863,10 +5859,10 @@
         <v>3</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="C34" t="s" s="2">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="D34" s="2"/>
       <c r="E34" t="s" s="2">
@@ -5892,10 +5888,10 @@
         <v>129</v>
       </c>
       <c r="M34" t="s" s="2">
+        <v>269</v>
+      </c>
+      <c r="N34" t="s" s="2">
         <v>270</v>
-      </c>
-      <c r="N34" t="s" s="2">
-        <v>271</v>
       </c>
       <c r="O34" t="s" s="2">
         <v>175</v>
@@ -5939,7 +5935,7 @@
         <v>132</v>
       </c>
       <c r="AD34" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="AE34" t="s" s="2">
         <v>79</v>
@@ -5948,7 +5944,7 @@
         <v>133</v>
       </c>
       <c r="AG34" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="AH34" t="s" s="2">
         <v>77</v>
@@ -5968,10 +5964,10 @@
         <v>3</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="C35" t="s" s="2">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="D35" s="2"/>
       <c r="E35" t="s" s="2">
@@ -5994,16 +5990,16 @@
         <v>87</v>
       </c>
       <c r="L35" t="s" s="2">
+        <v>272</v>
+      </c>
+      <c r="M35" t="s" s="2">
         <v>273</v>
       </c>
-      <c r="M35" t="s" s="2">
+      <c r="N35" t="s" s="2">
         <v>274</v>
       </c>
-      <c r="N35" t="s" s="2">
+      <c r="O35" t="s" s="2">
         <v>275</v>
-      </c>
-      <c r="O35" t="s" s="2">
-        <v>276</v>
       </c>
       <c r="P35" s="2"/>
       <c r="Q35" t="s" s="2">
@@ -6053,7 +6049,7 @@
         <v>79</v>
       </c>
       <c r="AG35" t="s" s="2">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="AH35" t="s" s="2">
         <v>77</v>
@@ -6073,10 +6069,10 @@
         <v>3</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="C36" t="s" s="2">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="D36" s="2"/>
       <c r="E36" t="s" s="2">
@@ -6102,10 +6098,10 @@
         <v>169</v>
       </c>
       <c r="M36" t="s" s="2">
+        <v>278</v>
+      </c>
+      <c r="N36" t="s" s="2">
         <v>279</v>
-      </c>
-      <c r="N36" t="s" s="2">
-        <v>280</v>
       </c>
       <c r="O36" s="2"/>
       <c r="P36" s="2"/>
@@ -6156,7 +6152,7 @@
         <v>79</v>
       </c>
       <c r="AG36" t="s" s="2">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="AH36" t="s" s="2">
         <v>77</v>
@@ -6176,10 +6172,10 @@
         <v>3</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="C37" t="s" s="2">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="D37" s="2"/>
       <c r="E37" t="s" s="2">
@@ -6202,13 +6198,13 @@
         <v>87</v>
       </c>
       <c r="L37" t="s" s="2">
+        <v>282</v>
+      </c>
+      <c r="M37" t="s" s="2">
         <v>283</v>
       </c>
-      <c r="M37" t="s" s="2">
+      <c r="N37" t="s" s="2">
         <v>284</v>
-      </c>
-      <c r="N37" t="s" s="2">
-        <v>285</v>
       </c>
       <c r="O37" s="2"/>
       <c r="P37" s="2"/>
@@ -6259,7 +6255,7 @@
         <v>79</v>
       </c>
       <c r="AG37" t="s" s="2">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="AH37" t="s" s="2">
         <v>86</v>
@@ -6279,10 +6275,10 @@
         <v>3</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="C38" t="s" s="2">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="D38" s="2"/>
       <c r="E38" t="s" s="2">
@@ -6305,13 +6301,13 @@
         <v>79</v>
       </c>
       <c r="L38" t="s" s="2">
+        <v>287</v>
+      </c>
+      <c r="M38" t="s" s="2">
         <v>288</v>
       </c>
-      <c r="M38" t="s" s="2">
+      <c r="N38" t="s" s="2">
         <v>289</v>
-      </c>
-      <c r="N38" t="s" s="2">
-        <v>290</v>
       </c>
       <c r="O38" s="2"/>
       <c r="P38" s="2"/>
@@ -6362,7 +6358,7 @@
         <v>79</v>
       </c>
       <c r="AG38" t="s" s="2">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="AH38" t="s" s="2">
         <v>77</v>
@@ -6382,10 +6378,10 @@
         <v>3</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="C39" t="s" s="2">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="D39" s="2"/>
       <c r="E39" t="s" s="2">
@@ -6408,13 +6404,13 @@
         <v>79</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>268</v>
+        <v>145</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="O39" s="2"/>
       <c r="P39" s="2"/>
@@ -6465,7 +6461,7 @@
         <v>79</v>
       </c>
       <c r="AG39" t="s" s="2">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="AH39" t="s" s="2">
         <v>77</v>
@@ -6485,10 +6481,10 @@
         <v>3</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="C40" t="s" s="2">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="D40" s="2"/>
       <c r="E40" t="s" s="2">
@@ -6514,10 +6510,10 @@
         <v>129</v>
       </c>
       <c r="M40" t="s" s="2">
+        <v>269</v>
+      </c>
+      <c r="N40" t="s" s="2">
         <v>270</v>
-      </c>
-      <c r="N40" t="s" s="2">
-        <v>271</v>
       </c>
       <c r="O40" t="s" s="2">
         <v>175</v>
@@ -6570,7 +6566,7 @@
         <v>79</v>
       </c>
       <c r="AG40" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="AH40" t="s" s="2">
         <v>77</v>
@@ -6590,14 +6586,14 @@
         <v>3</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="C41" t="s" s="2">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D41" s="2"/>
       <c r="E41" t="s" s="2">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="F41" s="2"/>
       <c r="G41" t="s" s="2">
@@ -6619,10 +6615,10 @@
         <v>129</v>
       </c>
       <c r="M41" t="s" s="2">
+        <v>294</v>
+      </c>
+      <c r="N41" t="s" s="2">
         <v>295</v>
-      </c>
-      <c r="N41" t="s" s="2">
-        <v>296</v>
       </c>
       <c r="O41" t="s" s="2">
         <v>175</v>
@@ -6677,7 +6673,7 @@
         <v>79</v>
       </c>
       <c r="AG41" t="s" s="2">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="AH41" t="s" s="2">
         <v>77</v>
@@ -6697,10 +6693,10 @@
         <v>3</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="C42" t="s" s="2">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="D42" s="2"/>
       <c r="E42" t="s" s="2">
@@ -6726,13 +6722,13 @@
         <v>185</v>
       </c>
       <c r="M42" t="s" s="2">
+        <v>298</v>
+      </c>
+      <c r="N42" t="s" s="2">
         <v>299</v>
       </c>
-      <c r="N42" t="s" s="2">
+      <c r="O42" t="s" s="2">
         <v>300</v>
-      </c>
-      <c r="O42" t="s" s="2">
-        <v>301</v>
       </c>
       <c r="P42" s="2"/>
       <c r="Q42" t="s" s="2">
@@ -6758,11 +6754,11 @@
         <v>79</v>
       </c>
       <c r="Y42" t="s" s="2">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="Z42" s="2"/>
       <c r="AA42" t="s" s="2">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="AB42" t="s" s="2">
         <v>79</v>
@@ -6780,7 +6776,7 @@
         <v>79</v>
       </c>
       <c r="AG42" t="s" s="2">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="AH42" t="s" s="2">
         <v>77</v>
@@ -6800,14 +6796,14 @@
         <v>3</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="C43" t="s" s="2">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="D43" s="2"/>
       <c r="E43" t="s" s="2">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="F43" s="2"/>
       <c r="G43" t="s" s="2">
@@ -6829,13 +6825,13 @@
         <v>185</v>
       </c>
       <c r="M43" t="s" s="2">
+        <v>305</v>
+      </c>
+      <c r="N43" t="s" s="2">
         <v>306</v>
       </c>
-      <c r="N43" t="s" s="2">
+      <c r="O43" t="s" s="2">
         <v>307</v>
-      </c>
-      <c r="O43" t="s" s="2">
-        <v>308</v>
       </c>
       <c r="P43" s="2"/>
       <c r="Q43" t="s" s="2">
@@ -6864,11 +6860,11 @@
         <v>110</v>
       </c>
       <c r="Z43" t="s" s="2">
+        <v>308</v>
+      </c>
+      <c r="AA43" t="s" s="2">
         <v>309</v>
       </c>
-      <c r="AA43" t="s" s="2">
-        <v>310</v>
-      </c>
       <c r="AB43" t="s" s="2">
         <v>79</v>
       </c>
@@ -6885,7 +6881,7 @@
         <v>79</v>
       </c>
       <c r="AG43" t="s" s="2">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="AH43" t="s" s="2">
         <v>86</v>
@@ -6905,14 +6901,14 @@
         <v>3</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="C44" t="s" s="2">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="D44" s="2"/>
       <c r="E44" t="s" s="2">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="F44" s="2"/>
       <c r="G44" t="s" s="2">
@@ -6931,16 +6927,16 @@
         <v>79</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>268</v>
+        <v>145</v>
       </c>
       <c r="M44" t="s" s="2">
+        <v>312</v>
+      </c>
+      <c r="N44" t="s" s="2">
         <v>313</v>
       </c>
-      <c r="N44" t="s" s="2">
+      <c r="O44" t="s" s="2">
         <v>314</v>
-      </c>
-      <c r="O44" t="s" s="2">
-        <v>315</v>
       </c>
       <c r="P44" s="2"/>
       <c r="Q44" t="s" s="2">
@@ -6990,7 +6986,7 @@
         <v>79</v>
       </c>
       <c r="AG44" t="s" s="2">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="AH44" t="s" s="2">
         <v>77</v>
@@ -7010,10 +7006,10 @@
         <v>3</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="C45" t="s" s="2">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="D45" s="2"/>
       <c r="E45" t="s" s="2">
@@ -7039,10 +7035,10 @@
         <v>169</v>
       </c>
       <c r="M45" t="s" s="2">
+        <v>316</v>
+      </c>
+      <c r="N45" t="s" s="2">
         <v>317</v>
-      </c>
-      <c r="N45" t="s" s="2">
-        <v>318</v>
       </c>
       <c r="O45" s="2"/>
       <c r="P45" s="2"/>
@@ -7093,7 +7089,7 @@
         <v>79</v>
       </c>
       <c r="AG45" t="s" s="2">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="AH45" t="s" s="2">
         <v>77</v>
@@ -7113,10 +7109,10 @@
         <v>3</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="C46" t="s" s="2">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="D46" s="2"/>
       <c r="E46" t="s" s="2">
@@ -7142,13 +7138,13 @@
         <v>106</v>
       </c>
       <c r="M46" t="s" s="2">
+        <v>319</v>
+      </c>
+      <c r="N46" t="s" s="2">
         <v>320</v>
       </c>
-      <c r="N46" t="s" s="2">
+      <c r="O46" t="s" s="2">
         <v>321</v>
-      </c>
-      <c r="O46" t="s" s="2">
-        <v>322</v>
       </c>
       <c r="P46" s="2"/>
       <c r="Q46" t="s" s="2">
@@ -7177,11 +7173,11 @@
         <v>189</v>
       </c>
       <c r="Z46" t="s" s="2">
+        <v>322</v>
+      </c>
+      <c r="AA46" t="s" s="2">
         <v>323</v>
       </c>
-      <c r="AA46" t="s" s="2">
-        <v>324</v>
-      </c>
       <c r="AB46" t="s" s="2">
         <v>79</v>
       </c>
@@ -7198,7 +7194,7 @@
         <v>79</v>
       </c>
       <c r="AG46" t="s" s="2">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="AH46" t="s" s="2">
         <v>77</v>
@@ -7218,10 +7214,10 @@
         <v>3</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="C47" t="s" s="2">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="D47" s="2"/>
       <c r="E47" t="s" s="2">
@@ -7247,13 +7243,13 @@
         <v>185</v>
       </c>
       <c r="M47" t="s" s="2">
+        <v>325</v>
+      </c>
+      <c r="N47" t="s" s="2">
         <v>326</v>
       </c>
-      <c r="N47" t="s" s="2">
+      <c r="O47" t="s" s="2">
         <v>327</v>
-      </c>
-      <c r="O47" t="s" s="2">
-        <v>328</v>
       </c>
       <c r="P47" s="2"/>
       <c r="Q47" t="s" s="2">
@@ -7279,14 +7275,14 @@
         <v>79</v>
       </c>
       <c r="Y47" t="s" s="2">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="Z47" t="s" s="2">
+        <v>328</v>
+      </c>
+      <c r="AA47" t="s" s="2">
         <v>329</v>
       </c>
-      <c r="AA47" t="s" s="2">
-        <v>330</v>
-      </c>
       <c r="AB47" t="s" s="2">
         <v>79</v>
       </c>
@@ -7303,7 +7299,7 @@
         <v>79</v>
       </c>
       <c r="AG47" t="s" s="2">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="AH47" t="s" s="2">
         <v>77</v>
@@ -7323,10 +7319,10 @@
         <v>3</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="C48" t="s" s="2">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="D48" s="2"/>
       <c r="E48" t="s" s="2">
@@ -7352,13 +7348,13 @@
         <v>263</v>
       </c>
       <c r="M48" t="s" s="2">
+        <v>331</v>
+      </c>
+      <c r="N48" t="s" s="2">
         <v>332</v>
       </c>
-      <c r="N48" t="s" s="2">
+      <c r="O48" t="s" s="2">
         <v>333</v>
-      </c>
-      <c r="O48" t="s" s="2">
-        <v>334</v>
       </c>
       <c r="P48" s="2"/>
       <c r="Q48" t="s" s="2">
@@ -7408,7 +7404,7 @@
         <v>79</v>
       </c>
       <c r="AG48" t="s" s="2">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="AH48" t="s" s="2">
         <v>77</v>
@@ -7425,17 +7421,17 @@
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="C49" t="s" s="2">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="D49" s="2"/>
       <c r="E49" t="s" s="2">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="F49" s="2"/>
       <c r="G49" t="s" s="2">
@@ -7457,10 +7453,10 @@
         <v>80</v>
       </c>
       <c r="M49" t="s" s="2">
+        <v>342</v>
+      </c>
+      <c r="N49" t="s" s="2">
         <v>343</v>
-      </c>
-      <c r="N49" t="s" s="2">
-        <v>344</v>
       </c>
       <c r="O49" s="2"/>
       <c r="P49" s="2"/>
@@ -7511,7 +7507,7 @@
         <v>79</v>
       </c>
       <c r="AG49" t="s" s="2">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="AH49" t="s" s="2">
         <v>77</v>
@@ -7523,18 +7519,18 @@
         <v>79</v>
       </c>
       <c r="AK49" t="s" s="2">
-        <v>345</v>
+        <v>344</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="C50" t="s" s="2">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="D50" s="2"/>
       <c r="E50" t="s" s="2">
@@ -7633,13 +7629,13 @@
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="C51" t="s" s="2">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="D51" s="2"/>
       <c r="E51" t="s" s="2">
@@ -7736,13 +7732,13 @@
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="C52" t="s" s="2">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="D52" s="2"/>
       <c r="E52" t="s" s="2">
@@ -7841,13 +7837,13 @@
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="C53" t="s" s="2">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="D53" s="2"/>
       <c r="E53" t="s" s="2">
@@ -7873,7 +7869,7 @@
         <v>106</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="N53" t="s" s="2">
         <v>108</v>
@@ -7946,13 +7942,13 @@
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="C54" t="s" s="2">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="D54" s="2"/>
       <c r="E54" t="s" s="2">
@@ -8051,13 +8047,13 @@
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="C55" t="s" s="2">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="D55" s="2"/>
       <c r="E55" t="s" s="2">
@@ -8156,13 +8152,13 @@
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="C56" t="s" s="2">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="D56" s="2"/>
       <c r="E56" t="s" s="2">
@@ -8257,16 +8253,16 @@
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="B57" t="s" s="2">
+        <v>353</v>
+      </c>
+      <c r="C57" t="s" s="2">
+        <v>352</v>
+      </c>
+      <c r="D57" t="s" s="2">
         <v>354</v>
-      </c>
-      <c r="C57" t="s" s="2">
-        <v>353</v>
-      </c>
-      <c r="D57" t="s" s="2">
-        <v>355</v>
       </c>
       <c r="E57" t="s" s="2">
         <v>79</v>
@@ -8288,13 +8284,13 @@
         <v>79</v>
       </c>
       <c r="L57" t="s" s="2">
+        <v>355</v>
+      </c>
+      <c r="M57" t="s" s="2">
         <v>356</v>
       </c>
-      <c r="M57" t="s" s="2">
+      <c r="N57" t="s" s="2">
         <v>357</v>
-      </c>
-      <c r="N57" t="s" s="2">
-        <v>358</v>
       </c>
       <c r="O57" s="2"/>
       <c r="P57" s="2"/>
@@ -8354,7 +8350,7 @@
         <v>78</v>
       </c>
       <c r="AJ57" t="s" s="2">
-        <v>79</v>
+        <v>142</v>
       </c>
       <c r="AK57" t="s" s="2">
         <v>135</v>
@@ -8362,13 +8358,13 @@
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="B58" t="s" s="2">
+        <v>358</v>
+      </c>
+      <c r="C58" t="s" s="2">
         <v>359</v>
-      </c>
-      <c r="C58" t="s" s="2">
-        <v>360</v>
       </c>
       <c r="D58" s="2"/>
       <c r="E58" t="s" s="2">
@@ -8391,13 +8387,13 @@
         <v>79</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>88</v>
+        <v>145</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="N58" t="s" s="2">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="O58" s="2"/>
       <c r="P58" s="2"/>
@@ -8448,7 +8444,7 @@
         <v>79</v>
       </c>
       <c r="AG58" t="s" s="2">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="AH58" t="s" s="2">
         <v>77</v>
@@ -8457,7 +8453,7 @@
         <v>86</v>
       </c>
       <c r="AJ58" t="s" s="2">
-        <v>147</v>
+        <v>79</v>
       </c>
       <c r="AK58" t="s" s="2">
         <v>79</v>
@@ -8465,13 +8461,13 @@
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="B59" t="s" s="2">
+        <v>360</v>
+      </c>
+      <c r="C59" t="s" s="2">
         <v>361</v>
-      </c>
-      <c r="C59" t="s" s="2">
-        <v>362</v>
       </c>
       <c r="D59" s="2"/>
       <c r="E59" t="s" s="2">
@@ -8542,7 +8538,7 @@
         <v>132</v>
       </c>
       <c r="AD59" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="AE59" t="s" s="2">
         <v>79</v>
@@ -8551,7 +8547,7 @@
         <v>133</v>
       </c>
       <c r="AG59" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="AH59" t="s" s="2">
         <v>77</v>
@@ -8568,13 +8564,13 @@
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="B60" t="s" s="2">
+        <v>362</v>
+      </c>
+      <c r="C60" t="s" s="2">
         <v>363</v>
-      </c>
-      <c r="C60" t="s" s="2">
-        <v>364</v>
       </c>
       <c r="D60" s="2"/>
       <c r="E60" t="s" s="2">
@@ -8600,13 +8596,13 @@
         <v>100</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="N60" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="O60" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="P60" s="2"/>
       <c r="Q60" t="s" s="2">
@@ -8614,7 +8610,7 @@
       </c>
       <c r="R60" s="2"/>
       <c r="S60" t="s" s="2">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="T60" t="s" s="2">
         <v>79</v>
@@ -8656,7 +8652,7 @@
         <v>79</v>
       </c>
       <c r="AG60" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="AH60" t="s" s="2">
         <v>86</v>
@@ -8673,13 +8669,13 @@
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="B61" t="s" s="2">
+        <v>365</v>
+      </c>
+      <c r="C61" t="s" s="2">
         <v>366</v>
-      </c>
-      <c r="C61" t="s" s="2">
-        <v>367</v>
       </c>
       <c r="D61" s="2"/>
       <c r="E61" t="s" s="2">
@@ -8702,13 +8698,13 @@
         <v>79</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="N61" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="O61" s="2"/>
       <c r="P61" s="2"/>
@@ -8759,7 +8755,7 @@
         <v>79</v>
       </c>
       <c r="AG61" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="AH61" t="s" s="2">
         <v>77</v>
@@ -8768,7 +8764,7 @@
         <v>86</v>
       </c>
       <c r="AJ61" t="s" s="2">
-        <v>166</v>
+        <v>79</v>
       </c>
       <c r="AK61" t="s" s="2">
         <v>98</v>
@@ -8776,16 +8772,16 @@
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="B62" t="s" s="2">
+        <v>368</v>
+      </c>
+      <c r="C62" t="s" s="2">
+        <v>352</v>
+      </c>
+      <c r="D62" t="s" s="2">
         <v>369</v>
-      </c>
-      <c r="C62" t="s" s="2">
-        <v>353</v>
-      </c>
-      <c r="D62" t="s" s="2">
-        <v>370</v>
       </c>
       <c r="E62" t="s" s="2">
         <v>79</v>
@@ -8807,13 +8803,13 @@
         <v>79</v>
       </c>
       <c r="L62" t="s" s="2">
+        <v>370</v>
+      </c>
+      <c r="M62" t="s" s="2">
         <v>371</v>
       </c>
-      <c r="M62" t="s" s="2">
+      <c r="N62" t="s" s="2">
         <v>372</v>
-      </c>
-      <c r="N62" t="s" s="2">
-        <v>373</v>
       </c>
       <c r="O62" s="2"/>
       <c r="P62" s="2"/>
@@ -8873,7 +8869,7 @@
         <v>78</v>
       </c>
       <c r="AJ62" t="s" s="2">
-        <v>79</v>
+        <v>142</v>
       </c>
       <c r="AK62" t="s" s="2">
         <v>135</v>
@@ -8881,16 +8877,16 @@
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="B63" t="s" s="2">
+        <v>373</v>
+      </c>
+      <c r="C63" t="s" s="2">
+        <v>352</v>
+      </c>
+      <c r="D63" t="s" s="2">
         <v>374</v>
-      </c>
-      <c r="C63" t="s" s="2">
-        <v>353</v>
-      </c>
-      <c r="D63" t="s" s="2">
-        <v>375</v>
       </c>
       <c r="E63" t="s" s="2">
         <v>79</v>
@@ -8912,16 +8908,16 @@
         <v>79</v>
       </c>
       <c r="L63" t="s" s="2">
+        <v>375</v>
+      </c>
+      <c r="M63" t="s" s="2">
         <v>376</v>
       </c>
-      <c r="M63" t="s" s="2">
+      <c r="N63" t="s" s="2">
         <v>377</v>
       </c>
-      <c r="N63" t="s" s="2">
+      <c r="O63" t="s" s="2">
         <v>378</v>
-      </c>
-      <c r="O63" t="s" s="2">
-        <v>379</v>
       </c>
       <c r="P63" s="2"/>
       <c r="Q63" t="s" s="2">
@@ -8980,7 +8976,7 @@
         <v>78</v>
       </c>
       <c r="AJ63" t="s" s="2">
-        <v>79</v>
+        <v>142</v>
       </c>
       <c r="AK63" t="s" s="2">
         <v>135</v>
@@ -8988,16 +8984,16 @@
     </row>
     <row r="64">
       <c r="A64" t="s" s="2">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="B64" t="s" s="2">
+        <v>379</v>
+      </c>
+      <c r="C64" t="s" s="2">
+        <v>352</v>
+      </c>
+      <c r="D64" t="s" s="2">
         <v>380</v>
-      </c>
-      <c r="C64" t="s" s="2">
-        <v>353</v>
-      </c>
-      <c r="D64" t="s" s="2">
-        <v>381</v>
       </c>
       <c r="E64" t="s" s="2">
         <v>79</v>
@@ -9019,13 +9015,13 @@
         <v>79</v>
       </c>
       <c r="L64" t="s" s="2">
+        <v>381</v>
+      </c>
+      <c r="M64" t="s" s="2">
         <v>382</v>
       </c>
-      <c r="M64" t="s" s="2">
+      <c r="N64" t="s" s="2">
         <v>383</v>
-      </c>
-      <c r="N64" t="s" s="2">
-        <v>384</v>
       </c>
       <c r="O64" s="2"/>
       <c r="P64" s="2"/>
@@ -9085,7 +9081,7 @@
         <v>78</v>
       </c>
       <c r="AJ64" t="s" s="2">
-        <v>79</v>
+        <v>142</v>
       </c>
       <c r="AK64" t="s" s="2">
         <v>135</v>
@@ -9093,16 +9089,16 @@
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="B65" t="s" s="2">
+        <v>384</v>
+      </c>
+      <c r="C65" t="s" s="2">
+        <v>352</v>
+      </c>
+      <c r="D65" t="s" s="2">
         <v>385</v>
-      </c>
-      <c r="C65" t="s" s="2">
-        <v>353</v>
-      </c>
-      <c r="D65" t="s" s="2">
-        <v>386</v>
       </c>
       <c r="E65" t="s" s="2">
         <v>79</v>
@@ -9124,13 +9120,13 @@
         <v>79</v>
       </c>
       <c r="L65" t="s" s="2">
+        <v>386</v>
+      </c>
+      <c r="M65" t="s" s="2">
         <v>387</v>
       </c>
-      <c r="M65" t="s" s="2">
+      <c r="N65" t="s" s="2">
         <v>388</v>
-      </c>
-      <c r="N65" t="s" s="2">
-        <v>389</v>
       </c>
       <c r="O65" s="2"/>
       <c r="P65" s="2"/>
@@ -9190,7 +9186,7 @@
         <v>78</v>
       </c>
       <c r="AJ65" t="s" s="2">
-        <v>79</v>
+        <v>142</v>
       </c>
       <c r="AK65" t="s" s="2">
         <v>135</v>
@@ -9198,16 +9194,16 @@
     </row>
     <row r="66">
       <c r="A66" t="s" s="2">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="B66" t="s" s="2">
+        <v>389</v>
+      </c>
+      <c r="C66" t="s" s="2">
+        <v>352</v>
+      </c>
+      <c r="D66" t="s" s="2">
         <v>390</v>
-      </c>
-      <c r="C66" t="s" s="2">
-        <v>353</v>
-      </c>
-      <c r="D66" t="s" s="2">
-        <v>391</v>
       </c>
       <c r="E66" t="s" s="2">
         <v>79</v>
@@ -9229,13 +9225,13 @@
         <v>79</v>
       </c>
       <c r="L66" t="s" s="2">
+        <v>391</v>
+      </c>
+      <c r="M66" t="s" s="2">
         <v>392</v>
       </c>
-      <c r="M66" t="s" s="2">
+      <c r="N66" t="s" s="2">
         <v>393</v>
-      </c>
-      <c r="N66" t="s" s="2">
-        <v>394</v>
       </c>
       <c r="O66" s="2"/>
       <c r="P66" s="2"/>
@@ -9295,7 +9291,7 @@
         <v>78</v>
       </c>
       <c r="AJ66" t="s" s="2">
-        <v>79</v>
+        <v>142</v>
       </c>
       <c r="AK66" t="s" s="2">
         <v>135</v>
@@ -9303,16 +9299,16 @@
     </row>
     <row r="67">
       <c r="A67" t="s" s="2">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="B67" t="s" s="2">
+        <v>394</v>
+      </c>
+      <c r="C67" t="s" s="2">
+        <v>352</v>
+      </c>
+      <c r="D67" t="s" s="2">
         <v>395</v>
-      </c>
-      <c r="C67" t="s" s="2">
-        <v>353</v>
-      </c>
-      <c r="D67" t="s" s="2">
-        <v>396</v>
       </c>
       <c r="E67" t="s" s="2">
         <v>79</v>
@@ -9334,16 +9330,16 @@
         <v>79</v>
       </c>
       <c r="L67" t="s" s="2">
+        <v>396</v>
+      </c>
+      <c r="M67" t="s" s="2">
         <v>397</v>
       </c>
-      <c r="M67" t="s" s="2">
+      <c r="N67" t="s" s="2">
         <v>398</v>
       </c>
-      <c r="N67" t="s" s="2">
+      <c r="O67" t="s" s="2">
         <v>399</v>
-      </c>
-      <c r="O67" t="s" s="2">
-        <v>400</v>
       </c>
       <c r="P67" s="2"/>
       <c r="Q67" t="s" s="2">
@@ -9402,7 +9398,7 @@
         <v>78</v>
       </c>
       <c r="AJ67" t="s" s="2">
-        <v>79</v>
+        <v>142</v>
       </c>
       <c r="AK67" t="s" s="2">
         <v>135</v>
@@ -9410,13 +9406,13 @@
     </row>
     <row r="68">
       <c r="A68" t="s" s="2">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="C68" t="s" s="2">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="D68" s="2"/>
       <c r="E68" t="s" s="2">
@@ -9517,13 +9513,13 @@
     </row>
     <row r="69">
       <c r="A69" t="s" s="2">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="C69" t="s" s="2">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="D69" s="2"/>
       <c r="E69" t="s" s="2">
@@ -9549,14 +9545,14 @@
         <v>179</v>
       </c>
       <c r="M69" t="s" s="2">
+        <v>402</v>
+      </c>
+      <c r="N69" t="s" s="2">
         <v>403</v>
-      </c>
-      <c r="N69" t="s" s="2">
-        <v>404</v>
       </c>
       <c r="O69" s="2"/>
       <c r="P69" t="s" s="2">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="Q69" t="s" s="2">
         <v>79</v>
@@ -9605,7 +9601,7 @@
         <v>79</v>
       </c>
       <c r="AG69" t="s" s="2">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="AH69" t="s" s="2">
         <v>77</v>
@@ -9622,13 +9618,13 @@
     </row>
     <row r="70">
       <c r="A70" t="s" s="2">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="C70" t="s" s="2">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="D70" s="2"/>
       <c r="E70" t="s" s="2">
@@ -9651,26 +9647,26 @@
         <v>87</v>
       </c>
       <c r="L70" t="s" s="2">
+        <v>406</v>
+      </c>
+      <c r="M70" t="s" s="2">
         <v>407</v>
       </c>
-      <c r="M70" t="s" s="2">
+      <c r="N70" t="s" s="2">
         <v>408</v>
       </c>
-      <c r="N70" t="s" s="2">
+      <c r="O70" t="s" s="2">
         <v>409</v>
       </c>
-      <c r="O70" t="s" s="2">
+      <c r="P70" t="s" s="2">
         <v>410</v>
       </c>
-      <c r="P70" t="s" s="2">
+      <c r="Q70" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="R70" t="s" s="2">
         <v>411</v>
       </c>
-      <c r="Q70" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="R70" t="s" s="2">
-        <v>412</v>
-      </c>
       <c r="S70" t="s" s="2">
         <v>79</v>
       </c>
@@ -9714,7 +9710,7 @@
         <v>79</v>
       </c>
       <c r="AG70" t="s" s="2">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="AH70" t="s" s="2">
         <v>77</v>
@@ -9731,13 +9727,13 @@
     </row>
     <row r="71">
       <c r="A71" t="s" s="2">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="C71" t="s" s="2">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="D71" s="2"/>
       <c r="E71" t="s" s="2">
@@ -9760,19 +9756,19 @@
         <v>87</v>
       </c>
       <c r="L71" t="s" s="2">
+        <v>413</v>
+      </c>
+      <c r="M71" t="s" s="2">
         <v>414</v>
       </c>
-      <c r="M71" t="s" s="2">
+      <c r="N71" t="s" s="2">
         <v>415</v>
       </c>
-      <c r="N71" t="s" s="2">
+      <c r="O71" t="s" s="2">
         <v>416</v>
       </c>
-      <c r="O71" t="s" s="2">
+      <c r="P71" t="s" s="2">
         <v>417</v>
-      </c>
-      <c r="P71" t="s" s="2">
-        <v>418</v>
       </c>
       <c r="Q71" t="s" s="2">
         <v>79</v>
@@ -9821,7 +9817,7 @@
         <v>79</v>
       </c>
       <c r="AG71" t="s" s="2">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="AH71" t="s" s="2">
         <v>77</v>
@@ -9833,18 +9829,18 @@
         <v>79</v>
       </c>
       <c r="AK71" t="s" s="2">
-        <v>419</v>
+        <v>418</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="s" s="2">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="C72" t="s" s="2">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="D72" s="2"/>
       <c r="E72" t="s" s="2">
@@ -9867,13 +9863,13 @@
         <v>79</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>268</v>
+        <v>145</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="N72" t="s" s="2">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="O72" s="2"/>
       <c r="P72" s="2"/>
@@ -9924,7 +9920,7 @@
         <v>79</v>
       </c>
       <c r="AG72" t="s" s="2">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="AH72" t="s" s="2">
         <v>77</v>
@@ -9941,13 +9937,13 @@
     </row>
     <row r="73">
       <c r="A73" t="s" s="2">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="C73" t="s" s="2">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="D73" s="2"/>
       <c r="E73" t="s" s="2">
@@ -9973,10 +9969,10 @@
         <v>129</v>
       </c>
       <c r="M73" t="s" s="2">
+        <v>269</v>
+      </c>
+      <c r="N73" t="s" s="2">
         <v>270</v>
-      </c>
-      <c r="N73" t="s" s="2">
-        <v>271</v>
       </c>
       <c r="O73" t="s" s="2">
         <v>175</v>
@@ -10020,7 +10016,7 @@
         <v>132</v>
       </c>
       <c r="AD73" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="AE73" t="s" s="2">
         <v>79</v>
@@ -10029,7 +10025,7 @@
         <v>133</v>
       </c>
       <c r="AG73" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="AH73" t="s" s="2">
         <v>77</v>
@@ -10046,13 +10042,13 @@
     </row>
     <row r="74">
       <c r="A74" t="s" s="2">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="C74" t="s" s="2">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="D74" s="2"/>
       <c r="E74" t="s" s="2">
@@ -10078,16 +10074,16 @@
         <v>106</v>
       </c>
       <c r="M74" t="s" s="2">
+        <v>422</v>
+      </c>
+      <c r="N74" t="s" s="2">
         <v>423</v>
       </c>
-      <c r="N74" t="s" s="2">
+      <c r="O74" t="s" s="2">
         <v>424</v>
       </c>
-      <c r="O74" t="s" s="2">
+      <c r="P74" t="s" s="2">
         <v>425</v>
-      </c>
-      <c r="P74" t="s" s="2">
-        <v>426</v>
       </c>
       <c r="Q74" t="s" s="2">
         <v>79</v>
@@ -10115,28 +10111,28 @@
         <v>189</v>
       </c>
       <c r="Z74" t="s" s="2">
+        <v>426</v>
+      </c>
+      <c r="AA74" t="s" s="2">
         <v>427</v>
       </c>
-      <c r="AA74" t="s" s="2">
+      <c r="AB74" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC74" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD74" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE74" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF74" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AG74" t="s" s="2">
         <v>428</v>
-      </c>
-      <c r="AB74" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC74" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD74" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE74" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF74" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AG74" t="s" s="2">
-        <v>429</v>
       </c>
       <c r="AH74" t="s" s="2">
         <v>77</v>
@@ -10153,13 +10149,13 @@
     </row>
     <row r="75">
       <c r="A75" t="s" s="2">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="C75" t="s" s="2">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="D75" s="2"/>
       <c r="E75" t="s" s="2">
@@ -10182,19 +10178,19 @@
         <v>87</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>268</v>
+        <v>145</v>
       </c>
       <c r="M75" t="s" s="2">
+        <v>430</v>
+      </c>
+      <c r="N75" t="s" s="2">
         <v>431</v>
       </c>
-      <c r="N75" t="s" s="2">
+      <c r="O75" t="s" s="2">
         <v>432</v>
       </c>
-      <c r="O75" t="s" s="2">
+      <c r="P75" t="s" s="2">
         <v>433</v>
-      </c>
-      <c r="P75" t="s" s="2">
-        <v>434</v>
       </c>
       <c r="Q75" t="s" s="2">
         <v>79</v>
@@ -10243,7 +10239,7 @@
         <v>79</v>
       </c>
       <c r="AG75" t="s" s="2">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="AH75" t="s" s="2">
         <v>77</v>
@@ -10260,17 +10256,17 @@
     </row>
     <row r="76">
       <c r="A76" t="s" s="2">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="C76" t="s" s="2">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="D76" s="2"/>
       <c r="E76" t="s" s="2">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="F76" s="2"/>
       <c r="G76" t="s" s="2">
@@ -10289,16 +10285,16 @@
         <v>87</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>268</v>
+        <v>145</v>
       </c>
       <c r="M76" t="s" s="2">
+        <v>437</v>
+      </c>
+      <c r="N76" t="s" s="2">
         <v>438</v>
       </c>
-      <c r="N76" t="s" s="2">
+      <c r="O76" t="s" s="2">
         <v>439</v>
-      </c>
-      <c r="O76" t="s" s="2">
-        <v>440</v>
       </c>
       <c r="P76" s="2"/>
       <c r="Q76" t="s" s="2">
@@ -10312,43 +10308,43 @@
         <v>79</v>
       </c>
       <c r="U76" t="s" s="2">
+        <v>440</v>
+      </c>
+      <c r="V76" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="W76" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="X76" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Y76" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Z76" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AA76" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB76" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC76" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD76" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE76" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF76" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AG76" t="s" s="2">
         <v>441</v>
-      </c>
-      <c r="V76" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="W76" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="X76" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Y76" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Z76" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AA76" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB76" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC76" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD76" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE76" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF76" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AG76" t="s" s="2">
-        <v>442</v>
       </c>
       <c r="AH76" t="s" s="2">
         <v>77</v>
@@ -10365,17 +10361,17 @@
     </row>
     <row r="77">
       <c r="A77" t="s" s="2">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="C77" t="s" s="2">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="D77" s="2"/>
       <c r="E77" t="s" s="2">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="F77" s="2"/>
       <c r="G77" t="s" s="2">
@@ -10394,16 +10390,16 @@
         <v>87</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>268</v>
+        <v>145</v>
       </c>
       <c r="M77" t="s" s="2">
+        <v>444</v>
+      </c>
+      <c r="N77" t="s" s="2">
         <v>445</v>
       </c>
-      <c r="N77" t="s" s="2">
+      <c r="O77" t="s" s="2">
         <v>446</v>
-      </c>
-      <c r="O77" t="s" s="2">
-        <v>447</v>
       </c>
       <c r="P77" s="2"/>
       <c r="Q77" t="s" s="2">
@@ -10453,7 +10449,7 @@
         <v>79</v>
       </c>
       <c r="AG77" t="s" s="2">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="AH77" t="s" s="2">
         <v>77</v>
@@ -10470,13 +10466,13 @@
     </row>
     <row r="78">
       <c r="A78" t="s" s="2">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="C78" t="s" s="2">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="D78" s="2"/>
       <c r="E78" t="s" s="2">
@@ -10499,13 +10495,13 @@
         <v>87</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>268</v>
+        <v>145</v>
       </c>
       <c r="M78" t="s" s="2">
+        <v>449</v>
+      </c>
+      <c r="N78" t="s" s="2">
         <v>450</v>
-      </c>
-      <c r="N78" t="s" s="2">
-        <v>451</v>
       </c>
       <c r="O78" s="2"/>
       <c r="P78" s="2"/>
@@ -10556,7 +10552,7 @@
         <v>79</v>
       </c>
       <c r="AG78" t="s" s="2">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="AH78" t="s" s="2">
         <v>77</v>
@@ -10573,13 +10569,13 @@
     </row>
     <row r="79">
       <c r="A79" t="s" s="2">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="C79" t="s" s="2">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="D79" s="2"/>
       <c r="E79" t="s" s="2">
@@ -10602,13 +10598,13 @@
         <v>87</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>268</v>
+        <v>145</v>
       </c>
       <c r="M79" t="s" s="2">
+        <v>453</v>
+      </c>
+      <c r="N79" t="s" s="2">
         <v>454</v>
-      </c>
-      <c r="N79" t="s" s="2">
-        <v>455</v>
       </c>
       <c r="O79" s="2"/>
       <c r="P79" s="2"/>
@@ -10659,7 +10655,7 @@
         <v>79</v>
       </c>
       <c r="AG79" t="s" s="2">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="AH79" t="s" s="2">
         <v>77</v>
@@ -10676,13 +10672,13 @@
     </row>
     <row r="80">
       <c r="A80" t="s" s="2">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="C80" t="s" s="2">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="D80" s="2"/>
       <c r="E80" t="s" s="2">
@@ -10705,17 +10701,17 @@
         <v>87</v>
       </c>
       <c r="L80" t="s" s="2">
+        <v>457</v>
+      </c>
+      <c r="M80" t="s" s="2">
         <v>458</v>
       </c>
-      <c r="M80" t="s" s="2">
+      <c r="N80" t="s" s="2">
         <v>459</v>
-      </c>
-      <c r="N80" t="s" s="2">
-        <v>460</v>
       </c>
       <c r="O80" s="2"/>
       <c r="P80" t="s" s="2">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="Q80" t="s" s="2">
         <v>79</v>
@@ -10764,7 +10760,7 @@
         <v>79</v>
       </c>
       <c r="AG80" t="s" s="2">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="AH80" t="s" s="2">
         <v>77</v>
@@ -10781,13 +10777,13 @@
     </row>
     <row r="81">
       <c r="A81" t="s" s="2">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="C81" t="s" s="2">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="D81" s="2"/>
       <c r="E81" t="s" s="2">
@@ -10810,19 +10806,19 @@
         <v>87</v>
       </c>
       <c r="L81" t="s" s="2">
+        <v>463</v>
+      </c>
+      <c r="M81" t="s" s="2">
         <v>464</v>
       </c>
-      <c r="M81" t="s" s="2">
+      <c r="N81" t="s" s="2">
         <v>465</v>
       </c>
-      <c r="N81" t="s" s="2">
+      <c r="O81" t="s" s="2">
         <v>466</v>
       </c>
-      <c r="O81" t="s" s="2">
+      <c r="P81" t="s" s="2">
         <v>467</v>
-      </c>
-      <c r="P81" t="s" s="2">
-        <v>468</v>
       </c>
       <c r="Q81" t="s" s="2">
         <v>79</v>
@@ -10871,7 +10867,7 @@
         <v>79</v>
       </c>
       <c r="AG81" t="s" s="2">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="AH81" t="s" s="2">
         <v>77</v>
@@ -10888,13 +10884,13 @@
     </row>
     <row r="82">
       <c r="A82" t="s" s="2">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="C82" t="s" s="2">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="D82" s="2"/>
       <c r="E82" t="s" s="2">
@@ -10920,16 +10916,16 @@
         <v>106</v>
       </c>
       <c r="M82" t="s" s="2">
+        <v>469</v>
+      </c>
+      <c r="N82" t="s" s="2">
         <v>470</v>
       </c>
-      <c r="N82" t="s" s="2">
+      <c r="O82" t="s" s="2">
         <v>471</v>
       </c>
-      <c r="O82" t="s" s="2">
+      <c r="P82" t="s" s="2">
         <v>472</v>
-      </c>
-      <c r="P82" t="s" s="2">
-        <v>473</v>
       </c>
       <c r="Q82" t="s" s="2">
         <v>79</v>
@@ -10957,11 +10953,11 @@
         <v>189</v>
       </c>
       <c r="Z82" t="s" s="2">
+        <v>473</v>
+      </c>
+      <c r="AA82" t="s" s="2">
         <v>474</v>
       </c>
-      <c r="AA82" t="s" s="2">
-        <v>475</v>
-      </c>
       <c r="AB82" t="s" s="2">
         <v>79</v>
       </c>
@@ -10978,7 +10974,7 @@
         <v>79</v>
       </c>
       <c r="AG82" t="s" s="2">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="AH82" t="s" s="2">
         <v>77</v>
@@ -10995,13 +10991,13 @@
     </row>
     <row r="83">
       <c r="A83" t="s" s="2">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="C83" t="s" s="2">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="D83" s="2"/>
       <c r="E83" t="s" s="2">
@@ -11024,19 +11020,19 @@
         <v>87</v>
       </c>
       <c r="L83" t="s" s="2">
+        <v>476</v>
+      </c>
+      <c r="M83" t="s" s="2">
         <v>477</v>
       </c>
-      <c r="M83" t="s" s="2">
+      <c r="N83" t="s" s="2">
         <v>478</v>
       </c>
-      <c r="N83" t="s" s="2">
+      <c r="O83" t="s" s="2">
         <v>479</v>
       </c>
-      <c r="O83" t="s" s="2">
+      <c r="P83" t="s" s="2">
         <v>480</v>
-      </c>
-      <c r="P83" t="s" s="2">
-        <v>481</v>
       </c>
       <c r="Q83" t="s" s="2">
         <v>79</v>
@@ -11085,7 +11081,7 @@
         <v>79</v>
       </c>
       <c r="AG83" t="s" s="2">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="AH83" t="s" s="2">
         <v>77</v>
@@ -11102,13 +11098,13 @@
     </row>
     <row r="84">
       <c r="A84" t="s" s="2">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="C84" t="s" s="2">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="D84" s="2"/>
       <c r="E84" t="s" s="2">
@@ -11131,19 +11127,19 @@
         <v>87</v>
       </c>
       <c r="L84" t="s" s="2">
+        <v>482</v>
+      </c>
+      <c r="M84" t="s" s="2">
         <v>483</v>
       </c>
-      <c r="M84" t="s" s="2">
+      <c r="N84" t="s" s="2">
         <v>484</v>
       </c>
-      <c r="N84" t="s" s="2">
+      <c r="O84" t="s" s="2">
         <v>485</v>
       </c>
-      <c r="O84" t="s" s="2">
+      <c r="P84" t="s" s="2">
         <v>486</v>
-      </c>
-      <c r="P84" t="s" s="2">
-        <v>487</v>
       </c>
       <c r="Q84" t="s" s="2">
         <v>79</v>
@@ -11192,7 +11188,7 @@
         <v>79</v>
       </c>
       <c r="AG84" t="s" s="2">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="AH84" t="s" s="2">
         <v>77</v>
@@ -11209,13 +11205,13 @@
     </row>
     <row r="85">
       <c r="A85" t="s" s="2">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="C85" t="s" s="2">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="D85" s="2"/>
       <c r="E85" t="s" s="2">
@@ -11238,19 +11234,19 @@
         <v>87</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="M85" t="s" s="2">
+        <v>488</v>
+      </c>
+      <c r="N85" t="s" s="2">
         <v>489</v>
       </c>
-      <c r="N85" t="s" s="2">
+      <c r="O85" t="s" s="2">
         <v>490</v>
       </c>
-      <c r="O85" t="s" s="2">
+      <c r="P85" t="s" s="2">
         <v>491</v>
-      </c>
-      <c r="P85" t="s" s="2">
-        <v>492</v>
       </c>
       <c r="Q85" t="s" s="2">
         <v>79</v>
@@ -11299,7 +11295,7 @@
         <v>79</v>
       </c>
       <c r="AG85" t="s" s="2">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="AH85" t="s" s="2">
         <v>77</v>
@@ -11316,13 +11312,13 @@
     </row>
     <row r="86">
       <c r="A86" t="s" s="2">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="C86" t="s" s="2">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="D86" s="2"/>
       <c r="E86" t="s" s="2">
@@ -11348,14 +11344,14 @@
         <v>185</v>
       </c>
       <c r="M86" t="s" s="2">
+        <v>493</v>
+      </c>
+      <c r="N86" t="s" s="2">
         <v>494</v>
-      </c>
-      <c r="N86" t="s" s="2">
-        <v>495</v>
       </c>
       <c r="O86" s="2"/>
       <c r="P86" t="s" s="2">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="Q86" t="s" s="2">
         <v>79</v>
@@ -11380,14 +11376,14 @@
         <v>79</v>
       </c>
       <c r="Y86" t="s" s="2">
+        <v>496</v>
+      </c>
+      <c r="Z86" t="s" s="2">
         <v>497</v>
       </c>
-      <c r="Z86" t="s" s="2">
+      <c r="AA86" t="s" s="2">
         <v>498</v>
       </c>
-      <c r="AA86" t="s" s="2">
-        <v>499</v>
-      </c>
       <c r="AB86" t="s" s="2">
         <v>79</v>
       </c>
@@ -11404,7 +11400,7 @@
         <v>79</v>
       </c>
       <c r="AG86" t="s" s="2">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="AH86" t="s" s="2">
         <v>77</v>
@@ -11421,13 +11417,13 @@
     </row>
     <row r="87">
       <c r="A87" t="s" s="2">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="C87" t="s" s="2">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="D87" s="2"/>
       <c r="E87" t="s" s="2">
@@ -11450,19 +11446,19 @@
         <v>79</v>
       </c>
       <c r="L87" t="s" s="2">
+        <v>500</v>
+      </c>
+      <c r="M87" t="s" s="2">
         <v>501</v>
       </c>
-      <c r="M87" t="s" s="2">
+      <c r="N87" t="s" s="2">
         <v>502</v>
       </c>
-      <c r="N87" t="s" s="2">
+      <c r="O87" t="s" s="2">
         <v>503</v>
       </c>
-      <c r="O87" t="s" s="2">
+      <c r="P87" t="s" s="2">
         <v>504</v>
-      </c>
-      <c r="P87" t="s" s="2">
-        <v>505</v>
       </c>
       <c r="Q87" t="s" s="2">
         <v>79</v>
@@ -11511,7 +11507,7 @@
         <v>79</v>
       </c>
       <c r="AG87" t="s" s="2">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="AH87" t="s" s="2">
         <v>77</v>
@@ -11528,13 +11524,13 @@
     </row>
     <row r="88">
       <c r="A88" t="s" s="2">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="C88" t="s" s="2">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="D88" s="2"/>
       <c r="E88" t="s" s="2">
@@ -11557,19 +11553,19 @@
         <v>79</v>
       </c>
       <c r="L88" t="s" s="2">
+        <v>506</v>
+      </c>
+      <c r="M88" t="s" s="2">
         <v>507</v>
       </c>
-      <c r="M88" t="s" s="2">
+      <c r="N88" t="s" s="2">
         <v>508</v>
       </c>
-      <c r="N88" t="s" s="2">
+      <c r="O88" t="s" s="2">
         <v>509</v>
       </c>
-      <c r="O88" t="s" s="2">
+      <c r="P88" t="s" s="2">
         <v>510</v>
-      </c>
-      <c r="P88" t="s" s="2">
-        <v>511</v>
       </c>
       <c r="Q88" t="s" s="2">
         <v>79</v>
@@ -11618,7 +11614,7 @@
         <v>79</v>
       </c>
       <c r="AG88" t="s" s="2">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="AH88" t="s" s="2">
         <v>77</v>
@@ -11635,13 +11631,13 @@
     </row>
     <row r="89">
       <c r="A89" t="s" s="2">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="C89" t="s" s="2">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="D89" s="2"/>
       <c r="E89" t="s" s="2">
@@ -11664,19 +11660,19 @@
         <v>79</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="M89" t="s" s="2">
+        <v>512</v>
+      </c>
+      <c r="N89" t="s" s="2">
         <v>513</v>
       </c>
-      <c r="N89" t="s" s="2">
+      <c r="O89" t="s" s="2">
         <v>514</v>
       </c>
-      <c r="O89" t="s" s="2">
+      <c r="P89" t="s" s="2">
         <v>515</v>
-      </c>
-      <c r="P89" t="s" s="2">
-        <v>516</v>
       </c>
       <c r="Q89" t="s" s="2">
         <v>79</v>
@@ -11725,7 +11721,7 @@
         <v>79</v>
       </c>
       <c r="AG89" t="s" s="2">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="AH89" t="s" s="2">
         <v>77</v>
@@ -11737,18 +11733,18 @@
         <v>79</v>
       </c>
       <c r="AK89" t="s" s="2">
-        <v>517</v>
+        <v>516</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="s" s="2">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="C90" t="s" s="2">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="D90" s="2"/>
       <c r="E90" t="s" s="2">
@@ -11771,13 +11767,13 @@
         <v>79</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>268</v>
+        <v>145</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="N90" t="s" s="2">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="O90" s="2"/>
       <c r="P90" s="2"/>
@@ -11828,7 +11824,7 @@
         <v>79</v>
       </c>
       <c r="AG90" t="s" s="2">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="AH90" t="s" s="2">
         <v>77</v>
@@ -11845,13 +11841,13 @@
     </row>
     <row r="91">
       <c r="A91" t="s" s="2">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="C91" t="s" s="2">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="D91" s="2"/>
       <c r="E91" t="s" s="2">
@@ -11877,10 +11873,10 @@
         <v>129</v>
       </c>
       <c r="M91" t="s" s="2">
+        <v>269</v>
+      </c>
+      <c r="N91" t="s" s="2">
         <v>270</v>
-      </c>
-      <c r="N91" t="s" s="2">
-        <v>271</v>
       </c>
       <c r="O91" t="s" s="2">
         <v>175</v>
@@ -11933,7 +11929,7 @@
         <v>79</v>
       </c>
       <c r="AG91" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="AH91" t="s" s="2">
         <v>77</v>
@@ -11950,17 +11946,17 @@
     </row>
     <row r="92">
       <c r="A92" t="s" s="2">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="C92" t="s" s="2">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="D92" s="2"/>
       <c r="E92" t="s" s="2">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="F92" s="2"/>
       <c r="G92" t="s" s="2">
@@ -11982,10 +11978,10 @@
         <v>129</v>
       </c>
       <c r="M92" t="s" s="2">
+        <v>294</v>
+      </c>
+      <c r="N92" t="s" s="2">
         <v>295</v>
-      </c>
-      <c r="N92" t="s" s="2">
-        <v>296</v>
       </c>
       <c r="O92" t="s" s="2">
         <v>175</v>
@@ -12040,7 +12036,7 @@
         <v>79</v>
       </c>
       <c r="AG92" t="s" s="2">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="AH92" t="s" s="2">
         <v>77</v>
@@ -12057,13 +12053,13 @@
     </row>
     <row r="93">
       <c r="A93" t="s" s="2">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="C93" t="s" s="2">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="D93" s="2"/>
       <c r="E93" t="s" s="2">
@@ -12089,14 +12085,14 @@
         <v>185</v>
       </c>
       <c r="M93" t="s" s="2">
+        <v>521</v>
+      </c>
+      <c r="N93" t="s" s="2">
         <v>522</v>
-      </c>
-      <c r="N93" t="s" s="2">
-        <v>523</v>
       </c>
       <c r="O93" s="2"/>
       <c r="P93" t="s" s="2">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="Q93" t="s" s="2">
         <v>79</v>
@@ -12121,14 +12117,14 @@
         <v>79</v>
       </c>
       <c r="Y93" t="s" s="2">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="Z93" t="s" s="2">
+        <v>524</v>
+      </c>
+      <c r="AA93" t="s" s="2">
         <v>525</v>
       </c>
-      <c r="AA93" t="s" s="2">
-        <v>526</v>
-      </c>
       <c r="AB93" t="s" s="2">
         <v>79</v>
       </c>
@@ -12145,7 +12141,7 @@
         <v>79</v>
       </c>
       <c r="AG93" t="s" s="2">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="AH93" t="s" s="2">
         <v>77</v>
@@ -12162,13 +12158,13 @@
     </row>
     <row r="94">
       <c r="A94" t="s" s="2">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="C94" t="s" s="2">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="D94" s="2"/>
       <c r="E94" t="s" s="2">
@@ -12191,17 +12187,17 @@
         <v>79</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="M94" t="s" s="2">
+        <v>527</v>
+      </c>
+      <c r="N94" t="s" s="2">
         <v>528</v>
-      </c>
-      <c r="N94" t="s" s="2">
-        <v>529</v>
       </c>
       <c r="O94" s="2"/>
       <c r="P94" t="s" s="2">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="Q94" t="s" s="2">
         <v>79</v>
@@ -12250,7 +12246,7 @@
         <v>79</v>
       </c>
       <c r="AG94" t="s" s="2">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="AH94" t="s" s="2">
         <v>77</v>
@@ -12267,13 +12263,13 @@
     </row>
     <row r="95">
       <c r="A95" t="s" s="2">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="C95" t="s" s="2">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="D95" s="2"/>
       <c r="E95" t="s" s="2">
@@ -12296,19 +12292,19 @@
         <v>79</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="M95" t="s" s="2">
+        <v>531</v>
+      </c>
+      <c r="N95" t="s" s="2">
         <v>532</v>
       </c>
-      <c r="N95" t="s" s="2">
+      <c r="O95" t="s" s="2">
         <v>533</v>
       </c>
-      <c r="O95" t="s" s="2">
-        <v>534</v>
-      </c>
       <c r="P95" t="s" s="2">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="Q95" t="s" s="2">
         <v>79</v>
@@ -12357,7 +12353,7 @@
         <v>79</v>
       </c>
       <c r="AG95" t="s" s="2">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="AH95" t="s" s="2">
         <v>77</v>
@@ -12374,13 +12370,13 @@
     </row>
     <row r="96">
       <c r="A96" t="s" s="2">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="C96" t="s" s="2">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="D96" s="2"/>
       <c r="E96" t="s" s="2">
@@ -12403,17 +12399,17 @@
         <v>79</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="M96" t="s" s="2">
+        <v>535</v>
+      </c>
+      <c r="N96" t="s" s="2">
         <v>536</v>
-      </c>
-      <c r="N96" t="s" s="2">
-        <v>537</v>
       </c>
       <c r="O96" s="2"/>
       <c r="P96" t="s" s="2">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="Q96" t="s" s="2">
         <v>79</v>
@@ -12462,7 +12458,7 @@
         <v>79</v>
       </c>
       <c r="AG96" t="s" s="2">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="AH96" t="s" s="2">
         <v>77</v>
@@ -12479,13 +12475,13 @@
     </row>
     <row r="97">
       <c r="A97" t="s" s="2">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="C97" t="s" s="2">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="D97" s="2"/>
       <c r="E97" t="s" s="2">
@@ -12511,14 +12507,14 @@
         <v>106</v>
       </c>
       <c r="M97" t="s" s="2">
+        <v>539</v>
+      </c>
+      <c r="N97" t="s" s="2">
         <v>540</v>
-      </c>
-      <c r="N97" t="s" s="2">
-        <v>541</v>
       </c>
       <c r="O97" s="2"/>
       <c r="P97" t="s" s="2">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="Q97" t="s" s="2">
         <v>79</v>
@@ -12546,11 +12542,11 @@
         <v>189</v>
       </c>
       <c r="Z97" t="s" s="2">
+        <v>473</v>
+      </c>
+      <c r="AA97" t="s" s="2">
         <v>474</v>
       </c>
-      <c r="AA97" t="s" s="2">
-        <v>475</v>
-      </c>
       <c r="AB97" t="s" s="2">
         <v>79</v>
       </c>
@@ -12567,7 +12563,7 @@
         <v>79</v>
       </c>
       <c r="AG97" t="s" s="2">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="AH97" t="s" s="2">
         <v>77</v>
@@ -12584,13 +12580,13 @@
     </row>
     <row r="98">
       <c r="A98" t="s" s="2">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="C98" t="s" s="2">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="D98" s="2"/>
       <c r="E98" t="s" s="2">
@@ -12613,17 +12609,17 @@
         <v>79</v>
       </c>
       <c r="L98" t="s" s="2">
+        <v>543</v>
+      </c>
+      <c r="M98" t="s" s="2">
         <v>544</v>
       </c>
-      <c r="M98" t="s" s="2">
+      <c r="N98" t="s" s="2">
         <v>545</v>
-      </c>
-      <c r="N98" t="s" s="2">
-        <v>546</v>
       </c>
       <c r="O98" s="2"/>
       <c r="P98" t="s" s="2">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="Q98" t="s" s="2">
         <v>79</v>
@@ -12672,7 +12668,7 @@
         <v>79</v>
       </c>
       <c r="AG98" t="s" s="2">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="AH98" t="s" s="2">
         <v>77</v>
@@ -12681,7 +12677,7 @@
         <v>86</v>
       </c>
       <c r="AJ98" t="s" s="2">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="AK98" t="s" s="2">
         <v>98</v>
@@ -12689,13 +12685,13 @@
     </row>
     <row r="99">
       <c r="A99" t="s" s="2">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="C99" t="s" s="2">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="D99" s="2"/>
       <c r="E99" t="s" s="2">
@@ -12718,13 +12714,13 @@
         <v>79</v>
       </c>
       <c r="L99" t="s" s="2">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="M99" t="s" s="2">
+        <v>549</v>
+      </c>
+      <c r="N99" t="s" s="2">
         <v>550</v>
-      </c>
-      <c r="N99" t="s" s="2">
-        <v>551</v>
       </c>
       <c r="O99" s="2"/>
       <c r="P99" s="2"/>
@@ -12775,7 +12771,7 @@
         <v>79</v>
       </c>
       <c r="AG99" t="s" s="2">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="AH99" t="s" s="2">
         <v>77</v>
@@ -12792,13 +12788,13 @@
     </row>
     <row r="100">
       <c r="A100" t="s" s="2">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="C100" t="s" s="2">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="D100" s="2"/>
       <c r="E100" t="s" s="2">
@@ -12821,19 +12817,19 @@
         <v>79</v>
       </c>
       <c r="L100" t="s" s="2">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="M100" t="s" s="2">
+        <v>552</v>
+      </c>
+      <c r="N100" t="s" s="2">
         <v>553</v>
       </c>
-      <c r="N100" t="s" s="2">
+      <c r="O100" t="s" s="2">
         <v>554</v>
       </c>
-      <c r="O100" t="s" s="2">
+      <c r="P100" t="s" s="2">
         <v>555</v>
-      </c>
-      <c r="P100" t="s" s="2">
-        <v>556</v>
       </c>
       <c r="Q100" t="s" s="2">
         <v>79</v>
@@ -12882,7 +12878,7 @@
         <v>79</v>
       </c>
       <c r="AG100" t="s" s="2">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="AH100" t="s" s="2">
         <v>77</v>
@@ -12899,13 +12895,13 @@
     </row>
     <row r="101">
       <c r="A101" t="s" s="2">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="C101" t="s" s="2">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="D101" s="2"/>
       <c r="E101" t="s" s="2">
@@ -12928,13 +12924,13 @@
         <v>79</v>
       </c>
       <c r="L101" t="s" s="2">
-        <v>268</v>
+        <v>145</v>
       </c>
       <c r="M101" t="s" s="2">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="N101" t="s" s="2">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="O101" s="2"/>
       <c r="P101" s="2"/>
@@ -12985,7 +12981,7 @@
         <v>79</v>
       </c>
       <c r="AG101" t="s" s="2">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="AH101" t="s" s="2">
         <v>77</v>
@@ -13002,13 +12998,13 @@
     </row>
     <row r="102">
       <c r="A102" t="s" s="2">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="C102" t="s" s="2">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="D102" s="2"/>
       <c r="E102" t="s" s="2">
@@ -13034,10 +13030,10 @@
         <v>129</v>
       </c>
       <c r="M102" t="s" s="2">
+        <v>269</v>
+      </c>
+      <c r="N102" t="s" s="2">
         <v>270</v>
-      </c>
-      <c r="N102" t="s" s="2">
-        <v>271</v>
       </c>
       <c r="O102" t="s" s="2">
         <v>175</v>
@@ -13090,7 +13086,7 @@
         <v>79</v>
       </c>
       <c r="AG102" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="AH102" t="s" s="2">
         <v>77</v>
@@ -13107,17 +13103,17 @@
     </row>
     <row r="103">
       <c r="A103" t="s" s="2">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="C103" t="s" s="2">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="D103" s="2"/>
       <c r="E103" t="s" s="2">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="F103" s="2"/>
       <c r="G103" t="s" s="2">
@@ -13139,10 +13135,10 @@
         <v>129</v>
       </c>
       <c r="M103" t="s" s="2">
+        <v>294</v>
+      </c>
+      <c r="N103" t="s" s="2">
         <v>295</v>
-      </c>
-      <c r="N103" t="s" s="2">
-        <v>296</v>
       </c>
       <c r="O103" t="s" s="2">
         <v>175</v>
@@ -13197,7 +13193,7 @@
         <v>79</v>
       </c>
       <c r="AG103" t="s" s="2">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="AH103" t="s" s="2">
         <v>77</v>
@@ -13214,13 +13210,13 @@
     </row>
     <row r="104">
       <c r="A104" t="s" s="2">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="C104" t="s" s="2">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="D104" s="2"/>
       <c r="E104" t="s" s="2">
@@ -13246,16 +13242,16 @@
         <v>185</v>
       </c>
       <c r="M104" t="s" s="2">
+        <v>560</v>
+      </c>
+      <c r="N104" t="s" s="2">
         <v>561</v>
       </c>
-      <c r="N104" t="s" s="2">
+      <c r="O104" t="s" s="2">
         <v>562</v>
       </c>
-      <c r="O104" t="s" s="2">
+      <c r="P104" t="s" s="2">
         <v>563</v>
-      </c>
-      <c r="P104" t="s" s="2">
-        <v>564</v>
       </c>
       <c r="Q104" t="s" s="2">
         <v>79</v>
@@ -13304,7 +13300,7 @@
         <v>79</v>
       </c>
       <c r="AG104" t="s" s="2">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="AH104" t="s" s="2">
         <v>86</v>
@@ -13321,13 +13317,13 @@
     </row>
     <row r="105">
       <c r="A105" t="s" s="2">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="C105" t="s" s="2">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="D105" s="2"/>
       <c r="E105" t="s" s="2">
@@ -13350,19 +13346,19 @@
         <v>79</v>
       </c>
       <c r="L105" t="s" s="2">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="M105" t="s" s="2">
+        <v>565</v>
+      </c>
+      <c r="N105" t="s" s="2">
         <v>566</v>
       </c>
-      <c r="N105" t="s" s="2">
+      <c r="O105" t="s" s="2">
         <v>567</v>
       </c>
-      <c r="O105" t="s" s="2">
+      <c r="P105" t="s" s="2">
         <v>568</v>
-      </c>
-      <c r="P105" t="s" s="2">
-        <v>569</v>
       </c>
       <c r="Q105" t="s" s="2">
         <v>79</v>
@@ -13411,7 +13407,7 @@
         <v>79</v>
       </c>
       <c r="AG105" t="s" s="2">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="AH105" t="s" s="2">
         <v>77</v>
@@ -13428,17 +13424,17 @@
     </row>
     <row r="106">
       <c r="A106" t="s" s="2">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="C106" t="s" s="2">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="D106" s="2"/>
       <c r="E106" t="s" s="2">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="F106" s="2"/>
       <c r="G106" t="s" s="2">
@@ -13457,16 +13453,16 @@
         <v>79</v>
       </c>
       <c r="L106" t="s" s="2">
+        <v>571</v>
+      </c>
+      <c r="M106" t="s" s="2">
         <v>572</v>
       </c>
-      <c r="M106" t="s" s="2">
+      <c r="N106" t="s" s="2">
         <v>573</v>
       </c>
-      <c r="N106" t="s" s="2">
+      <c r="O106" t="s" s="2">
         <v>574</v>
-      </c>
-      <c r="O106" t="s" s="2">
-        <v>575</v>
       </c>
       <c r="P106" s="2"/>
       <c r="Q106" t="s" s="2">
@@ -13516,7 +13512,7 @@
         <v>79</v>
       </c>
       <c r="AG106" t="s" s="2">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="AH106" t="s" s="2">
         <v>77</v>
@@ -13533,13 +13529,13 @@
     </row>
     <row r="107">
       <c r="A107" t="s" s="2">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="C107" t="s" s="2">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="D107" s="2"/>
       <c r="E107" t="s" s="2">
@@ -13562,19 +13558,19 @@
         <v>87</v>
       </c>
       <c r="L107" t="s" s="2">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="M107" t="s" s="2">
+        <v>576</v>
+      </c>
+      <c r="N107" t="s" s="2">
         <v>577</v>
       </c>
-      <c r="N107" t="s" s="2">
+      <c r="O107" t="s" s="2">
         <v>578</v>
       </c>
-      <c r="O107" t="s" s="2">
+      <c r="P107" t="s" s="2">
         <v>579</v>
-      </c>
-      <c r="P107" t="s" s="2">
-        <v>580</v>
       </c>
       <c r="Q107" t="s" s="2">
         <v>79</v>
@@ -13623,7 +13619,7 @@
         <v>79</v>
       </c>
       <c r="AG107" t="s" s="2">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="AH107" t="s" s="2">
         <v>77</v>
@@ -13640,13 +13636,13 @@
     </row>
     <row r="108">
       <c r="A108" t="s" s="2">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="C108" t="s" s="2">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="D108" s="2"/>
       <c r="E108" t="s" s="2">
@@ -13669,19 +13665,19 @@
         <v>87</v>
       </c>
       <c r="L108" t="s" s="2">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="M108" t="s" s="2">
+        <v>581</v>
+      </c>
+      <c r="N108" t="s" s="2">
         <v>582</v>
       </c>
-      <c r="N108" t="s" s="2">
+      <c r="O108" t="s" s="2">
         <v>583</v>
       </c>
-      <c r="O108" t="s" s="2">
+      <c r="P108" t="s" s="2">
         <v>584</v>
-      </c>
-      <c r="P108" t="s" s="2">
-        <v>585</v>
       </c>
       <c r="Q108" t="s" s="2">
         <v>79</v>
@@ -13730,7 +13726,7 @@
         <v>79</v>
       </c>
       <c r="AG108" t="s" s="2">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="AH108" t="s" s="2">
         <v>77</v>
@@ -13747,13 +13743,13 @@
     </row>
     <row r="109">
       <c r="A109" t="s" s="2">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="C109" t="s" s="2">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="D109" s="2"/>
       <c r="E109" t="s" s="2">
@@ -13776,13 +13772,13 @@
         <v>79</v>
       </c>
       <c r="L109" t="s" s="2">
-        <v>268</v>
+        <v>145</v>
       </c>
       <c r="M109" t="s" s="2">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="N109" t="s" s="2">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="O109" s="2"/>
       <c r="P109" s="2"/>
@@ -13833,7 +13829,7 @@
         <v>79</v>
       </c>
       <c r="AG109" t="s" s="2">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="AH109" t="s" s="2">
         <v>77</v>
@@ -13850,13 +13846,13 @@
     </row>
     <row r="110">
       <c r="A110" t="s" s="2">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="C110" t="s" s="2">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="D110" s="2"/>
       <c r="E110" t="s" s="2">
@@ -13882,10 +13878,10 @@
         <v>129</v>
       </c>
       <c r="M110" t="s" s="2">
+        <v>269</v>
+      </c>
+      <c r="N110" t="s" s="2">
         <v>270</v>
-      </c>
-      <c r="N110" t="s" s="2">
-        <v>271</v>
       </c>
       <c r="O110" t="s" s="2">
         <v>175</v>
@@ -13938,7 +13934,7 @@
         <v>79</v>
       </c>
       <c r="AG110" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="AH110" t="s" s="2">
         <v>77</v>
@@ -13955,17 +13951,17 @@
     </row>
     <row r="111">
       <c r="A111" t="s" s="2">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="C111" t="s" s="2">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="D111" s="2"/>
       <c r="E111" t="s" s="2">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="F111" s="2"/>
       <c r="G111" t="s" s="2">
@@ -13987,10 +13983,10 @@
         <v>129</v>
       </c>
       <c r="M111" t="s" s="2">
+        <v>294</v>
+      </c>
+      <c r="N111" t="s" s="2">
         <v>295</v>
-      </c>
-      <c r="N111" t="s" s="2">
-        <v>296</v>
       </c>
       <c r="O111" t="s" s="2">
         <v>175</v>
@@ -14045,7 +14041,7 @@
         <v>79</v>
       </c>
       <c r="AG111" t="s" s="2">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="AH111" t="s" s="2">
         <v>77</v>
@@ -14062,13 +14058,13 @@
     </row>
     <row r="112">
       <c r="A112" t="s" s="2">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="C112" t="s" s="2">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="D112" s="2"/>
       <c r="E112" t="s" s="2">
@@ -14091,16 +14087,16 @@
         <v>87</v>
       </c>
       <c r="L112" t="s" s="2">
+        <v>589</v>
+      </c>
+      <c r="M112" t="s" s="2">
         <v>590</v>
       </c>
-      <c r="M112" t="s" s="2">
+      <c r="N112" t="s" s="2">
         <v>591</v>
       </c>
-      <c r="N112" t="s" s="2">
+      <c r="O112" t="s" s="2">
         <v>592</v>
-      </c>
-      <c r="O112" t="s" s="2">
-        <v>593</v>
       </c>
       <c r="P112" s="2"/>
       <c r="Q112" t="s" s="2">
@@ -14150,7 +14146,7 @@
         <v>79</v>
       </c>
       <c r="AG112" t="s" s="2">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="AH112" t="s" s="2">
         <v>86</v>
@@ -14167,13 +14163,13 @@
     </row>
     <row r="113">
       <c r="A113" t="s" s="2">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="C113" t="s" s="2">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="D113" s="2"/>
       <c r="E113" t="s" s="2">
@@ -14199,10 +14195,10 @@
         <v>106</v>
       </c>
       <c r="M113" t="s" s="2">
+        <v>594</v>
+      </c>
+      <c r="N113" t="s" s="2">
         <v>595</v>
-      </c>
-      <c r="N113" t="s" s="2">
-        <v>596</v>
       </c>
       <c r="O113" s="2"/>
       <c r="P113" s="2"/>
@@ -14232,11 +14228,11 @@
         <v>189</v>
       </c>
       <c r="Z113" t="s" s="2">
+        <v>595</v>
+      </c>
+      <c r="AA113" t="s" s="2">
         <v>596</v>
       </c>
-      <c r="AA113" t="s" s="2">
-        <v>597</v>
-      </c>
       <c r="AB113" t="s" s="2">
         <v>79</v>
       </c>
@@ -14253,7 +14249,7 @@
         <v>79</v>
       </c>
       <c r="AG113" t="s" s="2">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="AH113" t="s" s="2">
         <v>86</v>

--- a/currentbuild/all-profiles.xlsx
+++ b/currentbuild/all-profiles.xlsx
@@ -36,7 +36,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.1.4</t>
+    <t>0.2.0</t>
   </si>
   <si>
     <t>Name</t>

--- a/currentbuild/all-profiles.xlsx
+++ b/currentbuild/all-profiles.xlsx
@@ -36,7 +36,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.2.0</t>
+    <t>0.2.1</t>
   </si>
   <si>
     <t>Name</t>
@@ -978,10 +978,10 @@
     <t>Clinical symptoms/signs associated with the Event</t>
   </si>
   <si>
-    <t>Clinical symptoms and/or signs that are observed or associated with the adverse reaction event.</t>
-  </si>
-  <si>
-    <t>Manifestation can be expressed as a single word, phrase or brief description. For example: nausea, rash or no reaction. It is preferable that manifestation should be coded with a terminology, where possible. The values entered here may be used to display on an application screen as part of a list of adverse reactions, as recommended in the UK NHS CUI guidelines.  Terminologies commonly used include, but are not limited to, SNOMED CT or ICD10.</t>
+    <t>Hvilken reaksjon pasienten har hatt.</t>
+  </si>
+  <si>
+    <t>Helse-NIM anbefaler KJ 7497 (Reaksjonstype) for koding av manifestasjon.</t>
   </si>
   <si>
     <t>Type of allergy or intolerance reaction expected to be used in MyHealth@EU</t>
@@ -1021,7 +1021,7 @@
     <t>Reaction severity</t>
   </si>
   <si>
-    <t>Clinical assessment of the severity of the reaction event as a whole, potentially considering multiple different manifestations.</t>
+    <t>Hvor alvorlig reaksjon pasienten har hatt.</t>
   </si>
   <si>
     <t>It is acknowledged that this assessment is very subjective. There may be some specific practice domains where objective scales have been applied. Objective scales can be included in this model as extensions.</t>
@@ -6292,7 +6292,7 @@
         <v>78</v>
       </c>
       <c r="I38" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="J38" t="s" s="2">
         <v>79</v>
@@ -6813,7 +6813,7 @@
         <v>78</v>
       </c>
       <c r="I43" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="J43" t="s" s="2">
         <v>79</v>
@@ -7126,7 +7126,7 @@
         <v>86</v>
       </c>
       <c r="I46" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="J46" t="s" s="2">
         <v>79</v>

--- a/currentbuild/all-profiles.xlsx
+++ b/currentbuild/all-profiles.xlsx
@@ -90,7 +90,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>Dummy-tekst: Helse-NIM for overfølsomhet er en liste som inneholder informasjon om unormale reaksjoner, symptomer eller funn initiert av eksponering for en definert stimulus i en dose som normalt tolereres av andre. Informasjon om en pasients overfølsomhet er relevant i mange situasjoner, som ved vaksinasjon, kost på institusjon, rekvirering og utlevering av legemidler, herunder inkludert muligheten til å dele informasjon om en avkreftet overfølsomhet.</t>
+    <t>Demo-profil for registrering av allergi og intoleranse med utgangspunkt i HL7 EU Core og relevante norske føringer for overfølsomhet.</t>
   </si>
   <si>
     <t>Purpose</t>
